--- a/research/traditional_assets/database/data/thailand/thailand_oil_gas_integrated.xlsx
+++ b/research/traditional_assets/database/data/thailand/thailand_oil_gas_integrated.xlsx
@@ -650,10 +650,10 @@
         <v>0.1142152540773733</v>
       </c>
       <c r="X2">
-        <v>0.1684248545115073</v>
+        <v>0.1683916769628458</v>
       </c>
       <c r="Y2">
-        <v>-0.05420960043413398</v>
+        <v>-0.05417642288547253</v>
       </c>
       <c r="Z2">
         <v>2.082536040000369</v>
@@ -662,10 +662,10 @@
         <v>0.08317758538426202</v>
       </c>
       <c r="AB2">
-        <v>0.1061927113708617</v>
+        <v>0.1061781953244433</v>
       </c>
       <c r="AC2">
-        <v>-0.0230151259865997</v>
+        <v>-0.02300060994018124</v>
       </c>
       <c r="AD2">
         <v>33899.4</v>
@@ -787,10 +787,10 @@
         <v>0.1142152540773733</v>
       </c>
       <c r="X3">
-        <v>0.1684248545115073</v>
+        <v>0.1683916769628458</v>
       </c>
       <c r="Y3">
-        <v>-0.05420960043413398</v>
+        <v>-0.05417642288547253</v>
       </c>
       <c r="Z3">
         <v>2.082536040000369</v>
@@ -799,10 +799,10 @@
         <v>0.08317758538426202</v>
       </c>
       <c r="AB3">
-        <v>0.1061927113708617</v>
+        <v>0.1061781953244433</v>
       </c>
       <c r="AC3">
-        <v>-0.0230151259865997</v>
+        <v>-0.02300060994018124</v>
       </c>
       <c r="AD3">
         <v>33899.4</v>
@@ -1139,7 +1139,7 @@
         <v>4.17011791774518</v>
       </c>
       <c r="F2">
-        <v>8.679026823922751</v>
+        <v>8.86276276680185</v>
       </c>
       <c r="G2">
         <v>3.1913029136679</v>
@@ -1157,13 +1157,13 @@
         <v>26421.8</v>
       </c>
       <c r="L2">
-        <v>50616.6620091681</v>
+        <v>50777.2499841777</v>
       </c>
       <c r="M2">
         <v>49390.870822207</v>
       </c>
       <c r="N2">
-        <v>49884.6040489433</v>
+        <v>50045.1920239529</v>
       </c>
       <c r="O2">
         <v>33967.270822207</v>
@@ -1172,16 +1172,16 @@
         <v>10266.1420397752</v>
       </c>
       <c r="Q2">
-        <v>0.106192711370862</v>
+        <v>0.106178195324443</v>
       </c>
       <c r="R2">
-        <v>0.105594974076461</v>
+        <v>0.10538877416876</v>
       </c>
       <c r="S2">
         <v>0.0577847822134061</v>
       </c>
       <c r="T2">
-        <v>0.0540247822134061</v>
+        <v>0.0529047822134061</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="W2">
-        <v>0.168424854511507</v>
+        <v>0.168391676962846</v>
       </c>
       <c r="X2">
-        <v>0.116157543494195</v>
+        <v>0.11613850746082</v>
       </c>
       <c r="Y2">
         <v>1.89645425378992</v>
@@ -1236,7 +1236,7 @@
         <v>26421.8</v>
       </c>
       <c r="AK2">
-        <v>0.0646600645739018</v>
+        <v>0.06464257005823122</v>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
@@ -1424,13 +1424,13 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0.1062521336440803</v>
+        <v>0.1062357776319679</v>
       </c>
       <c r="C2">
-        <v>60340.52137252543</v>
+        <v>60342.0119371553</v>
       </c>
       <c r="D2">
-        <v>49342.32137252542</v>
+        <v>49343.8119371553</v>
       </c>
       <c r="E2">
         <v>-33967.27082220704</v>
@@ -1475,19 +1475,19 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>0.1062521336440803</v>
+        <v>0.1062357776319679</v>
       </c>
       <c r="T2">
         <v>0.9349222590860211</v>
       </c>
       <c r="U2">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V2">
         <v>0.2</v>
       </c>
       <c r="W2">
-        <v>0.05402478221340606</v>
+        <v>0.05290478221340607</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -1506,13 +1506,13 @@
         <v>0.01</v>
       </c>
       <c r="B3">
-        <v>0.1062134771989262</v>
+        <v>0.1061859538988381</v>
       </c>
       <c r="C3">
-        <v>59768.20306881225</v>
+        <v>59778.83422191975</v>
       </c>
       <c r="D3">
-        <v>49373.89377703432</v>
+        <v>49384.52493014182</v>
       </c>
       <c r="E3">
         <v>-33363.38011398497</v>
@@ -1539,37 +1539,37 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M3">
-        <v>40.78132999049613</v>
+        <v>39.93588299898523</v>
       </c>
       <c r="N3">
-        <v>5976.237037356444</v>
+        <v>5977.082484347955</v>
       </c>
       <c r="O3">
-        <v>1195.247407471289</v>
+        <v>1195.416496869591</v>
       </c>
       <c r="P3">
-        <v>4780.989629885154</v>
+        <v>4781.665987478364</v>
       </c>
       <c r="Q3">
-        <v>9624.889629885154</v>
+        <v>9625.565987478363</v>
       </c>
       <c r="R3">
         <v>0.0101010101010101</v>
       </c>
       <c r="S3">
-        <v>0.1067406357341334</v>
+        <v>0.1067241475522263</v>
       </c>
       <c r="T3">
         <v>0.9424771864321708</v>
       </c>
       <c r="U3">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V3">
         <v>0.2</v>
       </c>
       <c r="W3">
-        <v>0.05402478221340606</v>
+        <v>0.05290478221340607</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>147.5434560066867</v>
+        <v>150.6669670356314</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1588,13 +1588,13 @@
         <v>0.02</v>
       </c>
       <c r="B4">
-        <v>0.1061748207537721</v>
+        <v>0.1061361301657082</v>
       </c>
       <c r="C4">
-        <v>59195.92519509648</v>
+        <v>59215.723745776</v>
       </c>
       <c r="D4">
-        <v>49405.50661154062</v>
+        <v>49425.30516222015</v>
       </c>
       <c r="E4">
         <v>-32759.4894057629</v>
@@ -1621,37 +1621,37 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M4">
-        <v>81.56265998099225</v>
+        <v>79.87176599797046</v>
       </c>
       <c r="N4">
-        <v>5935.455707365948</v>
+        <v>5937.14660134897</v>
       </c>
       <c r="O4">
-        <v>1187.09114147319</v>
+        <v>1187.429320269794</v>
       </c>
       <c r="P4">
-        <v>4748.364565892758</v>
+        <v>4749.717281079176</v>
       </c>
       <c r="Q4">
-        <v>9592.264565892758</v>
+        <v>9593.617281079176</v>
       </c>
       <c r="R4">
         <v>0.02040816326530612</v>
       </c>
       <c r="S4">
-        <v>0.1072391072545959</v>
+        <v>0.1072224842055511</v>
       </c>
       <c r="T4">
         <v>0.9501862959690581</v>
       </c>
       <c r="U4">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V4">
         <v>0.2</v>
       </c>
       <c r="W4">
-        <v>0.05402478221340606</v>
+        <v>0.05290478221340607</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>73.77172800334338</v>
+        <v>75.33348351781571</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1670,13 +1670,13 @@
         <v>0.03</v>
       </c>
       <c r="B5">
-        <v>0.106136164308618</v>
+        <v>0.1060863064325783</v>
       </c>
       <c r="C5">
-        <v>58623.68782908671</v>
+        <v>58652.68067543369</v>
       </c>
       <c r="D5">
-        <v>49437.15995375293</v>
+        <v>49466.15280009991</v>
       </c>
       <c r="E5">
         <v>-32155.59869754082</v>
@@ -1703,37 +1703,37 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M5">
-        <v>122.3439899714884</v>
+        <v>119.8076489969557</v>
       </c>
       <c r="N5">
-        <v>5894.674377375452</v>
+        <v>5897.210718349985</v>
       </c>
       <c r="O5">
-        <v>1178.93487547509</v>
+        <v>1179.442143669997</v>
       </c>
       <c r="P5">
-        <v>4715.739501900362</v>
+        <v>4717.768574679988</v>
       </c>
       <c r="Q5">
-        <v>9559.639501900361</v>
+        <v>9561.668574679989</v>
       </c>
       <c r="R5">
         <v>0.03092783505154639</v>
       </c>
       <c r="S5">
-        <v>0.1077478565383668</v>
+        <v>0.1077310958414187</v>
       </c>
       <c r="T5">
         <v>0.9580543562180462</v>
       </c>
       <c r="U5">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V5">
         <v>0.2</v>
       </c>
       <c r="W5">
-        <v>0.05402478221340606</v>
+        <v>0.05290478221340607</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>49.18115200222892</v>
+        <v>50.22232234521047</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1752,13 +1752,13 @@
         <v>0.04</v>
       </c>
       <c r="B6">
-        <v>0.1060975078634639</v>
+        <v>0.1060364826994484</v>
       </c>
       <c r="C6">
-        <v>58051.49104869088</v>
+        <v>58089.70517815397</v>
       </c>
       <c r="D6">
-        <v>49468.85388157917</v>
+        <v>49507.06801104225</v>
       </c>
       <c r="E6">
         <v>-31551.70798931875</v>
@@ -1785,37 +1785,37 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M6">
-        <v>163.1253199619845</v>
+        <v>159.7435319959409</v>
       </c>
       <c r="N6">
-        <v>5853.893047384956</v>
+        <v>5857.274835350999</v>
       </c>
       <c r="O6">
-        <v>1170.778609476991</v>
+        <v>1171.4549670702</v>
       </c>
       <c r="P6">
-        <v>4683.114437907965</v>
+        <v>4685.819868280799</v>
       </c>
       <c r="Q6">
-        <v>9527.014437907965</v>
+        <v>9529.719868280798</v>
       </c>
       <c r="R6">
         <v>0.04166666666666667</v>
       </c>
       <c r="S6">
-        <v>0.1082672047655496</v>
+        <v>0.1082503035530335</v>
       </c>
       <c r="T6">
         <v>0.9660863343888886</v>
       </c>
       <c r="U6">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V6">
         <v>0.2</v>
       </c>
       <c r="W6">
-        <v>0.05402478221340606</v>
+        <v>0.05290478221340607</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>36.88586400167169</v>
+        <v>37.66674175890785</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1834,13 +1834,13 @@
         <v>0.05</v>
       </c>
       <c r="B7">
-        <v>0.1060588514183098</v>
+        <v>0.1059866589663185</v>
       </c>
       <c r="C7">
-        <v>57479.3349320168</v>
+        <v>57526.79742175193</v>
       </c>
       <c r="D7">
-        <v>49500.58847312714</v>
+        <v>49548.05096286227</v>
       </c>
       <c r="E7">
         <v>-30947.81728109668</v>
@@ -1867,37 +1867,37 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M7">
-        <v>203.9066499524806</v>
+        <v>199.6794149949261</v>
       </c>
       <c r="N7">
-        <v>5813.111717394459</v>
+        <v>5817.338952352014</v>
       </c>
       <c r="O7">
-        <v>1162.622343478892</v>
+        <v>1163.467790470403</v>
       </c>
       <c r="P7">
-        <v>4650.489373915568</v>
+        <v>4653.871161881611</v>
       </c>
       <c r="Q7">
-        <v>9494.389373915568</v>
+        <v>9497.77116188161</v>
       </c>
       <c r="R7">
         <v>0.05263157894736843</v>
       </c>
       <c r="S7">
-        <v>0.1087974866396205</v>
+        <v>0.1087804419533139</v>
       </c>
       <c r="T7">
         <v>0.9742874068370114</v>
       </c>
       <c r="U7">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V7">
         <v>0.2</v>
       </c>
       <c r="W7">
-        <v>0.05402478221340606</v>
+        <v>0.05290478221340607</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>29.50869120133735</v>
+        <v>30.13339340712628</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1916,13 +1916,13 @@
         <v>0.06</v>
       </c>
       <c r="B8">
-        <v>0.1060201949731557</v>
+        <v>0.1059368352331887</v>
       </c>
       <c r="C8">
-        <v>56907.21955737274</v>
+        <v>56963.95757459871</v>
       </c>
       <c r="D8">
-        <v>49532.36380670517</v>
+        <v>49589.10182393114</v>
       </c>
       <c r="E8">
         <v>-30343.92657287461</v>
@@ -1949,37 +1949,37 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M8">
-        <v>244.6879799429767</v>
+        <v>239.6152979939114</v>
       </c>
       <c r="N8">
-        <v>5772.330387403963</v>
+        <v>5777.403069353029</v>
       </c>
       <c r="O8">
-        <v>1154.466077480793</v>
+        <v>1155.480613870606</v>
       </c>
       <c r="P8">
-        <v>4617.86430992317</v>
+        <v>4621.922455482423</v>
       </c>
       <c r="Q8">
-        <v>9461.76430992317</v>
+        <v>9465.822455482423</v>
       </c>
       <c r="R8">
         <v>0.06382978723404255</v>
       </c>
       <c r="S8">
-        <v>0.1093390511067567</v>
+        <v>0.1093218598940259</v>
       </c>
       <c r="T8">
         <v>0.9826629701882861</v>
       </c>
       <c r="U8">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V8">
         <v>0.2</v>
       </c>
       <c r="W8">
-        <v>0.05402478221340606</v>
+        <v>0.05290478221340607</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>24.59057600111446</v>
+        <v>25.11116117260524</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1998,13 +1998,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="B9">
-        <v>0.1059815385280016</v>
+        <v>0.1058870115000588</v>
       </c>
       <c r="C9">
-        <v>56335.14500326838</v>
+        <v>56401.185805624</v>
       </c>
       <c r="D9">
-        <v>49564.17996082287</v>
+        <v>49630.22076317849</v>
       </c>
       <c r="E9">
         <v>-29740.03586465254</v>
@@ -2031,37 +2031,37 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M9">
-        <v>285.4693099334729</v>
+        <v>279.5511809928966</v>
       </c>
       <c r="N9">
-        <v>5731.549057413467</v>
+        <v>5737.467186354043</v>
       </c>
       <c r="O9">
-        <v>1146.309811482693</v>
+        <v>1147.493437270809</v>
       </c>
       <c r="P9">
-        <v>4585.239245930774</v>
+        <v>4589.973749083235</v>
       </c>
       <c r="Q9">
-        <v>9429.139245930774</v>
+        <v>9433.873749083235</v>
       </c>
       <c r="R9">
         <v>0.07526881720430109</v>
       </c>
       <c r="S9">
-        <v>0.1098922621215733</v>
+        <v>0.1098749212313122</v>
       </c>
       <c r="T9">
         <v>0.9912186531815236</v>
       </c>
       <c r="U9">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V9">
         <v>0.2</v>
       </c>
       <c r="W9">
-        <v>0.05402478221340606</v>
+        <v>0.05290478221340607</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>21.07763657238382</v>
+        <v>21.52385243366163</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2080,13 +2080,13 @@
         <v>0.08</v>
       </c>
       <c r="B10">
-        <v>0.1059428820828475</v>
+        <v>0.1058371877669289</v>
       </c>
       <c r="C10">
-        <v>55763.11134841506</v>
+        <v>55838.48228431815</v>
       </c>
       <c r="D10">
-        <v>49596.03701419162</v>
+        <v>49671.40795009471</v>
       </c>
       <c r="E10">
         <v>-29136.14515643047</v>
@@ -2113,37 +2113,37 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M10">
-        <v>326.250639923969</v>
+        <v>319.4870639918818</v>
       </c>
       <c r="N10">
-        <v>5690.767727422971</v>
+        <v>5697.531303355058</v>
       </c>
       <c r="O10">
-        <v>1138.153545484594</v>
+        <v>1139.506260671012</v>
       </c>
       <c r="P10">
-        <v>4552.614181938377</v>
+        <v>4558.025042684047</v>
       </c>
       <c r="Q10">
-        <v>9396.514181938375</v>
+        <v>9401.925042684046</v>
       </c>
       <c r="R10">
         <v>0.08695652173913043</v>
       </c>
       <c r="S10">
-        <v>0.1104574994627989</v>
+        <v>0.1104400056411483</v>
       </c>
       <c r="T10">
         <v>0.9999603292833096</v>
       </c>
       <c r="U10">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V10">
         <v>0.2</v>
       </c>
       <c r="W10">
-        <v>0.05402478221340606</v>
+        <v>0.05290478221340607</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>18.44293200083584</v>
+        <v>18.83337087945393</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2162,13 +2162,13 @@
         <v>0.09</v>
       </c>
       <c r="B11">
-        <v>0.1059042256376934</v>
+        <v>0.105787364033799</v>
       </c>
       <c r="C11">
-        <v>55191.1186717267</v>
+        <v>55275.84718073471</v>
       </c>
       <c r="D11">
-        <v>49627.93504572532</v>
+        <v>49712.66355473334</v>
       </c>
       <c r="E11">
         <v>-28532.2544482084</v>
@@ -2195,37 +2195,37 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M11">
-        <v>367.0319699144651</v>
+        <v>359.422946990867</v>
       </c>
       <c r="N11">
-        <v>5649.986397432475</v>
+        <v>5657.595420356073</v>
       </c>
       <c r="O11">
-        <v>1129.997279486495</v>
+        <v>1131.519084071215</v>
       </c>
       <c r="P11">
-        <v>4519.98911794598</v>
+        <v>4526.076336284858</v>
       </c>
       <c r="Q11">
-        <v>9363.889117945979</v>
+        <v>9369.976336284857</v>
       </c>
       <c r="R11">
         <v>0.0989010989010989</v>
       </c>
       <c r="S11">
-        <v>0.1110351596027328</v>
+        <v>0.1110175094885632</v>
       </c>
       <c r="T11">
         <v>1.008894130134585</v>
       </c>
       <c r="U11">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V11">
         <v>0.2</v>
       </c>
       <c r="W11">
-        <v>0.05402478221340606</v>
+        <v>0.05290478221340607</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>16.39371733407631</v>
+        <v>16.74077411507016</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2244,13 +2244,13 @@
         <v>0.1</v>
       </c>
       <c r="B12">
-        <v>0.1058655691925393</v>
+        <v>0.1057375403006692</v>
       </c>
       <c r="C12">
-        <v>54619.16705232031</v>
+        <v>54713.28066549253</v>
       </c>
       <c r="D12">
-        <v>49659.87413454102</v>
+        <v>49753.98774771324</v>
       </c>
       <c r="E12">
         <v>-27928.36373998633</v>
@@ -2277,37 +2277,37 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M12">
-        <v>407.8132999049612</v>
+        <v>399.3588299898523</v>
       </c>
       <c r="N12">
-        <v>5609.205067441979</v>
+        <v>5617.659537357088</v>
       </c>
       <c r="O12">
-        <v>1121.841013488396</v>
+        <v>1123.531907471418</v>
       </c>
       <c r="P12">
-        <v>4487.364053953583</v>
+        <v>4494.12762988567</v>
       </c>
       <c r="Q12">
-        <v>9331.264053953582</v>
+        <v>9338.02762988567</v>
       </c>
       <c r="R12">
         <v>0.1111111111111111</v>
       </c>
       <c r="S12">
-        <v>0.1116256566346652</v>
+        <v>0.1116078467548095</v>
       </c>
       <c r="T12">
         <v>1.018026459893667</v>
       </c>
       <c r="U12">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V12">
         <v>0.2</v>
       </c>
       <c r="W12">
-        <v>0.05402478221340606</v>
+        <v>0.05290478221340607</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>14.75434560066867</v>
+        <v>15.06669670356314</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2326,13 +2326,13 @@
         <v>0.11</v>
       </c>
       <c r="B13">
-        <v>0.1058269127473852</v>
+        <v>0.1056877165675393</v>
       </c>
       <c r="C13">
-        <v>54047.25656951682</v>
+        <v>54150.78290977842</v>
       </c>
       <c r="D13">
-        <v>49691.8543599596</v>
+        <v>49795.38070022119</v>
       </c>
       <c r="E13">
         <v>-27324.47303176426</v>
@@ -2359,37 +2359,37 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M13">
-        <v>448.5946298954574</v>
+        <v>439.2947129888375</v>
       </c>
       <c r="N13">
-        <v>5568.423737451482</v>
+        <v>5577.723654358103</v>
       </c>
       <c r="O13">
-        <v>1113.684747490297</v>
+        <v>1115.544730871621</v>
       </c>
       <c r="P13">
-        <v>4454.738989961186</v>
+        <v>4462.178923486483</v>
       </c>
       <c r="Q13">
-        <v>9298.638989961186</v>
+        <v>9306.078923486482</v>
       </c>
       <c r="R13">
         <v>0.1235955056179775</v>
       </c>
       <c r="S13">
-        <v>0.1122294232628208</v>
+        <v>0.1122114500270389</v>
       </c>
       <c r="T13">
         <v>1.027364010546212</v>
       </c>
       <c r="U13">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V13">
         <v>0.2</v>
       </c>
       <c r="W13">
-        <v>0.05402478221340606</v>
+        <v>0.05290478221340607</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>13.41304145515334</v>
+        <v>13.69699700323922</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2408,13 +2408,13 @@
         <v>0.12</v>
       </c>
       <c r="B14">
-        <v>0.1057882563022311</v>
+        <v>0.1056378928344094</v>
       </c>
       <c r="C14">
-        <v>53475.38730284146</v>
+        <v>53588.35408534915</v>
       </c>
       <c r="D14">
-        <v>49723.87580150631</v>
+        <v>49836.842584014</v>
       </c>
       <c r="E14">
         <v>-26720.58232354219</v>
@@ -2441,37 +2441,37 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M14">
-        <v>489.3759598859535</v>
+        <v>479.2305959878227</v>
       </c>
       <c r="N14">
-        <v>5527.642407460987</v>
+        <v>5537.787771359117</v>
       </c>
       <c r="O14">
-        <v>1105.528481492197</v>
+        <v>1107.557554271823</v>
       </c>
       <c r="P14">
-        <v>4422.11392596879</v>
+        <v>4430.230217087294</v>
       </c>
       <c r="Q14">
-        <v>9266.013925968789</v>
+        <v>9274.130217087293</v>
       </c>
       <c r="R14">
         <v>0.1363636363636364</v>
       </c>
       <c r="S14">
-        <v>0.1128469118597981</v>
+        <v>0.1128287715554553</v>
       </c>
       <c r="T14">
         <v>1.036913778259042</v>
       </c>
       <c r="U14">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V14">
         <v>0.2</v>
       </c>
       <c r="W14">
-        <v>0.05402478221340606</v>
+        <v>0.05290478221340607</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>12.29528800055723</v>
+        <v>12.55558058630262</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2490,13 +2490,13 @@
         <v>0.13</v>
       </c>
       <c r="B15">
-        <v>0.105749599857077</v>
+        <v>0.1055880691012795</v>
       </c>
       <c r="C15">
-        <v>52903.55933202469</v>
+        <v>53025.99436453422</v>
       </c>
       <c r="D15">
-        <v>49755.93853891161</v>
+        <v>49878.37357142114</v>
       </c>
       <c r="E15">
         <v>-26116.69161532012</v>
@@ -2523,37 +2523,37 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M15">
-        <v>530.1572898764496</v>
+        <v>519.166478986808</v>
       </c>
       <c r="N15">
-        <v>5486.86107747049</v>
+        <v>5497.851888360132</v>
       </c>
       <c r="O15">
-        <v>1097.372215494098</v>
+        <v>1099.570377672026</v>
       </c>
       <c r="P15">
-        <v>4389.488861976392</v>
+        <v>4398.281510688105</v>
       </c>
       <c r="Q15">
-        <v>9233.388861976393</v>
+        <v>9242.181510688104</v>
       </c>
       <c r="R15">
         <v>0.1494252873563219</v>
       </c>
       <c r="S15">
-        <v>0.1134785955969358</v>
+        <v>0.1134602843833756</v>
       </c>
       <c r="T15">
         <v>1.046683080861821</v>
       </c>
       <c r="U15">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V15">
         <v>0.2</v>
       </c>
       <c r="W15">
-        <v>0.05402478221340606</v>
+        <v>0.05290478221340607</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>11.34949661589898</v>
+        <v>11.58976669504857</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2572,13 +2572,13 @@
         <v>0.14</v>
       </c>
       <c r="B16">
-        <v>0.1057109434119229</v>
+        <v>0.1055382453681497</v>
       </c>
       <c r="C16">
-        <v>52331.7727370027</v>
+        <v>52463.70392023788</v>
       </c>
       <c r="D16">
-        <v>49788.04265211168</v>
+        <v>49919.97383534686</v>
       </c>
       <c r="E16">
         <v>-25512.80090709805</v>
@@ -2605,37 +2605,37 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M16">
-        <v>570.9386198669458</v>
+        <v>559.1023619857932</v>
       </c>
       <c r="N16">
-        <v>5446.079747479995</v>
+        <v>5457.916005361147</v>
       </c>
       <c r="O16">
-        <v>1089.215949495999</v>
+        <v>1091.583201072229</v>
       </c>
       <c r="P16">
-        <v>4356.863797983996</v>
+        <v>4366.332804288917</v>
       </c>
       <c r="Q16">
-        <v>9200.763797983996</v>
+        <v>9210.232804288917</v>
       </c>
       <c r="R16">
         <v>0.1627906976744186</v>
       </c>
       <c r="S16">
-        <v>0.1141249696535419</v>
+        <v>0.1141064835561312</v>
       </c>
       <c r="T16">
         <v>1.056679576548387</v>
       </c>
       <c r="U16">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V16">
         <v>0.2</v>
       </c>
       <c r="W16">
-        <v>0.05402478221340606</v>
+        <v>0.05290478221340607</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>10.53881828619191</v>
+        <v>10.76192621683081</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2654,13 +2654,13 @@
         <v>0.15</v>
       </c>
       <c r="B17">
-        <v>0.1056722869667688</v>
+        <v>0.1054884216350198</v>
       </c>
       <c r="C17">
-        <v>51760.02759791815</v>
+        <v>51901.48292594176</v>
       </c>
       <c r="D17">
-        <v>49820.1882212492</v>
+        <v>49961.64354927282</v>
       </c>
       <c r="E17">
         <v>-24908.91019887598</v>
@@ -2687,37 +2687,37 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M17">
-        <v>611.7199498574417</v>
+        <v>599.0382449847783</v>
       </c>
       <c r="N17">
-        <v>5405.298417489498</v>
+        <v>5417.980122362162</v>
       </c>
       <c r="O17">
-        <v>1081.0596834979</v>
+        <v>1083.596024472432</v>
       </c>
       <c r="P17">
-        <v>4324.238733991599</v>
+        <v>4334.38409788973</v>
       </c>
       <c r="Q17">
-        <v>9168.138733991598</v>
+        <v>9178.284097889729</v>
       </c>
       <c r="R17">
         <v>0.1764705882352941</v>
       </c>
       <c r="S17">
-        <v>0.1147865525114798</v>
+        <v>0.1147678874153046</v>
       </c>
       <c r="T17">
         <v>1.066911283898165</v>
       </c>
       <c r="U17">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V17">
         <v>0.2</v>
       </c>
       <c r="W17">
-        <v>0.05402478221340606</v>
+        <v>0.05290478221340607</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>9.836230400445785</v>
+        <v>10.0444644690421</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2736,13 +2736,13 @@
         <v>0.16</v>
       </c>
       <c r="B18">
-        <v>0.1056336305216147</v>
+        <v>0.1054385979018899</v>
       </c>
       <c r="C18">
-        <v>51188.32399512078</v>
+        <v>51339.33155570722</v>
       </c>
       <c r="D18">
-        <v>49852.3753266739</v>
+        <v>50003.38288726035</v>
       </c>
       <c r="E18">
         <v>-24305.01949065391</v>
@@ -2769,37 +2769,37 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M18">
-        <v>652.501279847938</v>
+        <v>638.9741279837637</v>
       </c>
       <c r="N18">
-        <v>5364.517087499002</v>
+        <v>5378.044239363177</v>
       </c>
       <c r="O18">
-        <v>1072.9034174998</v>
+        <v>1075.608847872635</v>
       </c>
       <c r="P18">
-        <v>4291.613669999201</v>
+        <v>4302.435391490541</v>
       </c>
       <c r="Q18">
-        <v>9135.5136699992</v>
+        <v>9146.335391490542</v>
       </c>
       <c r="R18">
         <v>0.1904761904761905</v>
       </c>
       <c r="S18">
-        <v>0.1154638873422258</v>
+        <v>0.1154450389854106</v>
       </c>
       <c r="T18">
         <v>1.0773866033277</v>
       </c>
       <c r="U18">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V18">
         <v>0.2</v>
       </c>
       <c r="W18">
-        <v>0.05402478221340606</v>
+        <v>0.05290478221340607</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>9.221466000417921</v>
+        <v>9.416685439726963</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2818,13 +2818,13 @@
         <v>0.17</v>
       </c>
       <c r="B19">
-        <v>0.1055949740764606</v>
+        <v>0.10538877416876</v>
       </c>
       <c r="C19">
-        <v>50616.66200916813</v>
+        <v>50777.24998417775</v>
       </c>
       <c r="D19">
-        <v>49884.60404894332</v>
+        <v>50045.19202395294</v>
       </c>
       <c r="E19">
         <v>-23701.12878243184</v>
@@ -2851,37 +2851,37 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M19">
-        <v>693.2826098384342</v>
+        <v>678.9100109827489</v>
       </c>
       <c r="N19">
-        <v>5323.735757508506</v>
+        <v>5338.108356364191</v>
       </c>
       <c r="O19">
-        <v>1064.747151501701</v>
+        <v>1067.621671272838</v>
       </c>
       <c r="P19">
-        <v>4258.988606006805</v>
+        <v>4270.486685091353</v>
       </c>
       <c r="Q19">
-        <v>9102.888606006803</v>
+        <v>9114.386685091353</v>
       </c>
       <c r="R19">
         <v>0.2048192771084338</v>
       </c>
       <c r="S19">
-        <v>0.1161575434941946</v>
+        <v>0.1161385074608205</v>
       </c>
       <c r="T19">
         <v>1.088114340092887</v>
       </c>
       <c r="U19">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V19">
         <v>0.2</v>
       </c>
       <c r="W19">
-        <v>0.05402478221340606</v>
+        <v>0.05290478221340607</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>8.679026823922751</v>
+        <v>8.862762766801847</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2900,13 +2900,13 @@
         <v>0.18</v>
       </c>
       <c r="B20">
-        <v>0.1057147176313065</v>
+        <v>0.1055549504356302</v>
       </c>
       <c r="C20">
-        <v>49913.07359632431</v>
+        <v>50034.18548157191</v>
       </c>
       <c r="D20">
-        <v>49784.90634432156</v>
+        <v>49906.01822956918</v>
       </c>
       <c r="E20">
         <v>-23097.23807420977</v>
@@ -2933,37 +2933,37 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M20">
-        <v>746.0209758517271</v>
+        <v>735.1509431037299</v>
       </c>
       <c r="N20">
-        <v>5270.997391495213</v>
+        <v>5281.86742424321</v>
       </c>
       <c r="O20">
-        <v>1054.199478299043</v>
+        <v>1056.373484848642</v>
       </c>
       <c r="P20">
-        <v>4216.797913196171</v>
+        <v>4225.493939394568</v>
       </c>
       <c r="Q20">
-        <v>9060.697913196171</v>
+        <v>9069.393939394567</v>
       </c>
       <c r="R20">
         <v>0.2195121951219512</v>
       </c>
       <c r="S20">
-        <v>0.1168681180888944</v>
+        <v>0.1168488898014843</v>
       </c>
       <c r="T20">
         <v>1.099103728974298</v>
       </c>
       <c r="U20">
-        <v>0.06863097776675758</v>
+        <v>0.06763097776675758</v>
       </c>
       <c r="V20">
         <v>0.2</v>
       </c>
       <c r="W20">
-        <v>0.05490478221340607</v>
+        <v>0.05410478221340607</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>8.065481483918532</v>
+        <v>8.18473869045685</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2982,13 +2982,13 @@
         <v>0.19</v>
       </c>
       <c r="B21">
-        <v>0.1056848611861524</v>
+        <v>0.1055171267025003</v>
       </c>
       <c r="C21">
-        <v>49334.00385781527</v>
+        <v>49461.90433026128</v>
       </c>
       <c r="D21">
-        <v>49809.7273140346</v>
+        <v>49937.62778648062</v>
       </c>
       <c r="E21">
         <v>-22493.3473659877</v>
@@ -3015,37 +3015,37 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M21">
-        <v>787.4665856212677</v>
+        <v>775.9926621650484</v>
       </c>
       <c r="N21">
-        <v>5229.551781725672</v>
+        <v>5241.025705181892</v>
       </c>
       <c r="O21">
-        <v>1045.910356345134</v>
+        <v>1048.205141036378</v>
       </c>
       <c r="P21">
-        <v>4183.641425380538</v>
+        <v>4192.820564145513</v>
       </c>
       <c r="Q21">
-        <v>9027.541425380537</v>
+        <v>9036.720564145513</v>
       </c>
       <c r="R21">
         <v>0.2345679012345679</v>
       </c>
       <c r="S21">
-        <v>0.1175962377353151</v>
+        <v>0.1175768124468557</v>
       </c>
       <c r="T21">
         <v>1.110364460791052</v>
       </c>
       <c r="U21">
-        <v>0.06863097776675758</v>
+        <v>0.06763097776675758</v>
       </c>
       <c r="V21">
         <v>0.2</v>
       </c>
       <c r="W21">
-        <v>0.05490478221340607</v>
+        <v>0.05410478221340607</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>7.640982458449135</v>
+        <v>7.753962969906487</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3064,13 +3064,13 @@
         <v>0.2</v>
       </c>
       <c r="B22">
-        <v>0.1056550047409983</v>
+        <v>0.1054793029693704</v>
       </c>
       <c r="C22">
-        <v>48754.95888134324</v>
+        <v>48889.66324615603</v>
       </c>
       <c r="D22">
-        <v>49834.57304578465</v>
+        <v>49969.27741059744</v>
       </c>
       <c r="E22">
         <v>-21889.45665776563</v>
@@ -3097,37 +3097,37 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M22">
-        <v>828.9121953908081</v>
+        <v>816.8343812263666</v>
       </c>
       <c r="N22">
-        <v>5188.106171956132</v>
+        <v>5200.183986120574</v>
       </c>
       <c r="O22">
-        <v>1037.621234391226</v>
+        <v>1040.036797224115</v>
       </c>
       <c r="P22">
-        <v>4150.484937564906</v>
+        <v>4160.147188896459</v>
       </c>
       <c r="Q22">
-        <v>8994.384937564904</v>
+        <v>9004.047188896458</v>
       </c>
       <c r="R22">
         <v>0.25</v>
       </c>
       <c r="S22">
-        <v>0.1183425603728963</v>
+        <v>0.1183229331583615</v>
       </c>
       <c r="T22">
         <v>1.121906710903225</v>
       </c>
       <c r="U22">
-        <v>0.06863097776675758</v>
+        <v>0.06763097776675758</v>
       </c>
       <c r="V22">
         <v>0.2</v>
       </c>
       <c r="W22">
-        <v>0.05490478221340607</v>
+        <v>0.05410478221340607</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>7.258933335526678</v>
+        <v>7.366264821411164</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3146,13 +3146,13 @@
         <v>0.21</v>
       </c>
       <c r="B23">
-        <v>0.1056251482958442</v>
+        <v>0.1054414792362405</v>
       </c>
       <c r="C23">
-        <v>48175.93870398156</v>
+        <v>48317.46230548626</v>
       </c>
       <c r="D23">
-        <v>49859.44357664505</v>
+        <v>50000.96717814974</v>
       </c>
       <c r="E23">
         <v>-21285.56594954356</v>
@@ -3179,37 +3179,37 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M23">
-        <v>870.3578051603484</v>
+        <v>857.676100287685</v>
       </c>
       <c r="N23">
-        <v>5146.660562186592</v>
+        <v>5159.342267059255</v>
       </c>
       <c r="O23">
-        <v>1029.332112437319</v>
+        <v>1031.868453411851</v>
       </c>
       <c r="P23">
-        <v>4117.328449749273</v>
+        <v>4127.473813647404</v>
       </c>
       <c r="Q23">
-        <v>8961.228449749273</v>
+        <v>8971.373813647404</v>
       </c>
       <c r="R23">
         <v>0.2658227848101266</v>
       </c>
       <c r="S23">
-        <v>0.119107777254467</v>
+        <v>0.1190879430018041</v>
       </c>
       <c r="T23">
         <v>1.133741169878998</v>
       </c>
       <c r="U23">
-        <v>0.06863097776675758</v>
+        <v>0.06763097776675758</v>
       </c>
       <c r="V23">
         <v>0.2</v>
       </c>
       <c r="W23">
-        <v>0.05490478221340607</v>
+        <v>0.05410478221340607</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>6.913269843358742</v>
+        <v>7.01549030610587</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3228,13 +3228,13 @@
         <v>0.22</v>
       </c>
       <c r="B24">
-        <v>0.1059824918506901</v>
+        <v>0.1054036555031107</v>
       </c>
       <c r="C24">
-        <v>47275.9992569582</v>
+        <v>47745.3015846755</v>
       </c>
       <c r="D24">
-        <v>49563.39483784374</v>
+        <v>50032.69716556105</v>
       </c>
       <c r="E24">
         <v>-20681.67524132149</v>
@@ -3261,45 +3261,45 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M24">
-        <v>941.031725207837</v>
+        <v>898.5178193490034</v>
       </c>
       <c r="N24">
-        <v>5075.986642139103</v>
+        <v>5118.500547997936</v>
       </c>
       <c r="O24">
-        <v>1015.197328427821</v>
+        <v>1023.700109599587</v>
       </c>
       <c r="P24">
-        <v>4060.789313711283</v>
+        <v>4094.800438398349</v>
       </c>
       <c r="Q24">
-        <v>8904.689313711282</v>
+        <v>8938.700438398348</v>
       </c>
       <c r="R24">
         <v>0.282051282051282</v>
       </c>
       <c r="S24">
-        <v>0.1198926150817189</v>
+        <v>0.1198725684822581</v>
       </c>
       <c r="T24">
         <v>1.145879076520816</v>
       </c>
       <c r="U24">
-        <v>0.07083097776675758</v>
+        <v>0.06763097776675758</v>
       </c>
       <c r="V24">
         <v>0.2</v>
       </c>
       <c r="W24">
-        <v>0.05666478221340607</v>
+        <v>0.05410478221340607</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y24">
-        <v>6.394065371194597</v>
+        <v>6.696604383101057</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3310,13 +3310,13 @@
         <v>0.23</v>
       </c>
       <c r="B25">
-        <v>0.105970235405536</v>
+        <v>0.1056786317699808</v>
       </c>
       <c r="C25">
-        <v>46682.20442132806</v>
+        <v>46911.64937587541</v>
       </c>
       <c r="D25">
-        <v>49573.49071043568</v>
+        <v>49802.93566498303</v>
       </c>
       <c r="E25">
         <v>-20077.78453309942</v>
@@ -3343,37 +3343,37 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M25">
-        <v>983.805894535466</v>
+        <v>962.9716651018045</v>
       </c>
       <c r="N25">
-        <v>5033.212472811474</v>
+        <v>5054.046702245136</v>
       </c>
       <c r="O25">
-        <v>1006.642494562295</v>
+        <v>1010.809340449027</v>
       </c>
       <c r="P25">
-        <v>4026.569978249179</v>
+        <v>4043.237361796108</v>
       </c>
       <c r="Q25">
-        <v>8870.469978249179</v>
+        <v>8887.137361796107</v>
       </c>
       <c r="R25">
         <v>0.2987012987012987</v>
       </c>
       <c r="S25">
-        <v>0.1206978383070813</v>
+        <v>0.1206775738453213</v>
       </c>
       <c r="T25">
         <v>1.158332253465018</v>
       </c>
       <c r="U25">
-        <v>0.07083097776675758</v>
+        <v>0.06933097776675758</v>
       </c>
       <c r="V25">
         <v>0.2</v>
       </c>
       <c r="W25">
-        <v>0.05666478221340607</v>
+        <v>0.05546478221340606</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>6.116062528968745</v>
+        <v>6.24838568506668</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3392,13 +3392,13 @@
         <v>0.24</v>
       </c>
       <c r="B26">
-        <v>0.1059579789603819</v>
+        <v>0.1056544080368509</v>
       </c>
       <c r="C26">
-        <v>46088.4136995166</v>
+        <v>46327.91446005364</v>
       </c>
       <c r="D26">
-        <v>49583.5906968463</v>
+        <v>49823.09145738332</v>
       </c>
       <c r="E26">
         <v>-19473.89382487735</v>
@@ -3425,37 +3425,37 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M26">
-        <v>1026.580063863095</v>
+        <v>1004.8399983671</v>
       </c>
       <c r="N26">
-        <v>4990.438303483845</v>
+        <v>5012.178368979839</v>
       </c>
       <c r="O26">
-        <v>998.087660696769</v>
+        <v>1002.435673795968</v>
       </c>
       <c r="P26">
-        <v>3992.350642787076</v>
+        <v>4009.742695183872</v>
       </c>
       <c r="Q26">
-        <v>8836.250642787076</v>
+        <v>8853.642695183871</v>
       </c>
       <c r="R26">
         <v>0.3157894736842105</v>
       </c>
       <c r="S26">
-        <v>0.1215242516173216</v>
+        <v>0.121503763560044</v>
       </c>
       <c r="T26">
         <v>1.171113145591963</v>
       </c>
       <c r="U26">
-        <v>0.07083097776675758</v>
+        <v>0.06933097776675758</v>
       </c>
       <c r="V26">
         <v>0.2</v>
       </c>
       <c r="W26">
-        <v>0.05666478221340607</v>
+        <v>0.05546478221340606</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>5.861226590261714</v>
+        <v>5.988036281522234</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3474,13 +3474,13 @@
         <v>0.25</v>
       </c>
       <c r="B27">
-        <v>0.1059457225152278</v>
+        <v>0.105630184303721</v>
       </c>
       <c r="C27">
-        <v>45494.62709403875</v>
+        <v>45744.19586537618</v>
       </c>
       <c r="D27">
-        <v>49593.6947995905</v>
+        <v>49843.26357092794</v>
       </c>
       <c r="E27">
         <v>-18870.00311665528</v>
@@ -3507,37 +3507,37 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M27">
-        <v>1069.354233190724</v>
+        <v>1046.708331632396</v>
       </c>
       <c r="N27">
-        <v>4947.664134156216</v>
+        <v>4970.310035714544</v>
       </c>
       <c r="O27">
-        <v>989.5328268312433</v>
+        <v>994.0620071429089</v>
       </c>
       <c r="P27">
-        <v>3958.131307324973</v>
+        <v>3976.248028571635</v>
       </c>
       <c r="Q27">
-        <v>8802.031307324973</v>
+        <v>8820.148028571635</v>
       </c>
       <c r="R27">
         <v>0.3333333333333333</v>
       </c>
       <c r="S27">
-        <v>0.122372702615835</v>
+        <v>0.1223519850004927</v>
       </c>
       <c r="T27">
         <v>1.18423486150896</v>
       </c>
       <c r="U27">
-        <v>0.07083097776675758</v>
+        <v>0.06933097776675758</v>
       </c>
       <c r="V27">
         <v>0.2</v>
       </c>
       <c r="W27">
-        <v>0.05666478221340607</v>
+        <v>0.05546478221340606</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3545,7 +3545,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>5.626777526651246</v>
+        <v>5.748514830261345</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3556,13 +3556,13 @@
         <v>0.26</v>
       </c>
       <c r="B28">
-        <v>0.1062454660700737</v>
+        <v>0.1057723605705912</v>
       </c>
       <c r="C28">
-        <v>44644.80577524055</v>
+        <v>45022.14190535418</v>
       </c>
       <c r="D28">
-        <v>49347.76418901438</v>
+        <v>49725.10031912801</v>
       </c>
       <c r="E28">
         <v>-18266.1124084332</v>
@@ -3589,37 +3589,37 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M28">
-        <v>1135.680140139014</v>
+        <v>1101.137591628711</v>
       </c>
       <c r="N28">
-        <v>4881.338227207926</v>
+        <v>4915.880775718229</v>
       </c>
       <c r="O28">
-        <v>976.2676454415853</v>
+        <v>983.1761551436457</v>
       </c>
       <c r="P28">
-        <v>3905.070581766341</v>
+        <v>3932.704620574583</v>
       </c>
       <c r="Q28">
-        <v>8748.970581766342</v>
+        <v>8776.604620574582</v>
       </c>
       <c r="R28">
         <v>0.3513513513513514</v>
       </c>
       <c r="S28">
-        <v>0.1232440847224164</v>
+        <v>0.1232231313447373</v>
       </c>
       <c r="T28">
         <v>1.197711218396686</v>
       </c>
       <c r="U28">
-        <v>0.07233097776675758</v>
+        <v>0.07013097776675759</v>
       </c>
       <c r="V28">
         <v>0.2</v>
       </c>
       <c r="W28">
-        <v>0.05786478221340607</v>
+        <v>0.05610478221340607</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3627,7 +3627,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>5.298162884674925</v>
+        <v>5.464365591630621</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3638,13 +3638,13 @@
         <v>0.27</v>
       </c>
       <c r="B29">
-        <v>0.1062452096249196</v>
+        <v>0.1057545368374613</v>
       </c>
       <c r="C29">
-        <v>44041.12443009407</v>
+        <v>44433.03384686464</v>
       </c>
       <c r="D29">
-        <v>49347.97355208996</v>
+        <v>49739.88296886054</v>
       </c>
       <c r="E29">
         <v>-17662.22170021114</v>
@@ -3671,37 +3671,37 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M29">
-        <v>1179.360145528976</v>
+        <v>1143.489037460585</v>
       </c>
       <c r="N29">
-        <v>4837.658221817965</v>
+        <v>4873.529329886355</v>
       </c>
       <c r="O29">
-        <v>967.5316443635929</v>
+        <v>974.7058659772711</v>
       </c>
       <c r="P29">
-        <v>3870.126577454372</v>
+        <v>3898.823463909084</v>
       </c>
       <c r="Q29">
-        <v>8714.026577454371</v>
+        <v>8742.723463909084</v>
       </c>
       <c r="R29">
         <v>0.3698630136986302</v>
       </c>
       <c r="S29">
-        <v>0.1241393403113698</v>
+        <v>0.1241181447121119</v>
       </c>
       <c r="T29">
         <v>1.211556790541611</v>
       </c>
       <c r="U29">
-        <v>0.07233097776675758</v>
+        <v>0.07013097776675759</v>
       </c>
       <c r="V29">
         <v>0.2</v>
       </c>
       <c r="W29">
-        <v>0.05786478221340607</v>
+        <v>0.05610478221340607</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>5.101934629686965</v>
+        <v>5.261981680829487</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3720,13 +3720,13 @@
         <v>0.28</v>
       </c>
       <c r="B30">
-        <v>0.1062449531797655</v>
+        <v>0.1057367131043314</v>
       </c>
       <c r="C30">
-        <v>43437.44308672409</v>
+        <v>43843.93458038221</v>
       </c>
       <c r="D30">
-        <v>49348.18291694206</v>
+        <v>49754.67441060018</v>
       </c>
       <c r="E30">
         <v>-17058.33099198906</v>
@@ -3753,37 +3753,37 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M30">
-        <v>1223.040150918938</v>
+        <v>1185.840483292458</v>
       </c>
       <c r="N30">
-        <v>4793.978216428002</v>
+        <v>4831.177884054481</v>
       </c>
       <c r="O30">
-        <v>958.7956432856005</v>
+        <v>966.2355768108963</v>
       </c>
       <c r="P30">
-        <v>3835.182573142402</v>
+        <v>3864.942307243585</v>
       </c>
       <c r="Q30">
-        <v>8679.082573142401</v>
+        <v>8708.842307243583</v>
       </c>
       <c r="R30">
         <v>0.388888888888889</v>
       </c>
       <c r="S30">
-        <v>0.1250594641111275</v>
+        <v>0.1250380195619135</v>
       </c>
       <c r="T30">
         <v>1.225786961912783</v>
       </c>
       <c r="U30">
-        <v>0.07233097776675758</v>
+        <v>0.07013097776675759</v>
       </c>
       <c r="V30">
         <v>0.2</v>
       </c>
       <c r="W30">
-        <v>0.05786478221340607</v>
+        <v>0.05610478221340607</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>4.919722678626716</v>
+        <v>5.074053763657004</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3802,13 +3802,13 @@
         <v>0.29</v>
       </c>
       <c r="B31">
-        <v>0.1062446967346114</v>
+        <v>0.1057188893712016</v>
       </c>
       <c r="C31">
-        <v>42833.76174513064</v>
+        <v>43254.8441137528</v>
       </c>
       <c r="D31">
-        <v>49348.39228357068</v>
+        <v>49769.47465219285</v>
       </c>
       <c r="E31">
         <v>-16454.44028376699</v>
@@ -3835,37 +3835,37 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M31">
-        <v>1266.7201563089</v>
+        <v>1228.191929124332</v>
       </c>
       <c r="N31">
-        <v>4750.29821103804</v>
+        <v>4788.826438222608</v>
       </c>
       <c r="O31">
-        <v>950.059642207608</v>
+        <v>957.7652876445217</v>
       </c>
       <c r="P31">
-        <v>3800.238568830432</v>
+        <v>3831.061150578086</v>
       </c>
       <c r="Q31">
-        <v>8644.138568830433</v>
+        <v>8674.961150578085</v>
       </c>
       <c r="R31">
         <v>0.4084507042253521</v>
       </c>
       <c r="S31">
-        <v>0.12600550689116</v>
+        <v>0.1259838063793152</v>
       </c>
       <c r="T31">
         <v>1.240417983181735</v>
       </c>
       <c r="U31">
-        <v>0.07233097776675758</v>
+        <v>0.07013097776675759</v>
       </c>
       <c r="V31">
         <v>0.2</v>
       </c>
       <c r="W31">
-        <v>0.05786478221340607</v>
+        <v>0.05610478221340607</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>4.750077069018898</v>
+        <v>4.899086392496418</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3884,13 +3884,13 @@
         <v>0.3</v>
       </c>
       <c r="B32">
-        <v>0.1062444402894573</v>
+        <v>0.1057010656380717</v>
       </c>
       <c r="C32">
-        <v>42230.08040531371</v>
+        <v>42665.7624548317</v>
       </c>
       <c r="D32">
-        <v>49348.60165197583</v>
+        <v>49784.2837014938</v>
       </c>
       <c r="E32">
         <v>-15850.54957554493</v>
@@ -3917,37 +3917,37 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M32">
-        <v>1310.400161698862</v>
+        <v>1270.543374956205</v>
       </c>
       <c r="N32">
-        <v>4706.618205648078</v>
+        <v>4746.474992390735</v>
       </c>
       <c r="O32">
-        <v>941.3236411296157</v>
+        <v>949.294998478147</v>
       </c>
       <c r="P32">
-        <v>3765.294564518463</v>
+        <v>3797.179993912588</v>
       </c>
       <c r="Q32">
-        <v>8609.194564518462</v>
+        <v>8641.079993912586</v>
       </c>
       <c r="R32">
         <v>0.4285714285714286</v>
       </c>
       <c r="S32">
-        <v>0.1269785794649078</v>
+        <v>0.1269566156772141</v>
       </c>
       <c r="T32">
         <v>1.2554670336298</v>
       </c>
       <c r="U32">
-        <v>0.07233097776675758</v>
+        <v>0.07013097776675759</v>
       </c>
       <c r="V32">
         <v>0.2</v>
       </c>
       <c r="W32">
-        <v>0.05786478221340607</v>
+        <v>0.05610478221340607</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>4.59174116671827</v>
+        <v>4.735783512746539</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3966,13 +3966,13 @@
         <v>0.31</v>
       </c>
       <c r="B33">
-        <v>0.1062441838443032</v>
+        <v>0.1056832419049418</v>
       </c>
       <c r="C33">
-        <v>41626.39906727336</v>
+        <v>42076.68961148353</v>
       </c>
       <c r="D33">
-        <v>49348.81102215755</v>
+        <v>49799.10156636771</v>
       </c>
       <c r="E33">
         <v>-15246.65886732285</v>
@@ -3999,37 +3999,37 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M33">
-        <v>1354.080167088824</v>
+        <v>1312.894820788079</v>
       </c>
       <c r="N33">
-        <v>4662.938200258116</v>
+        <v>4704.123546558862</v>
       </c>
       <c r="O33">
-        <v>932.5876400516232</v>
+        <v>940.8247093117724</v>
       </c>
       <c r="P33">
-        <v>3730.350560206493</v>
+        <v>3763.298837247089</v>
       </c>
       <c r="Q33">
-        <v>8574.250560206492</v>
+        <v>8607.198837247088</v>
       </c>
       <c r="R33">
         <v>0.4492753623188406</v>
       </c>
       <c r="S33">
-        <v>0.1279798570407932</v>
+        <v>0.1279576223460665</v>
       </c>
       <c r="T33">
         <v>1.270952288438678</v>
       </c>
       <c r="U33">
-        <v>0.07233097776675758</v>
+        <v>0.07013097776675759</v>
       </c>
       <c r="V33">
         <v>0.2</v>
       </c>
       <c r="W33">
-        <v>0.05786478221340607</v>
+        <v>0.05610478221340607</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>4.443620483920905</v>
+        <v>4.58301630265794</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4048,13 +4048,13 @@
         <v>0.32</v>
       </c>
       <c r="B34">
-        <v>0.1062439273991491</v>
+        <v>0.1056654181718119</v>
       </c>
       <c r="C34">
-        <v>41022.7177310096</v>
+        <v>41487.62559158223</v>
       </c>
       <c r="D34">
-        <v>49349.02039411585</v>
+        <v>49813.92825468848</v>
       </c>
       <c r="E34">
         <v>-14642.76815910078</v>
@@ -4081,37 +4081,37 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M34">
-        <v>1397.760172478786</v>
+        <v>1355.246266619952</v>
       </c>
       <c r="N34">
-        <v>4619.258194868155</v>
+        <v>4661.772100726987</v>
       </c>
       <c r="O34">
-        <v>923.851638973631</v>
+        <v>932.3544201453975</v>
       </c>
       <c r="P34">
-        <v>3695.406555894524</v>
+        <v>3729.41768058159</v>
       </c>
       <c r="Q34">
-        <v>8539.306555894524</v>
+        <v>8573.317680581589</v>
       </c>
       <c r="R34">
         <v>0.4705882352941177</v>
       </c>
       <c r="S34">
-        <v>0.1290105839571458</v>
+        <v>0.1289880703875323</v>
       </c>
       <c r="T34">
         <v>1.286892991918406</v>
       </c>
       <c r="U34">
-        <v>0.07233097776675758</v>
+        <v>0.07013097776675759</v>
       </c>
       <c r="V34">
         <v>0.2</v>
       </c>
       <c r="W34">
-        <v>0.05786478221340607</v>
+        <v>0.05610478221340607</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>4.304757343798377</v>
+        <v>4.43979704319988</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4130,13 +4130,13 @@
         <v>0.33</v>
       </c>
       <c r="B35">
-        <v>0.106613270953995</v>
+        <v>0.105647594438682</v>
       </c>
       <c r="C35">
-        <v>40119.11049159958</v>
+        <v>40898.5704030112</v>
       </c>
       <c r="D35">
-        <v>49049.3038629279</v>
+        <v>49828.76377433951</v>
       </c>
       <c r="E35">
         <v>-14038.87745087871</v>
@@ -4163,45 +4163,45 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M35">
-        <v>1469.339928588608</v>
+        <v>1397.597712451826</v>
       </c>
       <c r="N35">
-        <v>4547.678438758332</v>
+        <v>4619.420654895114</v>
       </c>
       <c r="O35">
-        <v>909.5356877516665</v>
+        <v>923.8841309790229</v>
       </c>
       <c r="P35">
-        <v>3638.142751006666</v>
+        <v>3695.536523916091</v>
       </c>
       <c r="Q35">
-        <v>8482.042751006666</v>
+        <v>8539.436523916091</v>
       </c>
       <c r="R35">
         <v>0.4925373134328359</v>
       </c>
       <c r="S35">
-        <v>0.1300720788411507</v>
+        <v>0.1300492780720269</v>
       </c>
       <c r="T35">
         <v>1.30330953729305</v>
       </c>
       <c r="U35">
-        <v>0.07373097776675758</v>
+        <v>0.07013097776675759</v>
       </c>
       <c r="V35">
         <v>0.2</v>
       </c>
       <c r="W35">
-        <v>0.05898478221340606</v>
+        <v>0.05610478221340607</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y35">
-        <v>4.095048565873154</v>
+        <v>4.305257738860489</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4212,13 +4212,13 @@
         <v>0.34</v>
       </c>
       <c r="B36">
-        <v>0.1066242145088409</v>
+        <v>0.1059017707055522</v>
       </c>
       <c r="C36">
-        <v>39506.39478249073</v>
+        <v>40083.94897903429</v>
       </c>
       <c r="D36">
-        <v>49040.47886204113</v>
+        <v>49618.03305858468</v>
       </c>
       <c r="E36">
         <v>-13434.98674265664</v>
@@ -4245,37 +4245,37 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M36">
-        <v>1513.865380970081</v>
+        <v>1460.48144236325</v>
       </c>
       <c r="N36">
-        <v>4503.152986376859</v>
+        <v>4556.53692498369</v>
       </c>
       <c r="O36">
-        <v>900.6305972753719</v>
+        <v>911.3073849967382</v>
       </c>
       <c r="P36">
-        <v>3602.522389101488</v>
+        <v>3645.229539986952</v>
       </c>
       <c r="Q36">
-        <v>8446.422389101488</v>
+        <v>8489.129539986952</v>
       </c>
       <c r="R36">
         <v>0.5151515151515152</v>
       </c>
       <c r="S36">
-        <v>0.1311657402367921</v>
+        <v>0.1311426435651426</v>
       </c>
       <c r="T36">
         <v>1.320223553739654</v>
       </c>
       <c r="U36">
-        <v>0.07373097776675758</v>
+        <v>0.07113097776675759</v>
       </c>
       <c r="V36">
         <v>0.2</v>
       </c>
       <c r="W36">
-        <v>0.05898478221340606</v>
+        <v>0.05690478221340607</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>3.974605960994531</v>
+        <v>4.119886903602566</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4294,13 +4294,13 @@
         <v>0.35</v>
       </c>
       <c r="B37">
-        <v>0.1066351580636868</v>
+        <v>0.1058919469724223</v>
       </c>
       <c r="C37">
-        <v>38893.68224841698</v>
+        <v>39488.16974563961</v>
       </c>
       <c r="D37">
-        <v>49031.65703618946</v>
+        <v>49626.14453341207</v>
       </c>
       <c r="E37">
         <v>-12831.09603443457</v>
@@ -4327,37 +4327,37 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M37">
-        <v>1558.390833351554</v>
+        <v>1503.436778903346</v>
       </c>
       <c r="N37">
-        <v>4458.627533995386</v>
+        <v>4513.581588443594</v>
       </c>
       <c r="O37">
-        <v>891.7255067990773</v>
+        <v>902.7163176887188</v>
       </c>
       <c r="P37">
-        <v>3566.902027196309</v>
+        <v>3610.865270754875</v>
       </c>
       <c r="Q37">
-        <v>8410.802027196309</v>
+        <v>8454.765270754875</v>
       </c>
       <c r="R37">
         <v>0.5384615384615385</v>
       </c>
       <c r="S37">
-        <v>0.1322930527522995</v>
+        <v>0.132269651073431</v>
       </c>
       <c r="T37">
         <v>1.337658001461538</v>
       </c>
       <c r="U37">
-        <v>0.07373097776675758</v>
+        <v>0.07113097776675759</v>
       </c>
       <c r="V37">
         <v>0.2</v>
       </c>
       <c r="W37">
-        <v>0.05898478221340606</v>
+        <v>0.05690478221340607</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>3.861045790680402</v>
+        <v>4.002175849213922</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4376,13 +4376,13 @@
         <v>0.36</v>
       </c>
       <c r="B38">
-        <v>0.1066461016185327</v>
+        <v>0.1058821232392924</v>
       </c>
       <c r="C38">
-        <v>38280.97288766523</v>
+        <v>38892.39316477982</v>
       </c>
       <c r="D38">
-        <v>49022.83838365976</v>
+        <v>49634.25866077436</v>
       </c>
       <c r="E38">
         <v>-12227.2053262125</v>
@@ -4409,37 +4409,37 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M38">
-        <v>1602.916285733026</v>
+        <v>1546.392115443441</v>
       </c>
       <c r="N38">
-        <v>4414.102081613913</v>
+        <v>4470.626251903499</v>
       </c>
       <c r="O38">
-        <v>882.8204163227828</v>
+        <v>894.1252503806999</v>
       </c>
       <c r="P38">
-        <v>3531.281665291131</v>
+        <v>3576.501001522799</v>
       </c>
       <c r="Q38">
-        <v>8375.181665291129</v>
+        <v>8420.401001522798</v>
       </c>
       <c r="R38">
         <v>0.5625</v>
       </c>
       <c r="S38">
-        <v>0.1334555937839164</v>
+        <v>0.1334318775663535</v>
       </c>
       <c r="T38">
         <v>1.355637275674731</v>
       </c>
       <c r="U38">
-        <v>0.07373097776675758</v>
+        <v>0.07113097776675759</v>
       </c>
       <c r="V38">
         <v>0.2</v>
       </c>
       <c r="W38">
-        <v>0.05898478221340606</v>
+        <v>0.05690478221340607</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>3.753794518717058</v>
+        <v>3.891004297846869</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4458,13 +4458,13 @@
         <v>0.37</v>
       </c>
       <c r="B39">
-        <v>0.1066570451733786</v>
+        <v>0.1058722995061625</v>
       </c>
       <c r="C39">
-        <v>37668.26669852347</v>
+        <v>38296.61923775627</v>
       </c>
       <c r="D39">
-        <v>49014.02290274007</v>
+        <v>49642.37544197287</v>
       </c>
       <c r="E39">
         <v>-11623.31461799043</v>
@@ -4491,37 +4491,37 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M39">
-        <v>1647.441738114499</v>
+        <v>1589.347451983537</v>
       </c>
       <c r="N39">
-        <v>4369.576629232441</v>
+        <v>4427.670915363404</v>
       </c>
       <c r="O39">
-        <v>873.9153258464881</v>
+        <v>885.5341830726808</v>
       </c>
       <c r="P39">
-        <v>3495.661303385953</v>
+        <v>3542.136732290723</v>
       </c>
       <c r="Q39">
-        <v>8339.561303385952</v>
+        <v>8386.036732290722</v>
       </c>
       <c r="R39">
         <v>0.5873015873015873</v>
       </c>
       <c r="S39">
-        <v>0.1346550408800291</v>
+        <v>0.1346310001384164</v>
       </c>
       <c r="T39">
         <v>1.374187320497866</v>
       </c>
       <c r="U39">
-        <v>0.07373097776675758</v>
+        <v>0.07113097776675759</v>
       </c>
       <c r="V39">
         <v>0.2</v>
       </c>
       <c r="W39">
-        <v>0.05898478221340606</v>
+        <v>0.05690478221340607</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>3.652340612805786</v>
+        <v>3.785842019526684</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4540,13 +4540,13 @@
         <v>0.38</v>
       </c>
       <c r="B40">
-        <v>0.1066679887282245</v>
+        <v>0.1058624757730327</v>
       </c>
       <c r="C40">
-        <v>37055.5636792811</v>
+        <v>37700.84796587109</v>
       </c>
       <c r="D40">
-        <v>49005.21059171978</v>
+        <v>49650.49487830976</v>
       </c>
       <c r="E40">
         <v>-11019.42390976836</v>
@@ -4573,37 +4573,37 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M40">
-        <v>1691.967190495973</v>
+        <v>1632.302788523632</v>
       </c>
       <c r="N40">
-        <v>4325.051176850968</v>
+        <v>4384.715578823308</v>
       </c>
       <c r="O40">
-        <v>865.0102353701936</v>
+        <v>876.9431157646616</v>
       </c>
       <c r="P40">
-        <v>3460.040941480774</v>
+        <v>3507.772463058646</v>
       </c>
       <c r="Q40">
-        <v>8303.940941480774</v>
+        <v>8351.672463058647</v>
       </c>
       <c r="R40">
         <v>0.6129032258064516</v>
       </c>
       <c r="S40">
-        <v>0.1358931798179519</v>
+        <v>0.1358688040837716</v>
       </c>
       <c r="T40">
         <v>1.393335753863683</v>
       </c>
       <c r="U40">
-        <v>0.07373097776675758</v>
+        <v>0.07113097776675759</v>
       </c>
       <c r="V40">
         <v>0.2</v>
       </c>
       <c r="W40">
-        <v>0.05898478221340606</v>
+        <v>0.05690478221340607</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>3.556226386153002</v>
+        <v>3.686214597960191</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4622,13 +4622,13 @@
         <v>0.39</v>
       </c>
       <c r="B41">
-        <v>0.1066789322830704</v>
+        <v>0.1058526520399028</v>
       </c>
       <c r="C41">
-        <v>36442.8638282286</v>
+        <v>37105.07935042732</v>
       </c>
       <c r="D41">
-        <v>48996.40144888934</v>
+        <v>49658.61697108806</v>
       </c>
       <c r="E41">
         <v>-10415.53320154629</v>
@@ -4655,37 +4655,37 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M41">
-        <v>1736.492642877446</v>
+        <v>1675.258125063728</v>
       </c>
       <c r="N41">
-        <v>4280.525724469495</v>
+        <v>4341.760242283212</v>
       </c>
       <c r="O41">
-        <v>856.105144893899</v>
+        <v>868.3520484566425</v>
       </c>
       <c r="P41">
-        <v>3424.420579575596</v>
+        <v>3473.40819382657</v>
       </c>
       <c r="Q41">
-        <v>8268.320579575597</v>
+        <v>8317.30819382657</v>
       </c>
       <c r="R41">
         <v>0.639344262295082</v>
       </c>
       <c r="S41">
-        <v>0.1371719134751508</v>
+        <v>0.13714719176504</v>
       </c>
       <c r="T41">
         <v>1.413112004716904</v>
       </c>
       <c r="U41">
-        <v>0.07373097776675758</v>
+        <v>0.07113097776675759</v>
       </c>
       <c r="V41">
         <v>0.2</v>
       </c>
       <c r="W41">
-        <v>0.05898478221340606</v>
+        <v>0.05690478221340607</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>3.465041094200361</v>
+        <v>3.591696274935571</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4704,13 +4704,13 @@
         <v>0.4</v>
       </c>
       <c r="B42">
-        <v>0.1066898758379163</v>
+        <v>0.1058428283067729</v>
       </c>
       <c r="C42">
-        <v>35830.16714365776</v>
+        <v>36509.31339272881</v>
       </c>
       <c r="D42">
-        <v>48987.59547254058</v>
+        <v>49666.74172161163</v>
       </c>
       <c r="E42">
         <v>-9811.64249332422</v>
@@ -4737,37 +4737,37 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M42">
-        <v>1781.018095258918</v>
+        <v>1718.213461603823</v>
       </c>
       <c r="N42">
-        <v>4236.000272088022</v>
+        <v>4298.804905743116</v>
       </c>
       <c r="O42">
-        <v>847.2000544176044</v>
+        <v>859.7609811486233</v>
       </c>
       <c r="P42">
-        <v>3388.800217670418</v>
+        <v>3439.043924594493</v>
       </c>
       <c r="Q42">
-        <v>8232.700217670417</v>
+        <v>8282.943924594492</v>
       </c>
       <c r="R42">
         <v>0.6666666666666667</v>
       </c>
       <c r="S42">
-        <v>0.1384932715875898</v>
+        <v>0.1384681923690175</v>
       </c>
       <c r="T42">
         <v>1.433547463931899</v>
       </c>
       <c r="U42">
-        <v>0.07373097776675758</v>
+        <v>0.07113097776675759</v>
       </c>
       <c r="V42">
         <v>0.2</v>
       </c>
       <c r="W42">
-        <v>0.05898478221340606</v>
+        <v>0.05690478221340607</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4775,7 +4775,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>3.378415066845352</v>
+        <v>3.501903868062182</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4786,13 +4786,13 @@
         <v>0.41</v>
       </c>
       <c r="B43">
-        <v>0.1067008193927622</v>
+        <v>0.105833004573643</v>
       </c>
       <c r="C43">
-        <v>35217.4736238616</v>
+        <v>35913.55009408034</v>
       </c>
       <c r="D43">
-        <v>48978.79266096649</v>
+        <v>49674.86913118523</v>
       </c>
       <c r="E43">
         <v>-9207.751785102148</v>
@@ -4819,37 +4819,37 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M43">
-        <v>1825.543547640392</v>
+        <v>1761.168798143919</v>
       </c>
       <c r="N43">
-        <v>4191.474819706548</v>
+        <v>4255.849569203021</v>
       </c>
       <c r="O43">
-        <v>838.2949639413097</v>
+        <v>851.1699138406043</v>
       </c>
       <c r="P43">
-        <v>3353.179855765239</v>
+        <v>3404.679655362417</v>
       </c>
       <c r="Q43">
-        <v>8197.079855765238</v>
+        <v>8248.579655362417</v>
       </c>
       <c r="R43">
         <v>0.6949152542372882</v>
       </c>
       <c r="S43">
-        <v>0.1398594215004503</v>
+        <v>0.1398339726544857</v>
       </c>
       <c r="T43">
         <v>1.454675650577911</v>
       </c>
       <c r="U43">
-        <v>0.07373097776675758</v>
+        <v>0.07113097776675759</v>
       </c>
       <c r="V43">
         <v>0.2</v>
       </c>
       <c r="W43">
-        <v>0.05898478221340606</v>
+        <v>0.05690478221340607</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4857,7 +4857,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>3.296014699361318</v>
+        <v>3.41649157859725</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4868,13 +4868,13 @@
         <v>0.42</v>
       </c>
       <c r="B44">
-        <v>0.1067117629476081</v>
+        <v>0.1058231808405132</v>
       </c>
       <c r="C44">
-        <v>34604.78326713431</v>
+        <v>35317.78945578746</v>
       </c>
       <c r="D44">
-        <v>48969.99301246127</v>
+        <v>49682.99920111442</v>
       </c>
       <c r="E44">
         <v>-8603.861076880079</v>
@@ -4901,37 +4901,37 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M44">
-        <v>1870.069000021864</v>
+        <v>1804.124134684015</v>
       </c>
       <c r="N44">
-        <v>4146.949367325076</v>
+        <v>4212.894232662926</v>
       </c>
       <c r="O44">
-        <v>829.3898734650153</v>
+        <v>842.5788465325852</v>
       </c>
       <c r="P44">
-        <v>3317.559493860061</v>
+        <v>3370.315386130341</v>
       </c>
       <c r="Q44">
-        <v>8161.45949386006</v>
+        <v>8214.215386130341</v>
       </c>
       <c r="R44">
         <v>0.7241379310344827</v>
       </c>
       <c r="S44">
-        <v>0.1412726800309957</v>
+        <v>0.1412468488118666</v>
       </c>
       <c r="T44">
         <v>1.47653239538413</v>
       </c>
       <c r="U44">
-        <v>0.07373097776675758</v>
+        <v>0.07113097776675759</v>
       </c>
       <c r="V44">
         <v>0.2</v>
       </c>
       <c r="W44">
-        <v>0.05898478221340606</v>
+        <v>0.05690478221340607</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>3.217538158900335</v>
+        <v>3.335146541011602</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4950,13 +4950,13 @@
         <v>0.43</v>
       </c>
       <c r="B45">
-        <v>0.106722706502454</v>
+        <v>0.1058133571073833</v>
       </c>
       <c r="C45">
-        <v>33992.09607177138</v>
+        <v>34722.03147915663</v>
       </c>
       <c r="D45">
-        <v>48961.19652532041</v>
+        <v>49691.13193270566</v>
       </c>
       <c r="E45">
         <v>-7999.970368658011</v>
@@ -4983,37 +4983,37 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M45">
-        <v>1914.594452403337</v>
+        <v>1847.07947122411</v>
       </c>
       <c r="N45">
-        <v>4102.423914943603</v>
+        <v>4169.938896122831</v>
       </c>
       <c r="O45">
-        <v>820.4847829887208</v>
+        <v>833.9877792245661</v>
       </c>
       <c r="P45">
-        <v>3281.939131954883</v>
+        <v>3335.951116898264</v>
       </c>
       <c r="Q45">
-        <v>8125.839131954883</v>
+        <v>8179.851116898264</v>
       </c>
       <c r="R45">
         <v>0.7543859649122806</v>
       </c>
       <c r="S45">
-        <v>0.1427355265801568</v>
+        <v>0.1427092995712609</v>
       </c>
       <c r="T45">
         <v>1.499156043516883</v>
       </c>
       <c r="U45">
-        <v>0.07373097776675758</v>
+        <v>0.07113097776675759</v>
       </c>
       <c r="V45">
         <v>0.2</v>
       </c>
       <c r="W45">
-        <v>0.05898478221340606</v>
+        <v>0.05690478221340607</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>3.1427116900887</v>
+        <v>3.257584993546216</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5032,13 +5032,13 @@
         <v>0.44</v>
       </c>
       <c r="B46">
-        <v>0.1067336500572999</v>
+        <v>0.1058035333742534</v>
       </c>
       <c r="C46">
-        <v>33379.41203606948</v>
+        <v>34126.27616549515</v>
       </c>
       <c r="D46">
-        <v>48952.40319784058</v>
+        <v>49699.26732726624</v>
       </c>
       <c r="E46">
         <v>-7396.079660435938</v>
@@ -5065,37 +5065,37 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M46">
-        <v>1959.11990478481</v>
+        <v>1890.034807764206</v>
       </c>
       <c r="N46">
-        <v>4057.89846256213</v>
+        <v>4126.983559582734</v>
       </c>
       <c r="O46">
-        <v>811.5796925124259</v>
+        <v>825.3967119165469</v>
       </c>
       <c r="P46">
-        <v>3246.318770049704</v>
+        <v>3301.586847666188</v>
       </c>
       <c r="Q46">
-        <v>8090.218770049703</v>
+        <v>8145.486847666187</v>
       </c>
       <c r="R46">
         <v>0.7857142857142857</v>
       </c>
       <c r="S46">
-        <v>0.1442506176489307</v>
+        <v>0.1442239807149192</v>
       </c>
       <c r="T46">
         <v>1.522587679082949</v>
       </c>
       <c r="U46">
-        <v>0.07373097776675758</v>
+        <v>0.07113097776675759</v>
       </c>
       <c r="V46">
         <v>0.2</v>
       </c>
       <c r="W46">
-        <v>0.05898478221340606</v>
+        <v>0.05690478221340607</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>3.071286424404865</v>
+        <v>3.18354897096562</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5114,13 +5114,13 @@
         <v>0.45</v>
       </c>
       <c r="B47">
-        <v>0.1067445936121458</v>
+        <v>0.1057937096411235</v>
       </c>
       <c r="C47">
-        <v>32766.7311583265</v>
+        <v>33530.52351611115</v>
       </c>
       <c r="D47">
-        <v>48943.61302831966</v>
+        <v>49707.40538610431</v>
       </c>
       <c r="E47">
         <v>-6792.188952213866</v>
@@ -5147,37 +5147,37 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M47">
-        <v>2003.645357166283</v>
+        <v>1932.990144304301</v>
       </c>
       <c r="N47">
-        <v>4013.373010180657</v>
+        <v>4084.028223042639</v>
       </c>
       <c r="O47">
-        <v>802.6746020361314</v>
+        <v>816.8056446085278</v>
       </c>
       <c r="P47">
-        <v>3210.698408144525</v>
+        <v>3267.222578434111</v>
       </c>
       <c r="Q47">
-        <v>8054.598408144525</v>
+        <v>8111.12257843411</v>
       </c>
       <c r="R47">
         <v>0.8181818181818181</v>
       </c>
       <c r="S47">
-        <v>0.1458208029383874</v>
+        <v>0.1457937411728924</v>
       </c>
       <c r="T47">
         <v>1.546871374124144</v>
       </c>
       <c r="U47">
-        <v>0.07373097776675758</v>
+        <v>0.07113097776675759</v>
       </c>
       <c r="V47">
         <v>0.2</v>
       </c>
       <c r="W47">
-        <v>0.05898478221340606</v>
+        <v>0.05690478221340607</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>3.003035614973646</v>
+        <v>3.112803438277495</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5196,13 +5196,13 @@
         <v>0.46</v>
       </c>
       <c r="B48">
-        <v>0.1077123371669917</v>
+        <v>0.1057838859079937</v>
       </c>
       <c r="C48">
-        <v>31397.80930726009</v>
+        <v>32934.77353231363</v>
       </c>
       <c r="D48">
-        <v>48178.58188547532</v>
+        <v>49715.54611052887</v>
       </c>
       <c r="E48">
         <v>-6188.298243991798</v>
@@ -5229,45 +5229,45 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M48">
-        <v>2120.396138251116</v>
+        <v>1975.945480844397</v>
       </c>
       <c r="N48">
-        <v>3896.622229095824</v>
+        <v>4041.072886502543</v>
       </c>
       <c r="O48">
-        <v>779.3244458191649</v>
+        <v>808.2145773005086</v>
       </c>
       <c r="P48">
-        <v>3117.29778327666</v>
+        <v>3232.858309202034</v>
       </c>
       <c r="Q48">
-        <v>7961.197783276659</v>
+        <v>8076.758309202034</v>
       </c>
       <c r="R48">
         <v>0.8518518518518519</v>
       </c>
       <c r="S48">
-        <v>0.1474491432385646</v>
+        <v>0.1474216409070868</v>
       </c>
       <c r="T48">
         <v>1.572054465277976</v>
       </c>
       <c r="U48">
-        <v>0.07633097776675757</v>
+        <v>0.07113097776675759</v>
       </c>
       <c r="V48">
         <v>0.2</v>
       </c>
       <c r="W48">
-        <v>0.06106478221340605</v>
+        <v>0.05690478221340607</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y48">
-        <v>2.837685967637031</v>
+        <v>3.045133798314941</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5278,13 +5278,13 @@
         <v>0.47</v>
       </c>
       <c r="B49">
-        <v>0.1077440807218376</v>
+        <v>0.1067140621748638</v>
       </c>
       <c r="C49">
-        <v>30769.22924311153</v>
+        <v>31571.71130547326</v>
       </c>
       <c r="D49">
-        <v>48153.89252954884</v>
+        <v>48956.37459191057</v>
       </c>
       <c r="E49">
         <v>-5584.407535769726</v>
@@ -5311,37 +5311,37 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M49">
-        <v>2166.491706473966</v>
+        <v>2089.857975600586</v>
       </c>
       <c r="N49">
-        <v>3850.526660872974</v>
+        <v>3927.160391746354</v>
       </c>
       <c r="O49">
-        <v>770.1053321745949</v>
+        <v>785.4320783492709</v>
       </c>
       <c r="P49">
-        <v>3080.421328698379</v>
+        <v>3141.728313397084</v>
       </c>
       <c r="Q49">
-        <v>7924.321328698379</v>
+        <v>7985.628313397083</v>
       </c>
       <c r="R49">
         <v>0.8867924528301887</v>
       </c>
       <c r="S49">
-        <v>0.1491389303425222</v>
+        <v>0.1491109708199301</v>
       </c>
       <c r="T49">
         <v>1.598187861758368</v>
       </c>
       <c r="U49">
-        <v>0.07633097776675757</v>
+        <v>0.07363097776675757</v>
       </c>
       <c r="V49">
         <v>0.2</v>
       </c>
       <c r="W49">
-        <v>0.06106478221340605</v>
+        <v>0.05890478221340606</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>2.777309670453264</v>
+        <v>2.879151807250329</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5360,13 +5360,13 @@
         <v>0.48</v>
       </c>
       <c r="B50">
-        <v>0.1077758242766835</v>
+        <v>0.1067242384417339</v>
       </c>
       <c r="C50">
-        <v>30140.67447037084</v>
+        <v>30959.64334061929</v>
       </c>
       <c r="D50">
-        <v>48129.22846503022</v>
+        <v>48948.19733527867</v>
       </c>
       <c r="E50">
         <v>-4980.516827547657</v>
@@ -5393,37 +5393,37 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M50">
-        <v>2212.587274696816</v>
+        <v>2134.323038911236</v>
       </c>
       <c r="N50">
-        <v>3804.431092650124</v>
+        <v>3882.695328435704</v>
       </c>
       <c r="O50">
-        <v>760.8862185300248</v>
+        <v>776.5390656871409</v>
       </c>
       <c r="P50">
-        <v>3043.544874120099</v>
+        <v>3106.156262748563</v>
       </c>
       <c r="Q50">
-        <v>7887.444874120099</v>
+        <v>7950.056262748563</v>
       </c>
       <c r="R50">
         <v>0.923076923076923</v>
       </c>
       <c r="S50">
-        <v>0.1508937092581703</v>
+        <v>0.1508652749601904</v>
       </c>
       <c r="T50">
         <v>1.625326388872621</v>
       </c>
       <c r="U50">
-        <v>0.07633097776675757</v>
+        <v>0.07363097776675757</v>
       </c>
       <c r="V50">
         <v>0.2</v>
       </c>
       <c r="W50">
-        <v>0.06106478221340605</v>
+        <v>0.05890478221340606</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5431,7 +5431,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>2.719449052318821</v>
+        <v>2.819169477932614</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5442,13 +5442,13 @@
         <v>0.49</v>
       </c>
       <c r="B51">
-        <v>0.1078075678315294</v>
+        <v>0.106734414708604</v>
       </c>
       <c r="C51">
-        <v>29512.14495019568</v>
+        <v>30347.578107028</v>
       </c>
       <c r="D51">
-        <v>48104.58965307712</v>
+        <v>48940.02280990945</v>
       </c>
       <c r="E51">
         <v>-4376.626119325589</v>
@@ -5475,37 +5475,37 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M51">
-        <v>2258.682842919666</v>
+        <v>2178.788102221887</v>
       </c>
       <c r="N51">
-        <v>3758.335524427274</v>
+        <v>3838.230265125053</v>
       </c>
       <c r="O51">
-        <v>751.6671048854548</v>
+        <v>767.6460530250107</v>
       </c>
       <c r="P51">
-        <v>3006.668419541819</v>
+        <v>3070.584212100043</v>
       </c>
       <c r="Q51">
-        <v>7850.568419541819</v>
+        <v>7914.484212100042</v>
       </c>
       <c r="R51">
         <v>0.9607843137254901</v>
       </c>
       <c r="S51">
-        <v>0.1527173030332557</v>
+        <v>0.1526883753412452</v>
       </c>
       <c r="T51">
         <v>1.653529171952139</v>
       </c>
       <c r="U51">
-        <v>0.07633097776675757</v>
+        <v>0.07363097776675757</v>
       </c>
       <c r="V51">
         <v>0.2</v>
       </c>
       <c r="W51">
-        <v>0.06106478221340605</v>
+        <v>0.05890478221340606</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>2.663950092067417</v>
+        <v>2.761635406954398</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5524,13 +5524,13 @@
         <v>0.5</v>
       </c>
       <c r="B52">
-        <v>0.1078393113863753</v>
+        <v>0.1067445909754742</v>
       </c>
       <c r="C52">
-        <v>28883.6406438232</v>
+        <v>29735.51560333117</v>
       </c>
       <c r="D52">
-        <v>48079.97605492672</v>
+        <v>48931.85101443469</v>
       </c>
       <c r="E52">
         <v>-3772.735411103517</v>
@@ -5557,37 +5557,37 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M52">
-        <v>2304.778411142517</v>
+        <v>2223.253165532537</v>
       </c>
       <c r="N52">
-        <v>3712.239956204423</v>
+        <v>3793.765201814403</v>
       </c>
       <c r="O52">
-        <v>742.4479912408847</v>
+        <v>758.7530403628806</v>
       </c>
       <c r="P52">
-        <v>2969.791964963539</v>
+        <v>3035.012161451522</v>
       </c>
       <c r="Q52">
-        <v>7813.691964963538</v>
+        <v>7878.912161451522</v>
       </c>
       <c r="R52">
         <v>1</v>
       </c>
       <c r="S52">
-        <v>0.1546138405593445</v>
+        <v>0.1545843997375423</v>
       </c>
       <c r="T52">
         <v>1.682860066354838</v>
       </c>
       <c r="U52">
-        <v>0.07633097776675757</v>
+        <v>0.07363097776675757</v>
       </c>
       <c r="V52">
         <v>0.2</v>
       </c>
       <c r="W52">
-        <v>0.06106478221340605</v>
+        <v>0.05890478221340606</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>2.610671090226068</v>
+        <v>2.70640269881531</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5606,13 +5606,13 @@
         <v>0.51</v>
       </c>
       <c r="B53">
-        <v>0.1078710549412212</v>
+        <v>0.1067547672423443</v>
       </c>
       <c r="C53">
-        <v>28255.16151256989</v>
+        <v>29123.45582816158</v>
       </c>
       <c r="D53">
-        <v>48055.38763189548</v>
+        <v>48923.68194748717</v>
       </c>
       <c r="E53">
         <v>-3168.844702881444</v>
@@ -5639,37 +5639,37 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M53">
-        <v>2350.873979365367</v>
+        <v>2267.718228843188</v>
       </c>
       <c r="N53">
-        <v>3666.144387981573</v>
+        <v>3749.300138503752</v>
       </c>
       <c r="O53">
-        <v>733.2288775963146</v>
+        <v>749.8600277007504</v>
       </c>
       <c r="P53">
-        <v>2932.915510385258</v>
+        <v>2999.440110803002</v>
       </c>
       <c r="Q53">
-        <v>7776.815510385258</v>
+        <v>7843.340110803001</v>
       </c>
       <c r="R53">
         <v>1.040816326530612</v>
       </c>
       <c r="S53">
-        <v>0.1565877877803757</v>
+        <v>0.1565578128847086</v>
       </c>
       <c r="T53">
         <v>1.713388140120912</v>
       </c>
       <c r="U53">
-        <v>0.07633097776675757</v>
+        <v>0.07363097776675757</v>
       </c>
       <c r="V53">
         <v>0.2</v>
       </c>
       <c r="W53">
-        <v>0.06106478221340605</v>
+        <v>0.05890478221340606</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5677,7 +5677,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>2.559481461005949</v>
+        <v>2.653335979230696</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5688,13 +5688,13 @@
         <v>0.52</v>
       </c>
       <c r="B54">
-        <v>0.1079027984960671</v>
+        <v>0.1067649435092144</v>
       </c>
       <c r="C54">
-        <v>27626.70751783136</v>
+        <v>28511.39878015293</v>
       </c>
       <c r="D54">
-        <v>48030.82434537901</v>
+        <v>48915.51560770059</v>
       </c>
       <c r="E54">
         <v>-2564.953994659376</v>
@@ -5721,37 +5721,37 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M54">
-        <v>2396.969547588218</v>
+        <v>2312.183292153839</v>
       </c>
       <c r="N54">
-        <v>3620.048819758722</v>
+        <v>3704.835075193101</v>
       </c>
       <c r="O54">
-        <v>724.0097639517445</v>
+        <v>740.9670150386203</v>
       </c>
       <c r="P54">
-        <v>2896.039055806978</v>
+        <v>2963.868060154481</v>
       </c>
       <c r="Q54">
-        <v>7739.939055806977</v>
+        <v>7807.768060154481</v>
       </c>
       <c r="R54">
         <v>1.083333333333333</v>
       </c>
       <c r="S54">
-        <v>0.1586439828022832</v>
+        <v>0.1586134515796735</v>
       </c>
       <c r="T54">
         <v>1.745188216960573</v>
       </c>
       <c r="U54">
-        <v>0.07633097776675757</v>
+        <v>0.07363097776675757</v>
       </c>
       <c r="V54">
         <v>0.2</v>
       </c>
       <c r="W54">
-        <v>0.06106478221340605</v>
+        <v>0.05890478221340606</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>2.510260663678912</v>
+        <v>2.602310287322413</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5770,13 +5770,13 @@
         <v>0.53</v>
       </c>
       <c r="B55">
-        <v>0.109079342050913</v>
+        <v>0.1067751197760845</v>
       </c>
       <c r="C55">
-        <v>26129.78671501657</v>
+        <v>27899.34445793975</v>
       </c>
       <c r="D55">
-        <v>47137.7942507863</v>
+        <v>48907.35199370948</v>
       </c>
       <c r="E55">
         <v>-1961.063286437304</v>
@@ -5803,45 +5803,45 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M55">
-        <v>2529.481876157647</v>
+        <v>2356.64835546449</v>
       </c>
       <c r="N55">
-        <v>3487.536491189293</v>
+        <v>3660.37001188245</v>
       </c>
       <c r="O55">
-        <v>697.5072982378588</v>
+        <v>732.0740023764902</v>
       </c>
       <c r="P55">
-        <v>2790.029192951435</v>
+        <v>2928.29600950596</v>
       </c>
       <c r="Q55">
-        <v>7633.929192951435</v>
+        <v>7772.19600950596</v>
       </c>
       <c r="R55">
         <v>1.127659574468085</v>
       </c>
       <c r="S55">
-        <v>0.1607876754846974</v>
+        <v>0.1607565642616582</v>
       </c>
       <c r="T55">
         <v>1.778341488559368</v>
       </c>
       <c r="U55">
-        <v>0.07903097776675758</v>
+        <v>0.07363097776675757</v>
       </c>
       <c r="V55">
         <v>0.2</v>
       </c>
       <c r="W55">
-        <v>0.06322478221340606</v>
+        <v>0.05890478221340606</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y55">
-        <v>2.378755279514775</v>
+        <v>2.55321009322199</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5852,13 +5852,13 @@
         <v>0.54</v>
       </c>
       <c r="B56">
-        <v>0.1091326856057589</v>
+        <v>0.1067852960429547</v>
       </c>
       <c r="C56">
-        <v>25486.19300843146</v>
+        <v>27287.29286015754</v>
       </c>
       <c r="D56">
-        <v>47098.09125242326</v>
+        <v>48899.19110414934</v>
       </c>
       <c r="E56">
         <v>-1357.172578215232</v>
@@ -5885,45 +5885,45 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M56">
-        <v>2577.207949292696</v>
+        <v>2401.113418775141</v>
       </c>
       <c r="N56">
-        <v>3439.810418054244</v>
+        <v>3615.904948571799</v>
       </c>
       <c r="O56">
-        <v>687.9620836108488</v>
+        <v>723.1809897143598</v>
       </c>
       <c r="P56">
-        <v>2751.848334443395</v>
+        <v>2892.723958857439</v>
       </c>
       <c r="Q56">
-        <v>7595.748334443395</v>
+        <v>7736.623958857439</v>
       </c>
       <c r="R56">
         <v>1.173913043478261</v>
       </c>
       <c r="S56">
-        <v>0.1630245721967818</v>
+        <v>0.162992855755903</v>
       </c>
       <c r="T56">
         <v>1.812936206749415</v>
       </c>
       <c r="U56">
-        <v>0.07903097776675758</v>
+        <v>0.07363097776675757</v>
       </c>
       <c r="V56">
         <v>0.2</v>
       </c>
       <c r="W56">
-        <v>0.06322478221340606</v>
+        <v>0.05890478221340606</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y56">
-        <v>2.334704255820057</v>
+        <v>2.50592842482899</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5934,13 +5934,13 @@
         <v>0.55</v>
       </c>
       <c r="B57">
-        <v>0.1091860291606048</v>
+        <v>0.1083354723098248</v>
       </c>
       <c r="C57">
-        <v>24842.66612726828</v>
+        <v>25471.25226773462</v>
       </c>
       <c r="D57">
-        <v>47058.45507948215</v>
+        <v>47687.04121994849</v>
       </c>
       <c r="E57">
         <v>-753.2818699931595</v>
@@ -5967,37 +5967,37 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M57">
-        <v>2624.934022427747</v>
+        <v>2561.82744341854</v>
       </c>
       <c r="N57">
-        <v>3392.084344919193</v>
+        <v>3455.1909239284</v>
       </c>
       <c r="O57">
-        <v>678.4168689838388</v>
+        <v>691.03818478568</v>
       </c>
       <c r="P57">
-        <v>2713.667475935355</v>
+        <v>2764.15273914272</v>
       </c>
       <c r="Q57">
-        <v>7557.567475935354</v>
+        <v>7608.052739142719</v>
       </c>
       <c r="R57">
         <v>1.222222222222223</v>
       </c>
       <c r="S57">
-        <v>0.1653608865405143</v>
+        <v>0.1653285379832255</v>
       </c>
       <c r="T57">
         <v>1.849068467970131</v>
       </c>
       <c r="U57">
-        <v>0.07903097776675758</v>
+        <v>0.07713097776675758</v>
       </c>
       <c r="V57">
         <v>0.2</v>
       </c>
       <c r="W57">
-        <v>0.06322478221340606</v>
+        <v>0.06170478221340606</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>2.292255087532419</v>
+        <v>2.34872117667603</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6016,13 +6016,13 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1092393727154507</v>
+        <v>0.1083736485766949</v>
       </c>
       <c r="C58">
-        <v>24199.20590295475</v>
+        <v>24838.26763174474</v>
       </c>
       <c r="D58">
-        <v>47018.88556339069</v>
+        <v>47657.94729218069</v>
       </c>
       <c r="E58">
         <v>-149.391161771091</v>
@@ -6049,37 +6049,37 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M58">
-        <v>2672.660095562796</v>
+        <v>2608.406124207968</v>
       </c>
       <c r="N58">
-        <v>3344.358271784144</v>
+        <v>3408.612243138972</v>
       </c>
       <c r="O58">
-        <v>668.8716543568288</v>
+        <v>681.7224486277944</v>
       </c>
       <c r="P58">
-        <v>2675.486617427315</v>
+        <v>2726.889794511178</v>
       </c>
       <c r="Q58">
-        <v>7519.386617427314</v>
+        <v>7570.789794511177</v>
       </c>
       <c r="R58">
         <v>1.272727272727273</v>
       </c>
       <c r="S58">
-        <v>0.1678033969907802</v>
+        <v>0.1677703875845171</v>
       </c>
       <c r="T58">
         <v>1.886843104700879</v>
       </c>
       <c r="U58">
-        <v>0.07903097776675758</v>
+        <v>0.07713097776675758</v>
       </c>
       <c r="V58">
         <v>0.2</v>
       </c>
       <c r="W58">
-        <v>0.06322478221340606</v>
+        <v>0.06170478221340606</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>2.25132196096934</v>
+        <v>2.30677972709253</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6098,13 +6098,13 @@
         <v>0.5700000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1114359162702966</v>
+        <v>0.108411824843565</v>
       </c>
       <c r="C59">
-        <v>22021.80124217371</v>
+        <v>24205.3184745978</v>
       </c>
       <c r="D59">
-        <v>45445.37161083173</v>
+        <v>47628.88884325582</v>
       </c>
       <c r="E59">
         <v>454.4995464509775</v>
@@ -6131,45 +6131,45 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M59">
-        <v>2882.168489430539</v>
+        <v>2654.984804997396</v>
       </c>
       <c r="N59">
-        <v>3134.849877916401</v>
+        <v>3362.033562349544</v>
       </c>
       <c r="O59">
-        <v>626.9699755832803</v>
+        <v>672.4067124699088</v>
       </c>
       <c r="P59">
-        <v>2507.879902333121</v>
+        <v>2689.626849879635</v>
       </c>
       <c r="Q59">
-        <v>7351.779902333121</v>
+        <v>7533.526849879635</v>
       </c>
       <c r="R59">
         <v>1.325581395348838</v>
       </c>
       <c r="S59">
-        <v>0.1703595125782678</v>
+        <v>0.1703258115858688</v>
       </c>
       <c r="T59">
         <v>1.926374701279569</v>
       </c>
       <c r="U59">
-        <v>0.08373097776675759</v>
+        <v>0.07713097776675758</v>
       </c>
       <c r="V59">
         <v>0.2</v>
       </c>
       <c r="W59">
-        <v>0.06698478221340608</v>
+        <v>0.06170478221340606</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y59">
-        <v>2.087670581859629</v>
+        <v>2.266309907318977</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6180,13 +6180,13 @@
         <v>0.58</v>
       </c>
       <c r="B60">
-        <v>0.1115268598251425</v>
+        <v>0.1097492011104352</v>
       </c>
       <c r="C60">
-        <v>21355.02964086507</v>
+        <v>22605.35988045541</v>
       </c>
       <c r="D60">
-        <v>45382.49071774515</v>
+        <v>46632.82095733549</v>
       </c>
       <c r="E60">
         <v>1058.390254673046</v>
@@ -6213,37 +6213,37 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M60">
-        <v>2932.732848894233</v>
+        <v>2799.635336802089</v>
       </c>
       <c r="N60">
-        <v>3084.285518452707</v>
+        <v>3217.383030544851</v>
       </c>
       <c r="O60">
-        <v>616.8571036905415</v>
+        <v>643.4766061089704</v>
       </c>
       <c r="P60">
-        <v>2467.428414762166</v>
+        <v>2573.906424435881</v>
       </c>
       <c r="Q60">
-        <v>7311.328414762165</v>
+        <v>7417.806424435881</v>
       </c>
       <c r="R60">
         <v>1.380952380952381</v>
       </c>
       <c r="S60">
-        <v>0.1730373479556356</v>
+        <v>0.1730029224444277</v>
       </c>
       <c r="T60">
         <v>1.967788754838196</v>
       </c>
       <c r="U60">
-        <v>0.08373097776675759</v>
+        <v>0.07993097776675759</v>
       </c>
       <c r="V60">
         <v>0.2</v>
       </c>
       <c r="W60">
-        <v>0.06698478221340608</v>
+        <v>0.06394478221340608</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6251,7 +6251,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>2.051676261482738</v>
+        <v>2.149215038205632</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6262,13 +6262,13 @@
         <v>0.59</v>
       </c>
       <c r="B61">
-        <v>0.1116178033799884</v>
+        <v>0.1098097773773053</v>
       </c>
       <c r="C61">
-        <v>20688.4318105319</v>
+        <v>21957.33775476929</v>
       </c>
       <c r="D61">
-        <v>45319.78359563405</v>
+        <v>46588.68953987143</v>
       </c>
       <c r="E61">
         <v>1662.280962895114</v>
@@ -6295,37 +6295,37 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M61">
-        <v>2983.297208357926</v>
+        <v>2847.904911574538</v>
       </c>
       <c r="N61">
-        <v>3033.721158989014</v>
+        <v>3169.113455772402</v>
       </c>
       <c r="O61">
-        <v>606.7442317978029</v>
+        <v>633.8226911544804</v>
       </c>
       <c r="P61">
-        <v>2426.976927191211</v>
+        <v>2535.290764617921</v>
       </c>
       <c r="Q61">
-        <v>7270.876927191211</v>
+        <v>7379.190764617921</v>
       </c>
       <c r="R61">
         <v>1.439024390243902</v>
       </c>
       <c r="S61">
-        <v>0.1758458094489727</v>
+        <v>0.1758106240765749</v>
       </c>
       <c r="T61">
         <v>2.011223006131392</v>
       </c>
       <c r="U61">
-        <v>0.08373097776675759</v>
+        <v>0.07993097776675759</v>
       </c>
       <c r="V61">
         <v>0.2</v>
       </c>
       <c r="W61">
-        <v>0.06698478221340608</v>
+        <v>0.06394478221340608</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>2.016902087559302</v>
+        <v>2.112787664676723</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6344,13 +6344,13 @@
         <v>0.6</v>
       </c>
       <c r="B62">
-        <v>0.1161727469348343</v>
+        <v>0.1098703536441754</v>
       </c>
       <c r="C62">
-        <v>17151.17463322631</v>
+        <v>21309.39907849057</v>
       </c>
       <c r="D62">
-        <v>42386.41712655052</v>
+        <v>46544.64157181479</v>
       </c>
       <c r="E62">
         <v>2266.171671117183</v>
@@ -6377,45 +6377,45 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M62">
-        <v>3370.832583009535</v>
+        <v>2896.174486346988</v>
       </c>
       <c r="N62">
-        <v>2646.185784337405</v>
+        <v>3120.843880999952</v>
       </c>
       <c r="O62">
-        <v>529.2371568674811</v>
+        <v>624.1687761999906</v>
       </c>
       <c r="P62">
-        <v>2116.948627469924</v>
+        <v>2496.675104799962</v>
       </c>
       <c r="Q62">
-        <v>6960.848627469924</v>
+        <v>7340.575104799962</v>
       </c>
       <c r="R62">
         <v>1.5</v>
       </c>
       <c r="S62">
-        <v>0.1787946940169766</v>
+        <v>0.1787587107903295</v>
       </c>
       <c r="T62">
         <v>2.056828969989247</v>
       </c>
       <c r="U62">
-        <v>0.09303097776675757</v>
+        <v>0.07993097776675759</v>
       </c>
       <c r="V62">
         <v>0.2</v>
       </c>
       <c r="W62">
-        <v>0.07442478221340607</v>
+        <v>0.06394478221340608</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y62">
-        <v>1.785024387646938</v>
+        <v>2.077574536932112</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6426,13 +6426,13 @@
         <v>0.61</v>
       </c>
       <c r="B63">
-        <v>0.1163380904896802</v>
+        <v>0.1099309299110456</v>
       </c>
       <c r="C63">
-        <v>16447.92879877055</v>
+        <v>20661.54361514737</v>
       </c>
       <c r="D63">
-        <v>42287.06200031684</v>
+        <v>46500.67681669367</v>
       </c>
       <c r="E63">
         <v>2870.062379339259</v>
@@ -6459,45 +6459,45 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M63">
-        <v>3427.013126059694</v>
+        <v>2944.444061119438</v>
       </c>
       <c r="N63">
-        <v>2590.005241287246</v>
+        <v>3072.574306227502</v>
       </c>
       <c r="O63">
-        <v>518.0010482574493</v>
+        <v>614.5148612455005</v>
       </c>
       <c r="P63">
-        <v>2072.004193029797</v>
+        <v>2458.059444982001</v>
       </c>
       <c r="Q63">
-        <v>6915.904193029796</v>
+        <v>7301.959444982002</v>
       </c>
       <c r="R63">
         <v>1.564102564102564</v>
       </c>
       <c r="S63">
-        <v>0.1818948034346218</v>
+        <v>0.1818579814381227</v>
       </c>
       <c r="T63">
         <v>2.104773701224427</v>
       </c>
       <c r="U63">
-        <v>0.09303097776675757</v>
+        <v>0.07993097776675759</v>
       </c>
       <c r="V63">
         <v>0.2</v>
       </c>
       <c r="W63">
-        <v>0.07442478221340607</v>
+        <v>0.06394478221340608</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y63">
-        <v>1.75576169276748</v>
+        <v>2.043515937966011</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6508,13 +6508,13 @@
         <v>0.62</v>
       </c>
       <c r="B64">
-        <v>0.1188346340445261</v>
+        <v>0.1099915061779157</v>
       </c>
       <c r="C64">
-        <v>14398.53906845579</v>
+        <v>20013.77112916048</v>
       </c>
       <c r="D64">
-        <v>40841.56297822415</v>
+        <v>46456.79503892884</v>
       </c>
       <c r="E64">
         <v>3473.953087561327</v>
@@ -6541,45 +6541,45 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M64">
-        <v>3659.167421485764</v>
+        <v>2992.713635891888</v>
       </c>
       <c r="N64">
-        <v>2357.850945861176</v>
+        <v>3024.304731455052</v>
       </c>
       <c r="O64">
-        <v>471.5701891722352</v>
+        <v>604.8609462910105</v>
       </c>
       <c r="P64">
-        <v>1886.280756688941</v>
+        <v>2419.443785164042</v>
       </c>
       <c r="Q64">
-        <v>6730.18075668894</v>
+        <v>7263.343785164041</v>
       </c>
       <c r="R64">
         <v>1.631578947368421</v>
       </c>
       <c r="S64">
-        <v>0.1851580765058272</v>
+        <v>0.1851203715936945</v>
       </c>
       <c r="T64">
         <v>2.155241839366723</v>
       </c>
       <c r="U64">
-        <v>0.09773097776675757</v>
+        <v>0.07993097776675759</v>
       </c>
       <c r="V64">
         <v>0.2</v>
       </c>
       <c r="W64">
-        <v>0.07818478221340606</v>
+        <v>0.06394478221340608</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y64">
-        <v>1.644368151076235</v>
+        <v>2.010556003482689</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6590,13 +6590,13 @@
         <v>0.63</v>
       </c>
       <c r="B65">
-        <v>0.119037577599372</v>
+        <v>0.1139832824447858</v>
       </c>
       <c r="C65">
-        <v>13681.47514713806</v>
+        <v>16690.07689693796</v>
       </c>
       <c r="D65">
-        <v>40728.38976512849</v>
+        <v>43736.99151492839</v>
       </c>
       <c r="E65">
         <v>4077.843795783396</v>
@@ -6623,45 +6623,45 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M65">
-        <v>3718.186250864566</v>
+        <v>3337.735104684663</v>
       </c>
       <c r="N65">
-        <v>2298.832116482374</v>
+        <v>2679.283262662277</v>
       </c>
       <c r="O65">
-        <v>459.7664232964748</v>
+        <v>535.8566525324554</v>
       </c>
       <c r="P65">
-        <v>1839.065693185899</v>
+        <v>2143.426610129822</v>
       </c>
       <c r="Q65">
-        <v>6682.965693185899</v>
+        <v>6987.326610129821</v>
       </c>
       <c r="R65">
         <v>1.702702702702703</v>
       </c>
       <c r="S65">
-        <v>0.1885977427160167</v>
+        <v>0.188559107163081</v>
       </c>
       <c r="T65">
         <v>2.208437984976169</v>
       </c>
       <c r="U65">
-        <v>0.09773097776675757</v>
+        <v>0.08773097776675759</v>
       </c>
       <c r="V65">
         <v>0.2</v>
       </c>
       <c r="W65">
-        <v>0.07818478221340606</v>
+        <v>0.07018478221340607</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y65">
-        <v>1.61826706931312</v>
+        <v>1.802724955285331</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6672,13 +6672,13 @@
         <v>0.64</v>
       </c>
       <c r="B66">
-        <v>0.1192405211542179</v>
+        <v>0.1141062587116559</v>
       </c>
       <c r="C66">
-        <v>12965.03670542798</v>
+        <v>16007.44359554677</v>
       </c>
       <c r="D66">
-        <v>40615.8420316405</v>
+        <v>43658.24892175928</v>
       </c>
       <c r="E66">
         <v>4681.734504005472</v>
@@ -6705,45 +6705,45 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M66">
-        <v>3777.20508024337</v>
+        <v>3390.715026981245</v>
       </c>
       <c r="N66">
-        <v>2239.81328710357</v>
+        <v>2626.303340365695</v>
       </c>
       <c r="O66">
-        <v>447.9626574207141</v>
+        <v>525.2606680731391</v>
       </c>
       <c r="P66">
-        <v>1791.850629682856</v>
+        <v>2101.042672292556</v>
       </c>
       <c r="Q66">
-        <v>6635.750629682856</v>
+        <v>6944.942672292555</v>
       </c>
       <c r="R66">
         <v>1.777777777777778</v>
       </c>
       <c r="S66">
-        <v>0.1922285014934389</v>
+        <v>0.1921888835974334</v>
       </c>
       <c r="T66">
         <v>2.264589472008363</v>
       </c>
       <c r="U66">
-        <v>0.09773097776675757</v>
+        <v>0.08773097776675759</v>
       </c>
       <c r="V66">
         <v>0.2</v>
       </c>
       <c r="W66">
-        <v>0.07818478221340606</v>
+        <v>0.07018478221340607</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y66">
-        <v>1.592981646355103</v>
+        <v>1.774557377858998</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6754,13 +6754,13 @@
         <v>0.65</v>
       </c>
       <c r="B67">
-        <v>0.1194434647090638</v>
+        <v>0.1162572349785261</v>
       </c>
       <c r="C67">
-        <v>12249.21857231459</v>
+        <v>14070.71805052712</v>
       </c>
       <c r="D67">
-        <v>40503.91460674917</v>
+        <v>42325.4140849617</v>
       </c>
       <c r="E67">
         <v>5285.62521222754</v>
@@ -6787,37 +6787,37 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M67">
-        <v>3836.223909622172</v>
+        <v>3596.781243812121</v>
       </c>
       <c r="N67">
-        <v>2180.794457724768</v>
+        <v>2420.237123534819</v>
       </c>
       <c r="O67">
-        <v>436.1588915449536</v>
+        <v>484.0474247069637</v>
       </c>
       <c r="P67">
-        <v>1744.635566179815</v>
+        <v>1936.189698827855</v>
       </c>
       <c r="Q67">
-        <v>6588.535566179814</v>
+        <v>6780.089698827855</v>
       </c>
       <c r="R67">
         <v>1.857142857142857</v>
       </c>
       <c r="S67">
-        <v>0.1960667322009996</v>
+        <v>0.1960260758280346</v>
       </c>
       <c r="T67">
         <v>2.323949615442396</v>
       </c>
       <c r="U67">
-        <v>0.09773097776675757</v>
+        <v>0.09163097776675758</v>
       </c>
       <c r="V67">
         <v>0.2</v>
       </c>
       <c r="W67">
-        <v>0.07818478221340606</v>
+        <v>0.07330478221340607</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>1.568474236411178</v>
+        <v>1.672889719856769</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6836,13 +6836,13 @@
         <v>0.66</v>
       </c>
       <c r="B68">
-        <v>0.1196464082639097</v>
+        <v>0.1164114112453962</v>
       </c>
       <c r="C68">
-        <v>11534.01563363046</v>
+        <v>13374.41204820092</v>
       </c>
       <c r="D68">
-        <v>40392.6023762871</v>
+        <v>42232.99879085756</v>
       </c>
       <c r="E68">
         <v>5889.515920449609</v>
@@ -6869,37 +6869,37 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M68">
-        <v>3895.242739000974</v>
+        <v>3652.116339870769</v>
       </c>
       <c r="N68">
-        <v>2121.775628345966</v>
+        <v>2364.902027476171</v>
       </c>
       <c r="O68">
-        <v>424.3551256691932</v>
+        <v>472.9804054952342</v>
       </c>
       <c r="P68">
-        <v>1697.420502676773</v>
+        <v>1891.921621980937</v>
       </c>
       <c r="Q68">
-        <v>6541.320502676772</v>
+        <v>6735.821621980936</v>
       </c>
       <c r="R68">
         <v>1.941176470588236</v>
       </c>
       <c r="S68">
-        <v>0.2001307411854756</v>
+        <v>0.2000889852486711</v>
       </c>
       <c r="T68">
         <v>2.386801532019607</v>
       </c>
       <c r="U68">
-        <v>0.09773097776675757</v>
+        <v>0.09163097776675758</v>
       </c>
       <c r="V68">
         <v>0.2</v>
       </c>
       <c r="W68">
-        <v>0.07818478221340606</v>
+        <v>0.07330478221340607</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>1.544709475253433</v>
+        <v>1.647542905919545</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6918,13 +6918,13 @@
         <v>0.67</v>
       </c>
       <c r="B69">
-        <v>0.1198493518187556</v>
+        <v>0.1165655875122663</v>
       </c>
       <c r="C69">
-        <v>10819.42283127276</v>
+        <v>12678.50873440022</v>
       </c>
       <c r="D69">
-        <v>40281.90028215148</v>
+        <v>42140.98618527894</v>
       </c>
       <c r="E69">
         <v>6493.406628671684</v>
@@ -6951,37 +6951,37 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M69">
-        <v>3954.261568379778</v>
+        <v>3707.451435929418</v>
       </c>
       <c r="N69">
-        <v>2062.756798967162</v>
+        <v>2309.566931417522</v>
       </c>
       <c r="O69">
-        <v>412.5513597934325</v>
+        <v>461.9133862835045</v>
       </c>
       <c r="P69">
-        <v>1650.20543917373</v>
+        <v>1847.653545134018</v>
       </c>
       <c r="Q69">
-        <v>6494.10543917373</v>
+        <v>6691.553545134017</v>
       </c>
       <c r="R69">
         <v>2.030303030303031</v>
       </c>
       <c r="S69">
-        <v>0.2044410537447683</v>
+        <v>0.2043981316038916</v>
       </c>
       <c r="T69">
         <v>2.453462655662105</v>
       </c>
       <c r="U69">
-        <v>0.09773097776675757</v>
+        <v>0.09163097776675758</v>
       </c>
       <c r="V69">
         <v>0.2</v>
       </c>
       <c r="W69">
-        <v>0.07818478221340606</v>
+        <v>0.07330478221340607</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>1.521654109951143</v>
+        <v>1.62295271329388</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7000,13 +7000,13 @@
         <v>0.68</v>
       </c>
       <c r="B70">
-        <v>0.1289194953736015</v>
+        <v>0.1167197637791364</v>
       </c>
       <c r="C70">
-        <v>5819.901271601382</v>
+        <v>11983.00548284673</v>
       </c>
       <c r="D70">
-        <v>35886.26943070217</v>
+        <v>42049.37364194751</v>
       </c>
       <c r="E70">
         <v>7097.297336893753</v>
@@ -7033,45 +7033,45 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M70">
-        <v>4682.632858751923</v>
+        <v>3762.786531988066</v>
       </c>
       <c r="N70">
-        <v>1334.385508595017</v>
+        <v>2254.231835358874</v>
       </c>
       <c r="O70">
-        <v>266.8771017190035</v>
+        <v>450.8463670717749</v>
       </c>
       <c r="P70">
-        <v>1067.508406876014</v>
+        <v>1803.385468287099</v>
       </c>
       <c r="Q70">
-        <v>5911.408406876013</v>
+        <v>6647.285468287099</v>
       </c>
       <c r="R70">
         <v>2.125</v>
       </c>
       <c r="S70">
-        <v>0.2090207608390168</v>
+        <v>0.2089765996063134</v>
       </c>
       <c r="T70">
         <v>2.524290099532257</v>
       </c>
       <c r="U70">
-        <v>0.1140309777667576</v>
+        <v>0.09163097776675758</v>
       </c>
       <c r="V70">
         <v>0.2</v>
       </c>
       <c r="W70">
-        <v>0.09122478221340607</v>
+        <v>0.07330478221340607</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y70">
-        <v>1.284964794133076</v>
+        <v>1.599085761627794</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7082,13 +7082,13 @@
         <v>0.6900000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1292528389284474</v>
+        <v>0.1168739400460065</v>
       </c>
       <c r="C71">
-        <v>5072.666648710991</v>
+        <v>11287.89969005011</v>
       </c>
       <c r="D71">
-        <v>35742.92551603385</v>
+        <v>41958.15855737297</v>
       </c>
       <c r="E71">
         <v>7701.188045115821</v>
@@ -7115,45 +7115,45 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M71">
-        <v>4751.495106674745</v>
+        <v>3818.121628046713</v>
       </c>
       <c r="N71">
-        <v>1265.523260672195</v>
+        <v>2198.896739300227</v>
       </c>
       <c r="O71">
-        <v>253.104652134439</v>
+        <v>439.7793478600454</v>
       </c>
       <c r="P71">
-        <v>1012.418608537756</v>
+        <v>1759.117391440181</v>
       </c>
       <c r="Q71">
-        <v>5856.318608537756</v>
+        <v>6603.017391440181</v>
       </c>
       <c r="R71">
         <v>2.225806451612904</v>
       </c>
       <c r="S71">
-        <v>0.2138959329070878</v>
+        <v>0.2138504526411495</v>
       </c>
       <c r="T71">
         <v>2.599687055910163</v>
       </c>
       <c r="U71">
-        <v>0.1140309777667576</v>
+        <v>0.09163097776675758</v>
       </c>
       <c r="V71">
         <v>0.2</v>
       </c>
       <c r="W71">
-        <v>0.09122478221340607</v>
+        <v>0.07330478221340607</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y71">
-        <v>1.266342115957234</v>
+        <v>1.575910605662174</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7164,13 +7164,13 @@
         <v>0.7000000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1487663169911663</v>
+        <v>0.1170281163128767</v>
       </c>
       <c r="C72">
-        <v>-2304.980889274731</v>
+        <v>10593.18877506158</v>
       </c>
       <c r="D72">
-        <v>28969.1686862702</v>
+        <v>41867.33835060651</v>
       </c>
       <c r="E72">
         <v>8305.078753337897</v>
@@ -7197,45 +7197,45 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M72">
-        <v>6202.663185717888</v>
+        <v>3873.456724105362</v>
       </c>
       <c r="N72">
-        <v>-185.6448183709481</v>
+        <v>2143.561643241578</v>
       </c>
       <c r="O72">
-        <v>-37.12896367418962</v>
+        <v>428.7123286483156</v>
       </c>
       <c r="P72">
-        <v>-148.5158546967585</v>
+        <v>1714.849314593263</v>
       </c>
       <c r="Q72">
-        <v>4695.384145303241</v>
+        <v>6558.749314593262</v>
       </c>
       <c r="R72">
         <v>2.333333333333334</v>
       </c>
       <c r="S72">
-        <v>0.2199404674962408</v>
+        <v>0.2190492292116414</v>
       </c>
       <c r="T72">
-        <v>2.693168784222459</v>
+        <v>2.680110476046594</v>
       </c>
       <c r="U72">
-        <v>0.1467309777667576</v>
+        <v>0.09163097776675758</v>
       </c>
       <c r="V72">
-        <v>0.1940140287224233</v>
+        <v>0.2</v>
       </c>
       <c r="W72">
-        <v>0.1182631096318486</v>
+        <v>0.07330478221340607</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y72">
-        <v>0.9700701436121165</v>
+        <v>1.553397597009857</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7246,13 +7246,13 @@
         <v>0.71</v>
       </c>
       <c r="B73">
-        <v>0.1497756267688338</v>
+        <v>0.1171822925797468</v>
       </c>
       <c r="C73">
-        <v>-3190.080435708063</v>
+        <v>9898.870179230362</v>
       </c>
       <c r="D73">
-        <v>28687.95984805893</v>
+        <v>41776.91046299735</v>
       </c>
       <c r="E73">
         <v>8908.969461559958</v>
@@ -7279,45 +7279,45 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M73">
-        <v>6291.272659799571</v>
+        <v>3928.791820164009</v>
       </c>
       <c r="N73">
-        <v>-274.2542924526306</v>
+        <v>2088.226547182931</v>
       </c>
       <c r="O73">
-        <v>-54.85085849052612</v>
+        <v>417.6453094365862</v>
       </c>
       <c r="P73">
-        <v>-219.4034339621045</v>
+        <v>1670.581237746345</v>
       </c>
       <c r="Q73">
-        <v>4624.496566037895</v>
+        <v>6514.481237746344</v>
       </c>
       <c r="R73">
         <v>2.448275862068965</v>
       </c>
       <c r="S73">
-        <v>0.2259453112030076</v>
+        <v>0.2246065420973396</v>
       </c>
       <c r="T73">
-        <v>2.786036673333577</v>
+        <v>2.766080338951055</v>
       </c>
       <c r="U73">
-        <v>0.1467309777667576</v>
+        <v>0.09163097776675758</v>
       </c>
       <c r="V73">
-        <v>0.1912814367685864</v>
+        <v>0.2</v>
       </c>
       <c r="W73">
-        <v>0.1186640655210727</v>
+        <v>0.07330478221340607</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y73">
-        <v>0.956407183842932</v>
+        <v>1.531518757615352</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7328,13 +7328,13 @@
         <v>0.72</v>
       </c>
       <c r="B74">
-        <v>0.1507849365465014</v>
+        <v>0.1173364688466169</v>
       </c>
       <c r="C74">
-        <v>-4069.772981112314</v>
+        <v>9204.941365963401</v>
       </c>
       <c r="D74">
-        <v>28412.15801087674</v>
+        <v>41686.87235795247</v>
       </c>
       <c r="E74">
         <v>9512.860169782027</v>
@@ -7361,45 +7361,45 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M74">
-        <v>6379.882133881255</v>
+        <v>3984.126916222657</v>
       </c>
       <c r="N74">
-        <v>-362.8637665343149</v>
+        <v>2032.891451124283</v>
       </c>
       <c r="O74">
-        <v>-72.57275330686298</v>
+        <v>406.5782902248567</v>
       </c>
       <c r="P74">
-        <v>-290.2910132274519</v>
+        <v>1626.313160899427</v>
       </c>
       <c r="Q74">
-        <v>4553.608986772548</v>
+        <v>6470.213160899426</v>
       </c>
       <c r="R74">
         <v>2.571428571428571</v>
       </c>
       <c r="S74">
-        <v>0.2323790723174008</v>
+        <v>0.2305608059034448</v>
       </c>
       <c r="T74">
-        <v>2.885537983095491</v>
+        <v>2.858190906348693</v>
       </c>
       <c r="U74">
-        <v>0.1467309777667576</v>
+        <v>0.09163097776675758</v>
       </c>
       <c r="V74">
-        <v>0.1886247501468005</v>
+        <v>0.2</v>
       </c>
       <c r="W74">
-        <v>0.1190538837467072</v>
+        <v>0.07330478221340607</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y74">
-        <v>0.9431237507340025</v>
+        <v>1.510247663759583</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7410,13 +7410,13 @@
         <v>0.73</v>
       </c>
       <c r="B75">
-        <v>0.151794246324169</v>
+        <v>0.125783445113487</v>
       </c>
       <c r="C75">
-        <v>-4944.212986862403</v>
+        <v>4198.539351207328</v>
       </c>
       <c r="D75">
-        <v>28141.60871334873</v>
+        <v>37284.36105141846</v>
       </c>
       <c r="E75">
         <v>10116.7508780041</v>
@@ -7443,45 +7443,45 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M75">
-        <v>6468.491607962939</v>
+        <v>4665.455120424303</v>
       </c>
       <c r="N75">
-        <v>-451.4732406159992</v>
+        <v>1351.563246922637</v>
       </c>
       <c r="O75">
-        <v>-90.29464812319985</v>
+        <v>270.3126493845273</v>
       </c>
       <c r="P75">
-        <v>-361.1785924927993</v>
+        <v>1081.250597538109</v>
       </c>
       <c r="Q75">
-        <v>4482.721407507201</v>
+        <v>5925.150597538109</v>
       </c>
       <c r="R75">
         <v>2.703703703703703</v>
       </c>
       <c r="S75">
-        <v>0.2392894083291564</v>
+        <v>0.23695612628778</v>
       </c>
       <c r="T75">
-        <v>2.992409760247175</v>
+        <v>2.957124478738748</v>
       </c>
       <c r="U75">
-        <v>0.1467309777667576</v>
+        <v>0.1058309777667576</v>
       </c>
       <c r="V75">
-        <v>0.186040849459858</v>
+        <v>0.2</v>
       </c>
       <c r="W75">
-        <v>0.1194330220209545</v>
+        <v>0.08466478221340606</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y75">
-        <v>0.93020424729929</v>
+        <v>1.289695905766149</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7492,13 +7492,13 @@
         <v>0.74</v>
       </c>
       <c r="B76">
-        <v>0.1528035561018365</v>
+        <v>0.1260512213803572</v>
       </c>
       <c r="C76">
-        <v>-5813.54908651283</v>
+        <v>3470.240978612557</v>
       </c>
       <c r="D76">
-        <v>27876.16332192038</v>
+        <v>37159.95338704577</v>
       </c>
       <c r="E76">
         <v>10720.64158622617</v>
@@ -7525,45 +7525,45 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M76">
-        <v>6557.101082044624</v>
+        <v>4729.365464539705</v>
       </c>
       <c r="N76">
-        <v>-540.0827146976835</v>
+        <v>1287.652902807235</v>
       </c>
       <c r="O76">
-        <v>-108.0165429395367</v>
+        <v>257.5305805614471</v>
       </c>
       <c r="P76">
-        <v>-432.0661717581468</v>
+        <v>1030.122322245788</v>
       </c>
       <c r="Q76">
-        <v>4411.833828241853</v>
+        <v>5874.022322245788</v>
       </c>
       <c r="R76">
         <v>2.846153846153846</v>
       </c>
       <c r="S76">
-        <v>0.2467313086495085</v>
+        <v>0.2438433943939872</v>
       </c>
       <c r="T76">
-        <v>3.107502443333605</v>
+        <v>3.063668325928038</v>
       </c>
       <c r="U76">
-        <v>0.1467309777667576</v>
+        <v>0.1058309777667576</v>
       </c>
       <c r="V76">
-        <v>0.1835267839266167</v>
+        <v>0.2</v>
       </c>
       <c r="W76">
-        <v>0.1198019133148167</v>
+        <v>0.08466478221340606</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y76">
-        <v>0.9176339196330834</v>
+        <v>1.272267582715255</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7574,13 +7574,13 @@
         <v>0.75</v>
       </c>
       <c r="B77">
-        <v>0.1538128658795042</v>
+        <v>0.1263189976472273</v>
       </c>
       <c r="C77">
-        <v>-6677.924358083677</v>
+        <v>2742.770073346226</v>
       </c>
       <c r="D77">
-        <v>27615.6787585716</v>
+        <v>37036.3731900015</v>
       </c>
       <c r="E77">
         <v>11324.53229444825</v>
@@ -7607,45 +7607,45 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M77">
-        <v>6645.710556126308</v>
+        <v>4793.275808655107</v>
       </c>
       <c r="N77">
-        <v>-628.6921887793678</v>
+        <v>1223.742558691833</v>
       </c>
       <c r="O77">
-        <v>-125.7384377558736</v>
+        <v>244.7485117383667</v>
       </c>
       <c r="P77">
-        <v>-502.9537510234942</v>
+        <v>978.9940469534667</v>
       </c>
       <c r="Q77">
-        <v>4340.946248976506</v>
+        <v>5822.894046953466</v>
       </c>
       <c r="R77">
         <v>3</v>
       </c>
       <c r="S77">
-        <v>0.2547685609954889</v>
+        <v>0.251281643948691</v>
       </c>
       <c r="T77">
-        <v>3.23180254106695</v>
+        <v>3.178735680892472</v>
       </c>
       <c r="U77">
-        <v>0.1467309777667576</v>
+        <v>0.1058309777667576</v>
       </c>
       <c r="V77">
-        <v>0.1810797601409284</v>
+        <v>0.2</v>
       </c>
       <c r="W77">
-        <v>0.1201609675075092</v>
+        <v>0.08466478221340606</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y77">
-        <v>0.9053988007046422</v>
+        <v>1.255304014945718</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7656,13 +7656,13 @@
         <v>0.76</v>
       </c>
       <c r="B78">
-        <v>0.1548221756571717</v>
+        <v>0.1447090563326442</v>
       </c>
       <c r="C78">
-        <v>-7537.476581221774</v>
+        <v>-4747.255248965157</v>
       </c>
       <c r="D78">
-        <v>27360.01724365558</v>
+        <v>30150.23857591219</v>
       </c>
       <c r="E78">
         <v>11928.42300267032</v>
@@ -7689,37 +7689,37 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M78">
-        <v>6734.320030207992</v>
+        <v>6169.802996162</v>
       </c>
       <c r="N78">
-        <v>-717.3016628610521</v>
+        <v>-152.7846288150604</v>
       </c>
       <c r="O78">
-        <v>-143.4603325722104</v>
+        <v>-30.55692576301208</v>
       </c>
       <c r="P78">
-        <v>-573.8413302888417</v>
+        <v>-122.2277030520483</v>
       </c>
       <c r="Q78">
-        <v>4270.058669711158</v>
+        <v>4721.672296947952</v>
       </c>
       <c r="R78">
         <v>3.166666666666667</v>
       </c>
       <c r="S78">
-        <v>0.2634755843703009</v>
+        <v>0.2602875871847698</v>
       </c>
       <c r="T78">
-        <v>3.366460980278073</v>
+        <v>3.318054758521442</v>
       </c>
       <c r="U78">
-        <v>0.1467309777667576</v>
+        <v>0.1344309777667576</v>
       </c>
       <c r="V78">
-        <v>0.1786971317180215</v>
+        <v>0.1950473417413781</v>
       </c>
       <c r="W78">
-        <v>0.1205105729056572</v>
+        <v>0.1082105729056572</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.8934856585901074</v>
+        <v>0.9752367087068904</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7738,13 +7738,13 @@
         <v>0.77</v>
       </c>
       <c r="B79">
-        <v>0.1558314854348393</v>
+        <v>0.1455953661103118</v>
       </c>
       <c r="C79">
-        <v>-8392.338480208389</v>
+        <v>-5618.918422887713</v>
       </c>
       <c r="D79">
-        <v>27109.04605289103</v>
+        <v>29882.46611021171</v>
       </c>
       <c r="E79">
         <v>12532.31371089238</v>
@@ -7771,37 +7771,37 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M79">
-        <v>6822.929504289676</v>
+        <v>6250.984614532553</v>
       </c>
       <c r="N79">
-        <v>-805.9111369427355</v>
+        <v>-233.9662471856127</v>
       </c>
       <c r="O79">
-        <v>-161.1822273885471</v>
+        <v>-46.79324943712254</v>
       </c>
       <c r="P79">
-        <v>-644.7289095541885</v>
+        <v>-187.1729977484902</v>
       </c>
       <c r="Q79">
-        <v>4199.171090445811</v>
+        <v>4656.727002251509</v>
       </c>
       <c r="R79">
         <v>3.347826086956522</v>
       </c>
       <c r="S79">
-        <v>0.2729397402124879</v>
+        <v>0.2696131344536729</v>
       </c>
       <c r="T79">
-        <v>3.512828848985815</v>
+        <v>3.46231800889194</v>
       </c>
       <c r="U79">
-        <v>0.1467309777667576</v>
+        <v>0.1344309777667576</v>
       </c>
       <c r="V79">
-        <v>0.1763763897476576</v>
+        <v>0.1925142593811004</v>
       </c>
       <c r="W79">
-        <v>0.1208510976441131</v>
+        <v>0.1085510976441131</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.881881948738288</v>
+        <v>0.9625712969055022</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7820,13 +7820,13 @@
         <v>0.78</v>
       </c>
       <c r="B80">
-        <v>0.1568407952125069</v>
+        <v>0.1464816758879794</v>
       </c>
       <c r="C80">
-        <v>-9242.637953714082</v>
+        <v>-6485.867146987162</v>
       </c>
       <c r="D80">
-        <v>26862.63728760742</v>
+        <v>29619.40809433433</v>
       </c>
       <c r="E80">
         <v>13136.20441911446</v>
@@ -7853,37 +7853,37 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M80">
-        <v>6911.538978371361</v>
+        <v>6332.166232903106</v>
       </c>
       <c r="N80">
-        <v>-894.5206110244208</v>
+        <v>-315.1478655561659</v>
       </c>
       <c r="O80">
-        <v>-178.9041222048842</v>
+        <v>-63.02957311123319</v>
       </c>
       <c r="P80">
-        <v>-715.6164888195366</v>
+        <v>-252.1182924449327</v>
       </c>
       <c r="Q80">
-        <v>4128.283511180463</v>
+        <v>4591.781707555067</v>
       </c>
       <c r="R80">
         <v>3.545454545454546</v>
       </c>
       <c r="S80">
-        <v>0.2832642738585101</v>
+        <v>0.2797864587470216</v>
       </c>
       <c r="T80">
-        <v>3.672502887576079</v>
+        <v>3.61969610020521</v>
       </c>
       <c r="U80">
-        <v>0.1467309777667576</v>
+        <v>0.1344309777667576</v>
       </c>
       <c r="V80">
-        <v>0.174115153981662</v>
+        <v>0.1900461278505735</v>
       </c>
       <c r="W80">
-        <v>0.1211828909790188</v>
+        <v>0.1088828909790188</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.8705757699083098</v>
+        <v>0.9502306392528674</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7902,13 +7902,13 @@
         <v>0.79</v>
       </c>
       <c r="B81">
-        <v>0.1578501049901744</v>
+        <v>0.147367985665647</v>
       </c>
       <c r="C81">
-        <v>-10088.49829213594</v>
+        <v>-7348.224839965165</v>
       </c>
       <c r="D81">
-        <v>26620.66765740763</v>
+        <v>29360.94110957839</v>
       </c>
       <c r="E81">
         <v>13740.09512733653</v>
@@ -7935,37 +7935,37 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M81">
-        <v>7000.148452453044</v>
+        <v>6413.347851273658</v>
       </c>
       <c r="N81">
-        <v>-983.1300851061042</v>
+        <v>-396.3294839267182</v>
       </c>
       <c r="O81">
-        <v>-196.6260170212208</v>
+        <v>-79.26589678534366</v>
       </c>
       <c r="P81">
-        <v>-786.5040680848833</v>
+        <v>-317.0635871413746</v>
       </c>
       <c r="Q81">
-        <v>4057.395931915116</v>
+        <v>4526.836412858625</v>
       </c>
       <c r="R81">
         <v>3.761904761904763</v>
       </c>
       <c r="S81">
-        <v>0.2945720964232011</v>
+        <v>0.2909286710683084</v>
       </c>
       <c r="T81">
-        <v>3.847383977460655</v>
+        <v>3.792062581167363</v>
       </c>
       <c r="U81">
-        <v>0.1467309777667576</v>
+        <v>0.1344309777667576</v>
       </c>
       <c r="V81">
-        <v>0.1719111646907548</v>
+        <v>0.1876404806625916</v>
       </c>
       <c r="W81">
-        <v>0.121506284482661</v>
+        <v>0.109206284482661</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.8595558234537742</v>
+        <v>0.9382024033129578</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7984,13 +7984,13 @@
         <v>0.8</v>
       </c>
       <c r="B82">
-        <v>0.158859414767842</v>
+        <v>0.1482542954433145</v>
       </c>
       <c r="C82">
-        <v>-10930.0383832938</v>
+        <v>-8206.1106498503</v>
       </c>
       <c r="D82">
-        <v>26383.01827447183</v>
+        <v>29106.94600791534</v>
       </c>
       <c r="E82">
         <v>14343.9858355586</v>
@@ -8017,37 +8017,37 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M82">
-        <v>7088.757926534729</v>
+        <v>6494.529469644211</v>
       </c>
       <c r="N82">
-        <v>-1071.739559187788</v>
+        <v>-477.5111022972706</v>
       </c>
       <c r="O82">
-        <v>-214.3479118375577</v>
+        <v>-95.50222045945412</v>
       </c>
       <c r="P82">
-        <v>-857.3916473502308</v>
+        <v>-382.0088818378164</v>
       </c>
       <c r="Q82">
-        <v>3986.508352649769</v>
+        <v>4461.891118162183</v>
       </c>
       <c r="R82">
         <v>4.000000000000001</v>
       </c>
       <c r="S82">
-        <v>0.3070107012443611</v>
+        <v>0.3031851046217238</v>
       </c>
       <c r="T82">
-        <v>4.039753176333687</v>
+        <v>3.981665710225731</v>
       </c>
       <c r="U82">
-        <v>0.1467309777667576</v>
+        <v>0.1344309777667576</v>
       </c>
       <c r="V82">
-        <v>0.1697622751321204</v>
+        <v>0.1852949746543092</v>
       </c>
       <c r="W82">
-        <v>0.1218215931487122</v>
+        <v>0.1095215931487122</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.8488113756606021</v>
+        <v>0.9264748732715459</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8066,13 +8066,13 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1598687245455096</v>
+        <v>0.1491406052209821</v>
       </c>
       <c r="C83">
-        <v>-11767.37290720598</v>
+        <v>-9059.639637136948</v>
       </c>
       <c r="D83">
-        <v>26149.57445878172</v>
+        <v>28857.30772885076</v>
       </c>
       <c r="E83">
         <v>14947.87654378067</v>
@@ -8099,37 +8099,37 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M83">
-        <v>7177.367400616414</v>
+        <v>6575.711088014764</v>
       </c>
       <c r="N83">
-        <v>-1160.349033269474</v>
+        <v>-558.6927206678238</v>
       </c>
       <c r="O83">
-        <v>-232.0698066538947</v>
+        <v>-111.7385441335648</v>
       </c>
       <c r="P83">
-        <v>-928.279226615579</v>
+        <v>-446.954176534259</v>
       </c>
       <c r="Q83">
-        <v>3915.620773384421</v>
+        <v>4396.94582346574</v>
       </c>
       <c r="R83">
         <v>4.263157894736843</v>
       </c>
       <c r="S83">
-        <v>0.3207586328888012</v>
+        <v>0.3167316890754987</v>
       </c>
       <c r="T83">
-        <v>4.252371764561777</v>
+        <v>4.191227063395506</v>
       </c>
       <c r="U83">
-        <v>0.1467309777667576</v>
+        <v>0.1344309777667576</v>
       </c>
       <c r="V83">
-        <v>0.1676664445749337</v>
+        <v>0.1830073823746263</v>
       </c>
       <c r="W83">
-        <v>0.1221291164156017</v>
+        <v>0.1098291164156017</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.8383322228746686</v>
+        <v>0.9150369118731316</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8148,13 +8148,13 @@
         <v>0.8200000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1608780343231772</v>
+        <v>0.1500269149986497</v>
       </c>
       <c r="C84">
-        <v>-12600.61252061507</v>
+        <v>-9908.922948580308</v>
       </c>
       <c r="D84">
-        <v>25920.22555359471</v>
+        <v>28611.91512562947</v>
       </c>
       <c r="E84">
         <v>15551.76725200274</v>
@@ -8181,37 +8181,37 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M84">
-        <v>7265.976874698097</v>
+        <v>6656.892706385317</v>
       </c>
       <c r="N84">
-        <v>-1248.958507351157</v>
+        <v>-639.874339038377</v>
       </c>
       <c r="O84">
-        <v>-249.7917014702314</v>
+        <v>-127.9748678076754</v>
       </c>
       <c r="P84">
-        <v>-999.1668058809257</v>
+        <v>-511.8994712307016</v>
       </c>
       <c r="Q84">
-        <v>3844.733194119074</v>
+        <v>4332.000528769298</v>
       </c>
       <c r="R84">
         <v>4.555555555555557</v>
       </c>
       <c r="S84">
-        <v>0.3360341124937347</v>
+        <v>0.3317834495796932</v>
       </c>
       <c r="T84">
-        <v>4.488614640370765</v>
+        <v>4.424073011361925</v>
       </c>
       <c r="U84">
-        <v>0.1467309777667576</v>
+        <v>0.1344309777667576</v>
       </c>
       <c r="V84">
-        <v>0.165621731836215</v>
+        <v>0.1807755850285943</v>
       </c>
       <c r="W84">
-        <v>0.122429139115006</v>
+        <v>0.110129139115006</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.8281086591810751</v>
+        <v>0.9038779251429714</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8230,13 +8230,13 @@
         <v>0.8300000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1618873441008447</v>
+        <v>0.1509132247763173</v>
       </c>
       <c r="C85">
-        <v>-13429.86403188786</v>
+        <v>-10754.06798219868</v>
       </c>
       <c r="D85">
-        <v>25694.86475054398</v>
+        <v>28370.66080023317</v>
       </c>
       <c r="E85">
         <v>16155.65796022481</v>
@@ -8263,37 +8263,37 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M85">
-        <v>7354.586348779781</v>
+        <v>6738.074324755869</v>
       </c>
       <c r="N85">
-        <v>-1337.56798143284</v>
+        <v>-721.0559574089293</v>
       </c>
       <c r="O85">
-        <v>-267.5135962865681</v>
+        <v>-144.2111914817859</v>
       </c>
       <c r="P85">
-        <v>-1070.054385146272</v>
+        <v>-576.8447659271435</v>
       </c>
       <c r="Q85">
-        <v>3773.845614853727</v>
+        <v>4267.055234072856</v>
       </c>
       <c r="R85">
         <v>4.882352941176473</v>
       </c>
       <c r="S85">
-        <v>0.3531067073463073</v>
+        <v>0.3486060054373222</v>
       </c>
       <c r="T85">
-        <v>4.752650795686692</v>
+        <v>4.684312600265567</v>
       </c>
       <c r="U85">
-        <v>0.1467309777667576</v>
+        <v>0.1344309777667576</v>
       </c>
       <c r="V85">
-        <v>0.1636262892839715</v>
+        <v>0.1785975659318643</v>
       </c>
       <c r="W85">
-        <v>0.1227219323517741</v>
+        <v>0.1104219323517741</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.8181314464198575</v>
+        <v>0.8929878296593212</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8312,13 +8312,13 @@
         <v>0.84</v>
       </c>
       <c r="B86">
-        <v>0.1628966538785123</v>
+        <v>0.1517995345539848</v>
       </c>
       <c r="C86">
-        <v>-14255.23056686991</v>
+        <v>-11595.17854399784</v>
       </c>
       <c r="D86">
-        <v>25473.388923784</v>
+        <v>28133.44094665607</v>
       </c>
       <c r="E86">
         <v>16759.54866844688</v>
@@ -8345,37 +8345,37 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M86">
-        <v>7443.195822861465</v>
+        <v>6819.255943126422</v>
       </c>
       <c r="N86">
-        <v>-1426.177455514525</v>
+        <v>-802.2375757794816</v>
       </c>
       <c r="O86">
-        <v>-285.235491102905</v>
+        <v>-160.4475151558963</v>
       </c>
       <c r="P86">
-        <v>-1140.94196441162</v>
+        <v>-641.7900606235853</v>
       </c>
       <c r="Q86">
-        <v>3702.95803558838</v>
+        <v>4202.109939376414</v>
       </c>
       <c r="R86">
         <v>5.249999999999999</v>
       </c>
       <c r="S86">
-        <v>0.3723133765554513</v>
+        <v>0.3675313807771547</v>
       </c>
       <c r="T86">
-        <v>5.049691470417107</v>
+        <v>4.977082137782163</v>
       </c>
       <c r="U86">
-        <v>0.1467309777667576</v>
+        <v>0.1344309777667576</v>
       </c>
       <c r="V86">
-        <v>0.1616783572686861</v>
+        <v>0.1764714044326754</v>
       </c>
       <c r="W86">
-        <v>0.1230077543210001</v>
+        <v>0.1107077543210001</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.8083917863434306</v>
+        <v>0.882357022163377</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8394,13 +8394,13 @@
         <v>0.85</v>
       </c>
       <c r="B87">
-        <v>0.1931971756668634</v>
+        <v>0.1526858443316524</v>
       </c>
       <c r="C87">
-        <v>-20095.70041995127</v>
+        <v>-12432.35499689799</v>
       </c>
       <c r="D87">
-        <v>20236.80977892471</v>
+        <v>27900.15520197798</v>
       </c>
       <c r="E87">
         <v>17363.43937666895</v>
@@ -8427,45 +8427,45 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M87">
-        <v>9210.319520446394</v>
+        <v>6900.437561496974</v>
       </c>
       <c r="N87">
-        <v>-3193.301153099454</v>
+        <v>-883.4191941500339</v>
       </c>
       <c r="O87">
-        <v>-638.6602306198907</v>
+        <v>-176.6838388300068</v>
       </c>
       <c r="P87">
-        <v>-2554.640922479563</v>
+        <v>-706.7353553200271</v>
       </c>
       <c r="Q87">
-        <v>2289.259077520437</v>
+        <v>4137.164644679972</v>
       </c>
       <c r="R87">
         <v>5.666666666666666</v>
       </c>
       <c r="S87">
-        <v>0.4040556817303713</v>
+        <v>0.3889801394956317</v>
       </c>
       <c r="T87">
-        <v>5.540601978844466</v>
+        <v>5.308887613634307</v>
       </c>
       <c r="U87">
-        <v>0.1794309777667576</v>
+        <v>0.1344309777667576</v>
       </c>
       <c r="V87">
-        <v>0.1306581895229475</v>
+        <v>0.1743952702628792</v>
       </c>
       <c r="W87">
-        <v>0.1559868510674208</v>
+        <v>0.1109868510674208</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y87">
-        <v>0.6532909476147376</v>
+        <v>0.8719763513143961</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8476,13 +8476,13 @@
         <v>0.86</v>
       </c>
       <c r="B88">
-        <v>0.2409384928654342</v>
+        <v>0.15357215410932</v>
       </c>
       <c r="C88">
-        <v>-25650.59767001959</v>
+        <v>-13265.69440231202</v>
       </c>
       <c r="D88">
-        <v>15285.80323707846</v>
+        <v>27670.70650478603</v>
       </c>
       <c r="E88">
         <v>17967.33008489101</v>
@@ -8509,45 +8509,45 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M88">
-        <v>12029.66238803746</v>
+        <v>6981.619179867526</v>
       </c>
       <c r="N88">
-        <v>-6012.644020690517</v>
+        <v>-964.6008125205863</v>
       </c>
       <c r="O88">
-        <v>-1202.528804138103</v>
+        <v>-192.9201625041173</v>
       </c>
       <c r="P88">
-        <v>-4810.115216552414</v>
+        <v>-771.680650016469</v>
       </c>
       <c r="Q88">
-        <v>33.78478344758605</v>
+        <v>4072.219349983531</v>
       </c>
       <c r="R88">
         <v>6.142857142857142</v>
       </c>
       <c r="S88">
-        <v>0.4404525691461354</v>
+        <v>0.4134930066024625</v>
       </c>
       <c r="T88">
-        <v>6.103497912456859</v>
+        <v>5.688093871751043</v>
       </c>
       <c r="U88">
-        <v>0.2316309777667576</v>
+        <v>0.1344309777667576</v>
       </c>
       <c r="V88">
-        <v>0.1000363630043414</v>
+        <v>0.1723674182830783</v>
       </c>
       <c r="W88">
-        <v>0.2084594571918317</v>
+        <v>0.1112594571918317</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y88">
-        <v>0.5001818150217072</v>
+        <v>0.8618370914153916</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8558,13 +8558,13 @@
         <v>0.87</v>
       </c>
       <c r="B89">
-        <v>0.2427968026431018</v>
+        <v>0.1544584638869876</v>
       </c>
       <c r="C89">
-        <v>-26398.6823815648</v>
+        <v>-14095.29065479497</v>
       </c>
       <c r="D89">
-        <v>15141.60923375532</v>
+        <v>27445.00096052516</v>
       </c>
       <c r="E89">
         <v>18571.22079311309</v>
@@ -8591,45 +8591,45 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M89">
-        <v>12169.5421832472</v>
+        <v>7062.80079823808</v>
       </c>
       <c r="N89">
-        <v>-6152.523815900257</v>
+        <v>-1045.782430891139</v>
       </c>
       <c r="O89">
-        <v>-1230.504763180051</v>
+        <v>-209.1564861782279</v>
       </c>
       <c r="P89">
-        <v>-4922.019052720205</v>
+        <v>-836.6259447129116</v>
       </c>
       <c r="Q89">
-        <v>-78.11905272020522</v>
+        <v>4007.274055287088</v>
       </c>
       <c r="R89">
         <v>6.692307692307692</v>
       </c>
       <c r="S89">
-        <v>0.4708104590804535</v>
+        <v>0.4417770840334211</v>
       </c>
       <c r="T89">
-        <v>6.572997751876619</v>
+        <v>6.125639554193431</v>
       </c>
       <c r="U89">
-        <v>0.2316309777667576</v>
+        <v>0.1344309777667576</v>
       </c>
       <c r="V89">
-        <v>0.09888651975141798</v>
+        <v>0.1703861835901694</v>
       </c>
       <c r="W89">
-        <v>0.2087257965087849</v>
+        <v>0.1115257965087849</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y89">
-        <v>0.4944325987570898</v>
+        <v>0.8519309179508467</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8640,13 +8640,13 @@
         <v>0.88</v>
       </c>
       <c r="B90">
-        <v>0.2446551124207694</v>
+        <v>0.1553447736646552</v>
       </c>
       <c r="C90">
-        <v>-27144.07209449524</v>
+        <v>-14921.23461015663</v>
       </c>
       <c r="D90">
-        <v>15000.11022904696</v>
+        <v>27222.94771338556</v>
       </c>
       <c r="E90">
         <v>19175.11150133516</v>
@@ -8673,45 +8673,45 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M90">
-        <v>12309.42197845693</v>
+        <v>7143.982416608632</v>
       </c>
       <c r="N90">
-        <v>-6292.403611109994</v>
+        <v>-1126.964049261692</v>
       </c>
       <c r="O90">
-        <v>-1258.480722221999</v>
+        <v>-225.3928098523384</v>
       </c>
       <c r="P90">
-        <v>-5033.922888887995</v>
+        <v>-901.5712394093534</v>
       </c>
       <c r="Q90">
-        <v>-190.0228888879956</v>
+        <v>3942.328760590646</v>
       </c>
       <c r="R90">
         <v>7.333333333333334</v>
       </c>
       <c r="S90">
-        <v>0.5062279973371581</v>
+        <v>0.4747751743695396</v>
       </c>
       <c r="T90">
-        <v>7.120747564533005</v>
+        <v>6.636109517042884</v>
       </c>
       <c r="U90">
-        <v>0.2316309777667576</v>
+        <v>0.1344309777667576</v>
       </c>
       <c r="V90">
-        <v>0.09776280929969731</v>
+        <v>0.1684499769584629</v>
       </c>
       <c r="W90">
-        <v>0.2089860826594437</v>
+        <v>0.1117860826594436</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y90">
-        <v>0.4888140464984866</v>
+        <v>0.8422498847923144</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8722,13 +8722,13 @@
         <v>0.89</v>
       </c>
       <c r="B91">
-        <v>0.2465134221984369</v>
+        <v>0.1562310834423227</v>
       </c>
       <c r="C91">
-        <v>-27886.84166392854</v>
+        <v>-15743.61420740521</v>
       </c>
       <c r="D91">
-        <v>14861.23136783572</v>
+        <v>27004.45882435905</v>
       </c>
       <c r="E91">
         <v>19779.00220955723</v>
@@ -8755,45 +8755,45 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M91">
-        <v>12449.30177366667</v>
+        <v>7225.164034979184</v>
       </c>
       <c r="N91">
-        <v>-6432.283406319732</v>
+        <v>-1208.145667632244</v>
       </c>
       <c r="O91">
-        <v>-1286.456681263946</v>
+        <v>-241.6291335264488</v>
       </c>
       <c r="P91">
-        <v>-5145.826725055786</v>
+        <v>-966.5165341057952</v>
       </c>
       <c r="Q91">
-        <v>-301.9267250557859</v>
+        <v>3877.383465894204</v>
       </c>
       <c r="R91">
         <v>8.090909090909092</v>
       </c>
       <c r="S91">
-        <v>0.5480850880041724</v>
+        <v>0.5137729174940432</v>
       </c>
       <c r="T91">
-        <v>7.768088252217823</v>
+        <v>7.239392200410419</v>
       </c>
       <c r="U91">
-        <v>0.2316309777667576</v>
+        <v>0.1344309777667576</v>
       </c>
       <c r="V91">
-        <v>0.09666435076824004</v>
+        <v>0.1665572805881431</v>
       </c>
       <c r="W91">
-        <v>0.2092405196831213</v>
+        <v>0.1120405196831213</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y91">
-        <v>0.4833217538412002</v>
+        <v>0.8327864029407154</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8804,13 +8804,13 @@
         <v>0.9</v>
       </c>
       <c r="B92">
-        <v>0.2483717319761045</v>
+        <v>0.1571173932199903</v>
       </c>
       <c r="C92">
-        <v>-28627.06319822208</v>
+        <v>-16562.51458486514</v>
       </c>
       <c r="D92">
-        <v>14724.90054176426</v>
+        <v>26789.44915512119</v>
       </c>
       <c r="E92">
         <v>20382.8929177793</v>
@@ -8837,45 +8837,45 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M92">
-        <v>12589.18156887641</v>
+        <v>7306.345653349737</v>
       </c>
       <c r="N92">
-        <v>-6572.163201529471</v>
+        <v>-1289.327286002797</v>
       </c>
       <c r="O92">
-        <v>-1314.432640305894</v>
+        <v>-257.8654572005595</v>
       </c>
       <c r="P92">
-        <v>-5257.730561223577</v>
+        <v>-1031.461828802238</v>
       </c>
       <c r="Q92">
-        <v>-413.8305612235772</v>
+        <v>3812.438171197762</v>
       </c>
       <c r="R92">
         <v>9.000000000000002</v>
       </c>
       <c r="S92">
-        <v>0.5983135968045896</v>
+        <v>0.5605702092434475</v>
       </c>
       <c r="T92">
-        <v>8.544897077439606</v>
+        <v>7.963331420451461</v>
       </c>
       <c r="U92">
-        <v>0.2316309777667576</v>
+        <v>0.1344309777667576</v>
       </c>
       <c r="V92">
-        <v>0.0955903024263707</v>
+        <v>0.1647066441371637</v>
       </c>
       <c r="W92">
-        <v>0.2094893025507173</v>
+        <v>0.1122893025507173</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y92">
-        <v>0.4779515121318535</v>
+        <v>0.8235332206858185</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8886,13 +8886,13 @@
         <v>0.91</v>
       </c>
       <c r="B93">
-        <v>0.2502300417537721</v>
+        <v>0.1580037029976579</v>
       </c>
       <c r="C93">
-        <v>-29364.80618381589</v>
+        <v>-17378.01819079174</v>
       </c>
       <c r="D93">
-        <v>14591.04826439252</v>
+        <v>26577.83625741666</v>
       </c>
       <c r="E93">
         <v>20986.78362600137</v>
@@ -8919,45 +8919,45 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M93">
-        <v>12729.06136408615</v>
+        <v>7387.52727172029</v>
       </c>
       <c r="N93">
-        <v>-6712.042996739208</v>
+        <v>-1370.50890437335</v>
       </c>
       <c r="O93">
-        <v>-1342.408599347842</v>
+        <v>-274.1017808746699</v>
       </c>
       <c r="P93">
-        <v>-5369.634397391366</v>
+        <v>-1096.40712349868</v>
       </c>
       <c r="Q93">
-        <v>-525.7343973913667</v>
+        <v>3747.49287650132</v>
       </c>
       <c r="R93">
         <v>10.11111111111111</v>
       </c>
       <c r="S93">
-        <v>0.6597039964495442</v>
+        <v>0.6177668991593863</v>
       </c>
       <c r="T93">
-        <v>9.494330086044009</v>
+        <v>8.848146022723849</v>
       </c>
       <c r="U93">
-        <v>0.2316309777667576</v>
+        <v>0.1344309777667576</v>
       </c>
       <c r="V93">
-        <v>0.09453985954256444</v>
+        <v>0.1628966810147773</v>
       </c>
       <c r="W93">
-        <v>0.2097326176629815</v>
+        <v>0.1125326176629814</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y93">
-        <v>0.4726992977128222</v>
+        <v>0.8144834050738865</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8968,13 +8968,13 @@
         <v>0.92</v>
       </c>
       <c r="B94">
-        <v>0.2520883515314397</v>
+        <v>0.1588900127753254</v>
       </c>
       <c r="C94">
-        <v>-30100.137603328</v>
+        <v>-18190.20488878432</v>
       </c>
       <c r="D94">
-        <v>14459.60755310248</v>
+        <v>26369.54026764616</v>
       </c>
       <c r="E94">
         <v>21590.67433422344</v>
@@ -9001,45 +9001,45 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M94">
-        <v>12868.94115929589</v>
+        <v>7468.708890090842</v>
       </c>
       <c r="N94">
-        <v>-6851.922791948946</v>
+        <v>-1451.690522743902</v>
       </c>
       <c r="O94">
-        <v>-1370.384558389789</v>
+        <v>-290.3381045487804</v>
       </c>
       <c r="P94">
-        <v>-5481.538233559157</v>
+        <v>-1161.352418195122</v>
       </c>
       <c r="Q94">
-        <v>-637.638233559157</v>
+        <v>3682.547581804878</v>
       </c>
       <c r="R94">
         <v>11.50000000000001</v>
       </c>
       <c r="S94">
-        <v>0.7364419960057375</v>
+        <v>0.6892627615543098</v>
       </c>
       <c r="T94">
-        <v>10.68112134679951</v>
+        <v>9.954164275564333</v>
       </c>
       <c r="U94">
-        <v>0.2316309777667576</v>
+        <v>0.1344309777667576</v>
       </c>
       <c r="V94">
-        <v>0.09351225237362353</v>
+        <v>0.1611260649167906</v>
       </c>
       <c r="W94">
-        <v>0.2099706433162834</v>
+        <v>0.1127706433162834</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y94">
-        <v>0.4675612618681175</v>
+        <v>0.8056303245839529</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9050,13 +9050,13 @@
         <v>0.93</v>
       </c>
       <c r="B95">
-        <v>0.2539466613091073</v>
+        <v>0.1875557593128538</v>
       </c>
       <c r="C95">
-        <v>-30833.12204732353</v>
+        <v>-24126.52484917682</v>
       </c>
       <c r="D95">
-        <v>14330.51381732902</v>
+        <v>21037.11101547573</v>
       </c>
       <c r="E95">
         <v>22194.56504244552</v>
@@ -9083,45 +9083,45 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M95">
-        <v>13008.82095450563</v>
+        <v>9133.654279844597</v>
       </c>
       <c r="N95">
-        <v>-6991.802587158685</v>
+        <v>-3116.635912497657</v>
       </c>
       <c r="O95">
-        <v>-1398.360517431737</v>
+        <v>-623.3271824995314</v>
       </c>
       <c r="P95">
-        <v>-5593.442069726948</v>
+        <v>-2493.308729998126</v>
       </c>
       <c r="Q95">
-        <v>-749.5420697269483</v>
+        <v>2350.591270001874</v>
       </c>
       <c r="R95">
         <v>13.2857142857143</v>
       </c>
       <c r="S95">
-        <v>0.8351051382922714</v>
+        <v>0.8033779669172215</v>
       </c>
       <c r="T95">
-        <v>12.20699582491373</v>
+        <v>11.71949020954429</v>
       </c>
       <c r="U95">
-        <v>0.2316309777667576</v>
+        <v>0.1626309777667576</v>
       </c>
       <c r="V95">
-        <v>0.09250674428358455</v>
+        <v>0.1317548964082165</v>
       </c>
       <c r="W95">
-        <v>0.2102035501383315</v>
+        <v>0.1412035501383315</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y95">
-        <v>0.4625337214179227</v>
+        <v>0.6587744820410824</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9132,13 +9132,13 @@
         <v>0.9400000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2558049710867748</v>
+        <v>0.1887240690905213</v>
       </c>
       <c r="C96">
-        <v>-31563.82182014978</v>
+        <v>-24902.38003230963</v>
       </c>
       <c r="D96">
-        <v>14203.70475272484</v>
+        <v>20865.14654056499</v>
       </c>
       <c r="E96">
         <v>22798.45575066758</v>
@@ -9165,45 +9165,45 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M96">
-        <v>13148.70074971536</v>
+        <v>9231.865616187013</v>
       </c>
       <c r="N96">
-        <v>-7131.682382368421</v>
+        <v>-3214.847248840073</v>
       </c>
       <c r="O96">
-        <v>-1426.336476473684</v>
+        <v>-642.9694497680147</v>
       </c>
       <c r="P96">
-        <v>-5705.345905894736</v>
+        <v>-2571.877799072058</v>
       </c>
       <c r="Q96">
-        <v>-861.4459058947368</v>
+        <v>2272.022200927941</v>
       </c>
       <c r="R96">
         <v>15.66666666666668</v>
       </c>
       <c r="S96">
-        <v>0.966655994674317</v>
+        <v>0.9296409614034254</v>
       </c>
       <c r="T96">
-        <v>14.24149512906602</v>
+        <v>13.67273857780168</v>
       </c>
       <c r="U96">
-        <v>0.2316309777667576</v>
+        <v>0.1626309777667576</v>
       </c>
       <c r="V96">
-        <v>0.09152262998269536</v>
+        <v>0.1303532485740865</v>
       </c>
       <c r="W96">
-        <v>0.2104315014960807</v>
+        <v>0.1414315014960807</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y96">
-        <v>0.4576131499134768</v>
+        <v>0.6517662428704325</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9214,13 +9214,13 @@
         <v>0.9500000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2576632808644425</v>
+        <v>0.2430383165143261</v>
       </c>
       <c r="C97">
-        <v>-32292.29704020135</v>
+        <v>-31251.98360082108</v>
       </c>
       <c r="D97">
-        <v>14079.12024089534</v>
+        <v>15119.43368027561</v>
       </c>
       <c r="E97">
         <v>23402.34645888965</v>
@@ -9247,37 +9247,37 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M97">
-        <v>13288.5805449251</v>
+        <v>12428.03628570865</v>
       </c>
       <c r="N97">
-        <v>-7271.562177578158</v>
+        <v>-6411.017918361707</v>
       </c>
       <c r="O97">
-        <v>-1454.312435515632</v>
+        <v>-1282.203583672342</v>
       </c>
       <c r="P97">
-        <v>-5817.249742062527</v>
+        <v>-5128.814334689366</v>
       </c>
       <c r="Q97">
-        <v>-973.3497420625272</v>
+        <v>-284.9143346893661</v>
       </c>
       <c r="R97">
         <v>19.00000000000003</v>
       </c>
       <c r="S97">
-        <v>1.150827193609181</v>
+        <v>1.143327906606855</v>
       </c>
       <c r="T97">
-        <v>17.08979415487924</v>
+        <v>16.97840765950645</v>
       </c>
       <c r="U97">
-        <v>0.2316309777667576</v>
+        <v>0.2166309777667576</v>
       </c>
       <c r="V97">
-        <v>0.09055923387761436</v>
+        <v>0.09682975216713974</v>
       </c>
       <c r="W97">
-        <v>0.2106546538778773</v>
+        <v>0.1956546538778773</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.4527961693880718</v>
+        <v>0.4841487608356986</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9296,13 +9296,13 @@
         <v>0.96</v>
       </c>
       <c r="B98">
-        <v>0.2595215906421099</v>
+        <v>0.2447466262919937</v>
       </c>
       <c r="C98">
-        <v>-33018.60573495443</v>
+        <v>-31985.70147359584</v>
       </c>
       <c r="D98">
-        <v>13956.70225436433</v>
+        <v>14989.60651572292</v>
       </c>
       <c r="E98">
         <v>24006.23716711172</v>
@@ -9329,37 +9329,37 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M98">
-        <v>13428.46034013484</v>
+        <v>12558.85772029505</v>
       </c>
       <c r="N98">
-        <v>-7411.441972787896</v>
+        <v>-6541.839352948115</v>
       </c>
       <c r="O98">
-        <v>-1482.288394557579</v>
+        <v>-1308.367870589623</v>
       </c>
       <c r="P98">
-        <v>-5929.153578230316</v>
+        <v>-5233.471482358492</v>
       </c>
       <c r="Q98">
-        <v>-1085.253578230317</v>
+        <v>-389.5714823584922</v>
       </c>
       <c r="R98">
         <v>23.99999999999998</v>
       </c>
       <c r="S98">
-        <v>1.427083992011473</v>
+        <v>1.417709883258566</v>
       </c>
       <c r="T98">
-        <v>21.36224269359899</v>
+        <v>21.22300957438302</v>
       </c>
       <c r="U98">
-        <v>0.2316309777667576</v>
+        <v>0.2166309777667576</v>
       </c>
       <c r="V98">
-        <v>0.08961590852472255</v>
+        <v>0.09582110891539869</v>
       </c>
       <c r="W98">
-        <v>0.2108731572517198</v>
+        <v>0.1958731572517198</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.4480795426236127</v>
+        <v>0.4791055445769934</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9378,13 +9378,13 @@
         <v>0.97</v>
       </c>
       <c r="B99">
-        <v>0.2613799004197775</v>
+        <v>0.2464549360696613</v>
       </c>
       <c r="C99">
-        <v>-33742.80393108598</v>
+        <v>-32717.20873526919</v>
       </c>
       <c r="D99">
-        <v>13836.39476645484</v>
+        <v>14861.98996227163</v>
       </c>
       <c r="E99">
         <v>24610.12787533379</v>
@@ -9411,37 +9411,37 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M99">
-        <v>13568.34013534457</v>
+        <v>12689.67915488146</v>
       </c>
       <c r="N99">
-        <v>-7551.321767997633</v>
+        <v>-6672.660787534522</v>
       </c>
       <c r="O99">
-        <v>-1510.264353599527</v>
+        <v>-1334.532157506904</v>
       </c>
       <c r="P99">
-        <v>-6041.057414398107</v>
+        <v>-5338.128630027617</v>
       </c>
       <c r="Q99">
-        <v>-1197.157414398107</v>
+        <v>-494.2286300276173</v>
       </c>
       <c r="R99">
         <v>32.33333333333331</v>
       </c>
       <c r="S99">
-        <v>1.887511989348631</v>
+        <v>1.875013177678089</v>
       </c>
       <c r="T99">
-        <v>28.48299025813199</v>
+        <v>28.29734609917736</v>
       </c>
       <c r="U99">
-        <v>0.2316309777667576</v>
+        <v>0.2166309777667576</v>
       </c>
       <c r="V99">
-        <v>0.08869203317910684</v>
+        <v>0.09483326243173479</v>
       </c>
       <c r="W99">
-        <v>0.2110871554013594</v>
+        <v>0.1960871554013594</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.4434601658955343</v>
+        <v>0.4741663121586739</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9460,13 +9460,13 @@
         <v>0.98</v>
       </c>
       <c r="B100">
-        <v>0.2632382101974451</v>
+        <v>0.2481632458473288</v>
       </c>
       <c r="C100">
-        <v>-34464.94573997166</v>
+        <v>-33446.56137044267</v>
       </c>
       <c r="D100">
-        <v>13718.14366579124</v>
+        <v>14736.52803532023</v>
       </c>
       <c r="E100">
         <v>25214.01858355586</v>
@@ -9493,37 +9493,37 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M100">
-        <v>13708.21993055431</v>
+        <v>12820.50058946787</v>
       </c>
       <c r="N100">
-        <v>-7691.201563207371</v>
+        <v>-6803.482222120927</v>
       </c>
       <c r="O100">
-        <v>-1538.240312641474</v>
+        <v>-1360.696444424186</v>
       </c>
       <c r="P100">
-        <v>-6152.961250565897</v>
+        <v>-5442.785777696741</v>
       </c>
       <c r="Q100">
-        <v>-1309.061250565897</v>
+        <v>-598.8857776967416</v>
       </c>
       <c r="R100">
         <v>48.99999999999996</v>
       </c>
       <c r="S100">
-        <v>2.808367984022946</v>
+        <v>2.789619766517132</v>
       </c>
       <c r="T100">
-        <v>42.72448538719799</v>
+        <v>42.44601914876603</v>
       </c>
       <c r="U100">
-        <v>0.2316309777667576</v>
+        <v>0.2166309777667576</v>
       </c>
       <c r="V100">
-        <v>0.08778701243238128</v>
+        <v>0.09386557608039056</v>
       </c>
       <c r="W100">
-        <v>0.2112967862418226</v>
+        <v>0.1962967862418226</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9531,7 +9531,7 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.4389350621619064</v>
+        <v>0.4693278804019527</v>
       </c>
       <c r="Z100">
         <v>0</v>
@@ -9542,13 +9542,13 @@
         <v>0.99</v>
       </c>
       <c r="B101">
-        <v>0.2650965199751127</v>
+        <v>0.2498715556249964</v>
       </c>
       <c r="C101">
-        <v>-35185.08343883673</v>
+        <v>-34173.81348909996</v>
       </c>
       <c r="D101">
-        <v>13601.89667514824</v>
+        <v>14613.16662488501</v>
       </c>
       <c r="E101">
         <v>25817.90929177793</v>
@@ -9575,37 +9575,37 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M101">
-        <v>13848.09972576405</v>
+        <v>12951.32202405428</v>
       </c>
       <c r="N101">
-        <v>-7831.08135841711</v>
+        <v>-6934.303656707336</v>
       </c>
       <c r="O101">
-        <v>-1566.216271683422</v>
+        <v>-1386.860731341467</v>
       </c>
       <c r="P101">
-        <v>-6264.865086733688</v>
+        <v>-5547.442925365869</v>
       </c>
       <c r="Q101">
-        <v>-1420.965086733689</v>
+        <v>-703.5429253658695</v>
       </c>
       <c r="R101">
         <v>98.99999999999991</v>
       </c>
       <c r="S101">
-        <v>5.570935968045892</v>
+        <v>5.533439533034263</v>
       </c>
       <c r="T101">
-        <v>85.44897077439597</v>
+        <v>84.89203829753205</v>
       </c>
       <c r="U101">
-        <v>0.2316309777667576</v>
+        <v>0.2166309777667576</v>
       </c>
       <c r="V101">
-        <v>0.08690027493306429</v>
+        <v>0.09291743894826539</v>
       </c>
       <c r="W101">
-        <v>0.2115021821158118</v>
+        <v>0.1965021821158118</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
@@ -9613,7 +9613,7 @@
         </is>
       </c>
       <c r="Y101">
-        <v>0.4345013746653213</v>
+        <v>0.4645871947413269</v>
       </c>
       <c r="Z101">
         <v>0</v>

--- a/research/traditional_assets/database/data/thailand/thailand_oil_gas_integrated.xlsx
+++ b/research/traditional_assets/database/data/thailand/thailand_oil_gas_integrated.xlsx
@@ -1284,7 +1284,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1421,22 +1421,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1062357776319679</v>
+        <v>0.1061859538988381</v>
       </c>
       <c r="C2">
-        <v>60342.0119371553</v>
+        <v>59778.83422191975</v>
       </c>
       <c r="D2">
-        <v>49343.8119371553</v>
+        <v>49384.52493014182</v>
       </c>
       <c r="E2">
-        <v>-33967.27082220704</v>
+        <v>-33363.38011398497</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>603.8907082220704</v>
       </c>
       <c r="G2">
         <v>10998.2</v>
@@ -1457,28 +1457,28 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>39.93588299898523</v>
       </c>
       <c r="N2">
-        <v>6017.01836734694</v>
+        <v>5977.082484347955</v>
       </c>
       <c r="O2">
-        <v>1203.403673469388</v>
+        <v>1195.416496869591</v>
       </c>
       <c r="P2">
-        <v>4813.614693877552</v>
+        <v>4781.665987478364</v>
       </c>
       <c r="Q2">
-        <v>9657.514693877551</v>
+        <v>9625.565987478363</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1062357776319679</v>
+        <v>0.1067241475522263</v>
       </c>
       <c r="T2">
-        <v>0.9349222590860211</v>
+        <v>0.9424771864321708</v>
       </c>
       <c r="U2">
         <v>0.06613097776675758</v>
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>150.6669670356314</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1503,22 +1503,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1061859538988381</v>
+        <v>0.1061361301657082</v>
       </c>
       <c r="C3">
-        <v>59778.83422191975</v>
+        <v>59215.723745776</v>
       </c>
       <c r="D3">
-        <v>49384.52493014182</v>
+        <v>49425.30516222015</v>
       </c>
       <c r="E3">
-        <v>-33363.38011398497</v>
+        <v>-32759.4894057629</v>
       </c>
       <c r="F3">
-        <v>603.8907082220704</v>
+        <v>1207.781416444141</v>
       </c>
       <c r="G3">
         <v>10998.2</v>
@@ -1539,28 +1539,28 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M3">
-        <v>39.93588299898523</v>
+        <v>79.87176599797046</v>
       </c>
       <c r="N3">
-        <v>5977.082484347955</v>
+        <v>5937.14660134897</v>
       </c>
       <c r="O3">
-        <v>1195.416496869591</v>
+        <v>1187.429320269794</v>
       </c>
       <c r="P3">
-        <v>4781.665987478364</v>
+        <v>4749.717281079176</v>
       </c>
       <c r="Q3">
-        <v>9625.565987478363</v>
+        <v>9593.617281079176</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1067241475522263</v>
+        <v>0.1072224842055511</v>
       </c>
       <c r="T3">
-        <v>0.9424771864321708</v>
+        <v>0.9501862959690581</v>
       </c>
       <c r="U3">
         <v>0.06613097776675758</v>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>150.6669670356314</v>
+        <v>75.33348351781571</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1585,22 +1585,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1061361301657082</v>
+        <v>0.1060863064325783</v>
       </c>
       <c r="C4">
-        <v>59215.723745776</v>
+        <v>58652.68067543369</v>
       </c>
       <c r="D4">
-        <v>49425.30516222015</v>
+        <v>49466.15280009991</v>
       </c>
       <c r="E4">
-        <v>-32759.4894057629</v>
+        <v>-32155.59869754082</v>
       </c>
       <c r="F4">
-        <v>1207.781416444141</v>
+        <v>1811.672124666211</v>
       </c>
       <c r="G4">
         <v>10998.2</v>
@@ -1621,28 +1621,28 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M4">
-        <v>79.87176599797046</v>
+        <v>119.8076489969557</v>
       </c>
       <c r="N4">
-        <v>5937.14660134897</v>
+        <v>5897.210718349985</v>
       </c>
       <c r="O4">
-        <v>1187.429320269794</v>
+        <v>1179.442143669997</v>
       </c>
       <c r="P4">
-        <v>4749.717281079176</v>
+        <v>4717.768574679988</v>
       </c>
       <c r="Q4">
-        <v>9593.617281079176</v>
+        <v>9561.668574679989</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1072224842055511</v>
+        <v>0.1077310958414187</v>
       </c>
       <c r="T4">
-        <v>0.9501862959690581</v>
+        <v>0.9580543562180462</v>
       </c>
       <c r="U4">
         <v>0.06613097776675758</v>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>75.33348351781571</v>
+        <v>50.22232234521047</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1667,22 +1667,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1060863064325783</v>
+        <v>0.1060364826994484</v>
       </c>
       <c r="C5">
-        <v>58652.68067543369</v>
+        <v>58089.70517815397</v>
       </c>
       <c r="D5">
-        <v>49466.15280009991</v>
+        <v>49507.06801104225</v>
       </c>
       <c r="E5">
-        <v>-32155.59869754082</v>
+        <v>-31551.70798931875</v>
       </c>
       <c r="F5">
-        <v>1811.672124666211</v>
+        <v>2415.562832888282</v>
       </c>
       <c r="G5">
         <v>10998.2</v>
@@ -1703,28 +1703,28 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M5">
-        <v>119.8076489969557</v>
+        <v>159.7435319959409</v>
       </c>
       <c r="N5">
-        <v>5897.210718349985</v>
+        <v>5857.274835350999</v>
       </c>
       <c r="O5">
-        <v>1179.442143669997</v>
+        <v>1171.4549670702</v>
       </c>
       <c r="P5">
-        <v>4717.768574679988</v>
+        <v>4685.819868280799</v>
       </c>
       <c r="Q5">
-        <v>9561.668574679989</v>
+        <v>9529.719868280798</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1077310958414187</v>
+        <v>0.1082503035530335</v>
       </c>
       <c r="T5">
-        <v>0.9580543562180462</v>
+        <v>0.9660863343888886</v>
       </c>
       <c r="U5">
         <v>0.06613097776675758</v>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>50.22232234521047</v>
+        <v>37.66674175890785</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1749,22 +1749,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1060364826994484</v>
+        <v>0.1059866589663185</v>
       </c>
       <c r="C6">
-        <v>58089.70517815397</v>
+        <v>57526.79742175193</v>
       </c>
       <c r="D6">
-        <v>49507.06801104225</v>
+        <v>49548.05096286227</v>
       </c>
       <c r="E6">
-        <v>-31551.70798931875</v>
+        <v>-30947.81728109668</v>
       </c>
       <c r="F6">
-        <v>2415.562832888282</v>
+        <v>3019.453541110352</v>
       </c>
       <c r="G6">
         <v>10998.2</v>
@@ -1785,28 +1785,28 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M6">
-        <v>159.7435319959409</v>
+        <v>199.6794149949261</v>
       </c>
       <c r="N6">
-        <v>5857.274835350999</v>
+        <v>5817.338952352014</v>
       </c>
       <c r="O6">
-        <v>1171.4549670702</v>
+        <v>1163.467790470403</v>
       </c>
       <c r="P6">
-        <v>4685.819868280799</v>
+        <v>4653.871161881611</v>
       </c>
       <c r="Q6">
-        <v>9529.719868280798</v>
+        <v>9497.77116188161</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1082503035530335</v>
+        <v>0.1087804419533139</v>
       </c>
       <c r="T6">
-        <v>0.9660863343888886</v>
+        <v>0.9742874068370114</v>
       </c>
       <c r="U6">
         <v>0.06613097776675758</v>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>37.66674175890785</v>
+        <v>30.13339340712628</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1831,22 +1831,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1059866589663185</v>
+        <v>0.1059368352331887</v>
       </c>
       <c r="C7">
-        <v>57526.79742175193</v>
+        <v>56963.95757459871</v>
       </c>
       <c r="D7">
-        <v>49548.05096286227</v>
+        <v>49589.10182393114</v>
       </c>
       <c r="E7">
-        <v>-30947.81728109668</v>
+        <v>-30343.92657287461</v>
       </c>
       <c r="F7">
-        <v>3019.453541110352</v>
+        <v>3623.344249332423</v>
       </c>
       <c r="G7">
         <v>10998.2</v>
@@ -1867,28 +1867,28 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M7">
-        <v>199.6794149949261</v>
+        <v>239.6152979939114</v>
       </c>
       <c r="N7">
-        <v>5817.338952352014</v>
+        <v>5777.403069353029</v>
       </c>
       <c r="O7">
-        <v>1163.467790470403</v>
+        <v>1155.480613870606</v>
       </c>
       <c r="P7">
-        <v>4653.871161881611</v>
+        <v>4621.922455482423</v>
       </c>
       <c r="Q7">
-        <v>9497.77116188161</v>
+        <v>9465.822455482423</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1087804419533139</v>
+        <v>0.1093218598940259</v>
       </c>
       <c r="T7">
-        <v>0.9742874068370114</v>
+        <v>0.9826629701882861</v>
       </c>
       <c r="U7">
         <v>0.06613097776675758</v>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>30.13339340712628</v>
+        <v>25.11116117260523</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1913,22 +1913,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1059368352331887</v>
+        <v>0.1058870115000588</v>
       </c>
       <c r="C8">
-        <v>56963.95757459871</v>
+        <v>56401.18580562399</v>
       </c>
       <c r="D8">
-        <v>49589.10182393114</v>
+        <v>49630.22076317848</v>
       </c>
       <c r="E8">
-        <v>-30343.92657287461</v>
+        <v>-29740.03586465254</v>
       </c>
       <c r="F8">
-        <v>3623.344249332422</v>
+        <v>4227.234957554492</v>
       </c>
       <c r="G8">
         <v>10998.2</v>
@@ -1949,28 +1949,28 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M8">
-        <v>239.6152979939114</v>
+        <v>279.5511809928965</v>
       </c>
       <c r="N8">
-        <v>5777.403069353029</v>
+        <v>5737.467186354043</v>
       </c>
       <c r="O8">
-        <v>1155.480613870606</v>
+        <v>1147.493437270809</v>
       </c>
       <c r="P8">
-        <v>4621.922455482423</v>
+        <v>4589.973749083235</v>
       </c>
       <c r="Q8">
-        <v>9465.822455482423</v>
+        <v>9433.873749083235</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1093218598940259</v>
+        <v>0.1098749212313122</v>
       </c>
       <c r="T8">
-        <v>0.9826629701882861</v>
+        <v>0.9912186531815236</v>
       </c>
       <c r="U8">
         <v>0.06613097776675758</v>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>25.11116117260524</v>
+        <v>21.52385243366163</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1995,22 +1995,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1058870115000588</v>
+        <v>0.1058371877669289</v>
       </c>
       <c r="C9">
-        <v>56401.185805624</v>
+        <v>55838.48228431815</v>
       </c>
       <c r="D9">
-        <v>49630.22076317849</v>
+        <v>49671.40795009471</v>
       </c>
       <c r="E9">
-        <v>-29740.03586465254</v>
+        <v>-29136.14515643047</v>
       </c>
       <c r="F9">
-        <v>4227.234957554493</v>
+        <v>4831.125665776563</v>
       </c>
       <c r="G9">
         <v>10998.2</v>
@@ -2031,28 +2031,28 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M9">
-        <v>279.5511809928966</v>
+        <v>319.4870639918818</v>
       </c>
       <c r="N9">
-        <v>5737.467186354043</v>
+        <v>5697.531303355058</v>
       </c>
       <c r="O9">
-        <v>1147.493437270809</v>
+        <v>1139.506260671012</v>
       </c>
       <c r="P9">
-        <v>4589.973749083235</v>
+        <v>4558.025042684047</v>
       </c>
       <c r="Q9">
-        <v>9433.873749083235</v>
+        <v>9401.925042684046</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1098749212313122</v>
+        <v>0.1104400056411483</v>
       </c>
       <c r="T9">
-        <v>0.9912186531815236</v>
+        <v>0.9999603292833096</v>
       </c>
       <c r="U9">
         <v>0.06613097776675758</v>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>21.52385243366163</v>
+        <v>18.83337087945393</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2077,22 +2077,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1058371877669289</v>
+        <v>0.105787364033799</v>
       </c>
       <c r="C10">
-        <v>55838.48228431815</v>
+        <v>55275.84718073471</v>
       </c>
       <c r="D10">
-        <v>49671.40795009471</v>
+        <v>49712.66355473334</v>
       </c>
       <c r="E10">
-        <v>-29136.14515643047</v>
+        <v>-28532.2544482084</v>
       </c>
       <c r="F10">
-        <v>4831.125665776563</v>
+        <v>5435.016373998633</v>
       </c>
       <c r="G10">
         <v>10998.2</v>
@@ -2113,28 +2113,28 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M10">
-        <v>319.4870639918818</v>
+        <v>359.422946990867</v>
       </c>
       <c r="N10">
-        <v>5697.531303355058</v>
+        <v>5657.595420356073</v>
       </c>
       <c r="O10">
-        <v>1139.506260671012</v>
+        <v>1131.519084071215</v>
       </c>
       <c r="P10">
-        <v>4558.025042684047</v>
+        <v>4526.076336284858</v>
       </c>
       <c r="Q10">
-        <v>9401.925042684046</v>
+        <v>9369.976336284857</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1104400056411483</v>
+        <v>0.1110175094885632</v>
       </c>
       <c r="T10">
-        <v>0.9999603292833096</v>
+        <v>1.008894130134585</v>
       </c>
       <c r="U10">
         <v>0.06613097776675758</v>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>18.83337087945393</v>
+        <v>16.74077411507016</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.105787364033799</v>
+        <v>0.1057375403006692</v>
       </c>
       <c r="C11">
-        <v>55275.84718073471</v>
+        <v>54713.28066549255</v>
       </c>
       <c r="D11">
-        <v>49712.66355473334</v>
+        <v>49753.98774771325</v>
       </c>
       <c r="E11">
-        <v>-28532.2544482084</v>
+        <v>-27928.36373998633</v>
       </c>
       <c r="F11">
-        <v>5435.016373998633</v>
+        <v>6038.907082220703</v>
       </c>
       <c r="G11">
         <v>10998.2</v>
@@ -2195,28 +2195,28 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M11">
-        <v>359.422946990867</v>
+        <v>399.3588299898522</v>
       </c>
       <c r="N11">
-        <v>5657.595420356073</v>
+        <v>5617.659537357088</v>
       </c>
       <c r="O11">
-        <v>1131.519084071215</v>
+        <v>1123.531907471418</v>
       </c>
       <c r="P11">
-        <v>4526.076336284858</v>
+        <v>4494.12762988567</v>
       </c>
       <c r="Q11">
-        <v>9369.976336284857</v>
+        <v>9338.02762988567</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1110175094885632</v>
+        <v>0.1116078467548095</v>
       </c>
       <c r="T11">
-        <v>1.008894130134585</v>
+        <v>1.018026459893667</v>
       </c>
       <c r="U11">
         <v>0.06613097776675758</v>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>16.74077411507016</v>
+        <v>15.06669670356314</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2241,22 +2241,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1057375403006692</v>
+        <v>0.1056877165675393</v>
       </c>
       <c r="C12">
-        <v>54713.28066549253</v>
+        <v>54150.78290977842</v>
       </c>
       <c r="D12">
-        <v>49753.98774771324</v>
+        <v>49795.38070022119</v>
       </c>
       <c r="E12">
-        <v>-27928.36373998633</v>
+        <v>-27324.47303176426</v>
       </c>
       <c r="F12">
-        <v>6038.907082220704</v>
+        <v>6642.797790442774</v>
       </c>
       <c r="G12">
         <v>10998.2</v>
@@ -2277,28 +2277,28 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M12">
-        <v>399.3588299898523</v>
+        <v>439.2947129888375</v>
       </c>
       <c r="N12">
-        <v>5617.659537357088</v>
+        <v>5577.723654358103</v>
       </c>
       <c r="O12">
-        <v>1123.531907471418</v>
+        <v>1115.544730871621</v>
       </c>
       <c r="P12">
-        <v>4494.12762988567</v>
+        <v>4462.178923486483</v>
       </c>
       <c r="Q12">
-        <v>9338.02762988567</v>
+        <v>9306.078923486482</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1116078467548095</v>
+        <v>0.1122114500270389</v>
       </c>
       <c r="T12">
-        <v>1.018026459893667</v>
+        <v>1.027364010546212</v>
       </c>
       <c r="U12">
         <v>0.06613097776675758</v>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>15.06669670356314</v>
+        <v>13.69699700323922</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2323,22 +2323,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1056877165675393</v>
+        <v>0.1056378928344094</v>
       </c>
       <c r="C13">
-        <v>54150.78290977842</v>
+        <v>53588.35408534915</v>
       </c>
       <c r="D13">
-        <v>49795.38070022119</v>
+        <v>49836.842584014</v>
       </c>
       <c r="E13">
-        <v>-27324.47303176426</v>
+        <v>-26720.58232354219</v>
       </c>
       <c r="F13">
-        <v>6642.797790442774</v>
+        <v>7246.688498664845</v>
       </c>
       <c r="G13">
         <v>10998.2</v>
@@ -2359,28 +2359,28 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M13">
-        <v>439.2947129888375</v>
+        <v>479.2305959878227</v>
       </c>
       <c r="N13">
-        <v>5577.723654358103</v>
+        <v>5537.787771359117</v>
       </c>
       <c r="O13">
-        <v>1115.544730871621</v>
+        <v>1107.557554271823</v>
       </c>
       <c r="P13">
-        <v>4462.178923486483</v>
+        <v>4430.230217087294</v>
       </c>
       <c r="Q13">
-        <v>9306.078923486482</v>
+        <v>9274.130217087293</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1122114500270389</v>
+        <v>0.1128287715554553</v>
       </c>
       <c r="T13">
-        <v>1.027364010546212</v>
+        <v>1.036913778259042</v>
       </c>
       <c r="U13">
         <v>0.06613097776675758</v>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>13.69699700323922</v>
+        <v>12.55558058630262</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2405,22 +2405,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1056378928344094</v>
+        <v>0.1055880691012795</v>
       </c>
       <c r="C14">
-        <v>53588.35408534915</v>
+        <v>53025.99436453422</v>
       </c>
       <c r="D14">
-        <v>49836.842584014</v>
+        <v>49878.37357142114</v>
       </c>
       <c r="E14">
-        <v>-26720.58232354219</v>
+        <v>-26116.69161532012</v>
       </c>
       <c r="F14">
-        <v>7246.688498664845</v>
+        <v>7850.579206886915</v>
       </c>
       <c r="G14">
         <v>10998.2</v>
@@ -2441,28 +2441,28 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M14">
-        <v>479.2305959878227</v>
+        <v>519.166478986808</v>
       </c>
       <c r="N14">
-        <v>5537.787771359117</v>
+        <v>5497.851888360132</v>
       </c>
       <c r="O14">
-        <v>1107.557554271823</v>
+        <v>1099.570377672026</v>
       </c>
       <c r="P14">
-        <v>4430.230217087294</v>
+        <v>4398.281510688105</v>
       </c>
       <c r="Q14">
-        <v>9274.130217087293</v>
+        <v>9242.181510688104</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1128287715554553</v>
+        <v>0.1134602843833756</v>
       </c>
       <c r="T14">
-        <v>1.036913778259042</v>
+        <v>1.046683080861821</v>
       </c>
       <c r="U14">
         <v>0.06613097776675758</v>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>12.55558058630262</v>
+        <v>11.58976669504857</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2487,22 +2487,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1055880691012795</v>
+        <v>0.1055382453681497</v>
       </c>
       <c r="C15">
-        <v>53025.99436453422</v>
+        <v>52463.70392023788</v>
       </c>
       <c r="D15">
-        <v>49878.37357142114</v>
+        <v>49919.97383534686</v>
       </c>
       <c r="E15">
-        <v>-26116.69161532012</v>
+        <v>-25512.80090709805</v>
       </c>
       <c r="F15">
-        <v>7850.579206886915</v>
+        <v>8454.469915108986</v>
       </c>
       <c r="G15">
         <v>10998.2</v>
@@ -2523,28 +2523,28 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M15">
-        <v>519.166478986808</v>
+        <v>559.1023619857932</v>
       </c>
       <c r="N15">
-        <v>5497.851888360132</v>
+        <v>5457.916005361147</v>
       </c>
       <c r="O15">
-        <v>1099.570377672026</v>
+        <v>1091.583201072229</v>
       </c>
       <c r="P15">
-        <v>4398.281510688105</v>
+        <v>4366.332804288917</v>
       </c>
       <c r="Q15">
-        <v>9242.181510688104</v>
+        <v>9210.232804288917</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1134602843833756</v>
+        <v>0.1141064835561312</v>
       </c>
       <c r="T15">
-        <v>1.046683080861821</v>
+        <v>1.056679576548387</v>
       </c>
       <c r="U15">
         <v>0.06613097776675758</v>
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>11.58976669504857</v>
+        <v>10.76192621683081</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2569,22 +2569,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1055382453681497</v>
+        <v>0.1054884216350198</v>
       </c>
       <c r="C16">
-        <v>52463.70392023788</v>
+        <v>51901.48292594176</v>
       </c>
       <c r="D16">
-        <v>49919.97383534686</v>
+        <v>49961.64354927282</v>
       </c>
       <c r="E16">
-        <v>-25512.80090709805</v>
+        <v>-24908.91019887598</v>
       </c>
       <c r="F16">
-        <v>8454.469915108986</v>
+        <v>9058.360623331057</v>
       </c>
       <c r="G16">
         <v>10998.2</v>
@@ -2605,28 +2605,28 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M16">
-        <v>559.1023619857932</v>
+        <v>599.0382449847784</v>
       </c>
       <c r="N16">
-        <v>5457.916005361147</v>
+        <v>5417.980122362162</v>
       </c>
       <c r="O16">
-        <v>1091.583201072229</v>
+        <v>1083.596024472432</v>
       </c>
       <c r="P16">
-        <v>4366.332804288917</v>
+        <v>4334.38409788973</v>
       </c>
       <c r="Q16">
-        <v>9210.232804288917</v>
+        <v>9178.284097889729</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1141064835561312</v>
+        <v>0.1147678874153046</v>
       </c>
       <c r="T16">
-        <v>1.056679576548387</v>
+        <v>1.066911283898165</v>
       </c>
       <c r="U16">
         <v>0.06613097776675758</v>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>10.76192621683081</v>
+        <v>10.04446446904209</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2651,22 +2651,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1054884216350198</v>
+        <v>0.1054385979018899</v>
       </c>
       <c r="C17">
-        <v>51901.48292594176</v>
+        <v>51339.33155570722</v>
       </c>
       <c r="D17">
-        <v>49961.64354927282</v>
+        <v>50003.38288726035</v>
       </c>
       <c r="E17">
-        <v>-24908.91019887598</v>
+        <v>-24305.01949065391</v>
       </c>
       <c r="F17">
-        <v>9058.360623331055</v>
+        <v>9662.251331553127</v>
       </c>
       <c r="G17">
         <v>10998.2</v>
@@ -2687,28 +2687,28 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M17">
-        <v>599.0382449847783</v>
+        <v>638.9741279837637</v>
       </c>
       <c r="N17">
-        <v>5417.980122362162</v>
+        <v>5378.044239363177</v>
       </c>
       <c r="O17">
-        <v>1083.596024472432</v>
+        <v>1075.608847872635</v>
       </c>
       <c r="P17">
-        <v>4334.38409788973</v>
+        <v>4302.435391490541</v>
       </c>
       <c r="Q17">
-        <v>9178.284097889729</v>
+        <v>9146.335391490542</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1147678874153046</v>
+        <v>0.1154450389854106</v>
       </c>
       <c r="T17">
-        <v>1.066911283898165</v>
+        <v>1.0773866033277</v>
       </c>
       <c r="U17">
         <v>0.06613097776675758</v>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>10.0444644690421</v>
+        <v>9.416685439726963</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2733,22 +2733,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1054385979018899</v>
+        <v>0.10538877416876</v>
       </c>
       <c r="C18">
-        <v>51339.33155570722</v>
+        <v>50777.24998417775</v>
       </c>
       <c r="D18">
-        <v>50003.38288726035</v>
+        <v>50045.19202395294</v>
       </c>
       <c r="E18">
-        <v>-24305.01949065391</v>
+        <v>-23701.12878243184</v>
       </c>
       <c r="F18">
-        <v>9662.251331553127</v>
+        <v>10266.1420397752</v>
       </c>
       <c r="G18">
         <v>10998.2</v>
@@ -2769,28 +2769,28 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M18">
-        <v>638.9741279837637</v>
+        <v>678.9100109827489</v>
       </c>
       <c r="N18">
-        <v>5378.044239363177</v>
+        <v>5338.108356364191</v>
       </c>
       <c r="O18">
-        <v>1075.608847872635</v>
+        <v>1067.621671272838</v>
       </c>
       <c r="P18">
-        <v>4302.435391490541</v>
+        <v>4270.486685091353</v>
       </c>
       <c r="Q18">
-        <v>9146.335391490542</v>
+        <v>9114.386685091353</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1154450389854106</v>
+        <v>0.1161385074608205</v>
       </c>
       <c r="T18">
-        <v>1.0773866033277</v>
+        <v>1.088114340092887</v>
       </c>
       <c r="U18">
         <v>0.06613097776675758</v>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>9.416685439726963</v>
+        <v>8.862762766801847</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2815,22 +2815,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.10538877416876</v>
+        <v>0.1055549504356302</v>
       </c>
       <c r="C19">
-        <v>50777.24998417775</v>
+        <v>50034.18548157192</v>
       </c>
       <c r="D19">
-        <v>50045.19202395294</v>
+        <v>49906.01822956919</v>
       </c>
       <c r="E19">
-        <v>-23701.12878243184</v>
+        <v>-23097.23807420977</v>
       </c>
       <c r="F19">
-        <v>10266.1420397752</v>
+        <v>10870.03274799727</v>
       </c>
       <c r="G19">
         <v>10998.2</v>
@@ -2851,45 +2851,45 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M19">
-        <v>678.9100109827489</v>
+        <v>735.15094310373</v>
       </c>
       <c r="N19">
-        <v>5338.108356364191</v>
+        <v>5281.86742424321</v>
       </c>
       <c r="O19">
-        <v>1067.621671272838</v>
+        <v>1056.373484848642</v>
       </c>
       <c r="P19">
-        <v>4270.486685091353</v>
+        <v>4225.493939394568</v>
       </c>
       <c r="Q19">
-        <v>9114.386685091353</v>
+        <v>9069.393939394567</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1161385074608205</v>
+        <v>0.1168488898014843</v>
       </c>
       <c r="T19">
-        <v>1.088114340092887</v>
+        <v>1.099103728974298</v>
       </c>
       <c r="U19">
-        <v>0.06613097776675758</v>
+        <v>0.06763097776675758</v>
       </c>
       <c r="V19">
         <v>0.2</v>
       </c>
       <c r="W19">
-        <v>0.05290478221340607</v>
+        <v>0.05410478221340607</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y19">
-        <v>8.862762766801847</v>
+        <v>8.184738690456847</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2897,22 +2897,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1055549504356302</v>
+        <v>0.1055171267025003</v>
       </c>
       <c r="C20">
-        <v>50034.18548157191</v>
+        <v>49461.90433026128</v>
       </c>
       <c r="D20">
-        <v>49906.01822956918</v>
+        <v>49937.62778648062</v>
       </c>
       <c r="E20">
-        <v>-23097.23807420977</v>
+        <v>-22493.3473659877</v>
       </c>
       <c r="F20">
-        <v>10870.03274799727</v>
+        <v>11473.92345621934</v>
       </c>
       <c r="G20">
         <v>10998.2</v>
@@ -2933,28 +2933,28 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M20">
-        <v>735.1509431037299</v>
+        <v>775.9926621650484</v>
       </c>
       <c r="N20">
-        <v>5281.86742424321</v>
+        <v>5241.025705181892</v>
       </c>
       <c r="O20">
-        <v>1056.373484848642</v>
+        <v>1048.205141036378</v>
       </c>
       <c r="P20">
-        <v>4225.493939394568</v>
+        <v>4192.820564145513</v>
       </c>
       <c r="Q20">
-        <v>9069.393939394567</v>
+        <v>9036.720564145513</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1168488898014843</v>
+        <v>0.1175768124468557</v>
       </c>
       <c r="T20">
-        <v>1.099103728974298</v>
+        <v>1.110364460791052</v>
       </c>
       <c r="U20">
         <v>0.06763097776675758</v>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>8.18473869045685</v>
+        <v>7.753962969906487</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2979,22 +2979,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1055171267025003</v>
+        <v>0.1054793029693704</v>
       </c>
       <c r="C21">
-        <v>49461.90433026128</v>
+        <v>48889.66324615603</v>
       </c>
       <c r="D21">
-        <v>49937.62778648062</v>
+        <v>49969.27741059744</v>
       </c>
       <c r="E21">
-        <v>-22493.3473659877</v>
+        <v>-21889.45665776563</v>
       </c>
       <c r="F21">
-        <v>11473.92345621934</v>
+        <v>12077.81416444141</v>
       </c>
       <c r="G21">
         <v>10998.2</v>
@@ -3015,28 +3015,28 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M21">
-        <v>775.9926621650484</v>
+        <v>816.8343812263666</v>
       </c>
       <c r="N21">
-        <v>5241.025705181892</v>
+        <v>5200.183986120574</v>
       </c>
       <c r="O21">
-        <v>1048.205141036378</v>
+        <v>1040.036797224115</v>
       </c>
       <c r="P21">
-        <v>4192.820564145513</v>
+        <v>4160.147188896459</v>
       </c>
       <c r="Q21">
-        <v>9036.720564145513</v>
+        <v>9004.047188896458</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1175768124468557</v>
+        <v>0.1183229331583615</v>
       </c>
       <c r="T21">
-        <v>1.110364460791052</v>
+        <v>1.121906710903225</v>
       </c>
       <c r="U21">
         <v>0.06763097776675758</v>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>7.753962969906487</v>
+        <v>7.366264821411164</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3061,22 +3061,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1054793029693704</v>
+        <v>0.1054414792362405</v>
       </c>
       <c r="C22">
-        <v>48889.66324615603</v>
+        <v>48317.46230548626</v>
       </c>
       <c r="D22">
-        <v>49969.27741059744</v>
+        <v>50000.96717814974</v>
       </c>
       <c r="E22">
-        <v>-21889.45665776563</v>
+        <v>-21285.56594954355</v>
       </c>
       <c r="F22">
-        <v>12077.81416444141</v>
+        <v>12681.70487266348</v>
       </c>
       <c r="G22">
         <v>10998.2</v>
@@ -3097,28 +3097,28 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M22">
-        <v>816.8343812263666</v>
+        <v>857.6761002876851</v>
       </c>
       <c r="N22">
-        <v>5200.183986120574</v>
+        <v>5159.342267059255</v>
       </c>
       <c r="O22">
-        <v>1040.036797224115</v>
+        <v>1031.868453411851</v>
       </c>
       <c r="P22">
-        <v>4160.147188896459</v>
+        <v>4127.473813647404</v>
       </c>
       <c r="Q22">
-        <v>9004.047188896458</v>
+        <v>8971.373813647404</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1183229331583615</v>
+        <v>0.1190879430018041</v>
       </c>
       <c r="T22">
-        <v>1.121906710903225</v>
+        <v>1.133741169878998</v>
       </c>
       <c r="U22">
         <v>0.06763097776675758</v>
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>7.366264821411164</v>
+        <v>7.015490306105869</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3143,22 +3143,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1054414792362405</v>
+        <v>0.1054036555031107</v>
       </c>
       <c r="C23">
-        <v>48317.46230548626</v>
+        <v>47745.3015846755</v>
       </c>
       <c r="D23">
-        <v>50000.96717814974</v>
+        <v>50032.69716556105</v>
       </c>
       <c r="E23">
-        <v>-21285.56594954356</v>
+        <v>-20681.67524132149</v>
       </c>
       <c r="F23">
-        <v>12681.70487266348</v>
+        <v>13285.59558088555</v>
       </c>
       <c r="G23">
         <v>10998.2</v>
@@ -3179,28 +3179,28 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M23">
-        <v>857.676100287685</v>
+        <v>898.5178193490034</v>
       </c>
       <c r="N23">
-        <v>5159.342267059255</v>
+        <v>5118.500547997936</v>
       </c>
       <c r="O23">
-        <v>1031.868453411851</v>
+        <v>1023.700109599587</v>
       </c>
       <c r="P23">
-        <v>4127.473813647404</v>
+        <v>4094.800438398349</v>
       </c>
       <c r="Q23">
-        <v>8971.373813647404</v>
+        <v>8938.700438398348</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1190879430018041</v>
+        <v>0.1198725684822581</v>
       </c>
       <c r="T23">
-        <v>1.133741169878998</v>
+        <v>1.145879076520816</v>
       </c>
       <c r="U23">
         <v>0.06763097776675758</v>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>7.01549030610587</v>
+        <v>6.696604383101057</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1054036555031107</v>
+        <v>0.1056786317699808</v>
       </c>
       <c r="C24">
-        <v>47745.3015846755</v>
+        <v>46911.64937587541</v>
       </c>
       <c r="D24">
-        <v>50032.69716556105</v>
+        <v>49802.93566498303</v>
       </c>
       <c r="E24">
-        <v>-20681.67524132149</v>
+        <v>-20077.78453309942</v>
       </c>
       <c r="F24">
-        <v>13285.59558088555</v>
+        <v>13889.48628910762</v>
       </c>
       <c r="G24">
         <v>10998.2</v>
@@ -3261,45 +3261,45 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M24">
-        <v>898.5178193490034</v>
+        <v>962.9716651018045</v>
       </c>
       <c r="N24">
-        <v>5118.500547997936</v>
+        <v>5054.046702245136</v>
       </c>
       <c r="O24">
-        <v>1023.700109599587</v>
+        <v>1010.809340449027</v>
       </c>
       <c r="P24">
-        <v>4094.800438398349</v>
+        <v>4043.237361796108</v>
       </c>
       <c r="Q24">
-        <v>8938.700438398348</v>
+        <v>8887.137361796107</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1198725684822581</v>
+        <v>0.1206775738453213</v>
       </c>
       <c r="T24">
-        <v>1.145879076520816</v>
+        <v>1.158332253465018</v>
       </c>
       <c r="U24">
-        <v>0.06763097776675758</v>
+        <v>0.06933097776675758</v>
       </c>
       <c r="V24">
         <v>0.2</v>
       </c>
       <c r="W24">
-        <v>0.05410478221340607</v>
+        <v>0.05546478221340606</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y24">
-        <v>6.696604383101057</v>
+        <v>6.24838568506668</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3307,22 +3307,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1056786317699808</v>
+        <v>0.1056544080368509</v>
       </c>
       <c r="C25">
-        <v>46911.64937587541</v>
+        <v>46327.91446005364</v>
       </c>
       <c r="D25">
-        <v>49802.93566498303</v>
+        <v>49823.09145738332</v>
       </c>
       <c r="E25">
-        <v>-20077.78453309942</v>
+        <v>-19473.89382487734</v>
       </c>
       <c r="F25">
-        <v>13889.48628910762</v>
+        <v>14493.37699732969</v>
       </c>
       <c r="G25">
         <v>10998.2</v>
@@ -3343,28 +3343,28 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M25">
-        <v>962.9716651018045</v>
+        <v>1004.839998367101</v>
       </c>
       <c r="N25">
-        <v>5054.046702245136</v>
+        <v>5012.178368979839</v>
       </c>
       <c r="O25">
-        <v>1010.809340449027</v>
+        <v>1002.435673795968</v>
       </c>
       <c r="P25">
-        <v>4043.237361796108</v>
+        <v>4009.742695183872</v>
       </c>
       <c r="Q25">
-        <v>8887.137361796107</v>
+        <v>8853.642695183871</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1206775738453213</v>
+        <v>0.121503763560044</v>
       </c>
       <c r="T25">
-        <v>1.158332253465018</v>
+        <v>1.171113145591963</v>
       </c>
       <c r="U25">
         <v>0.06933097776675758</v>
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>6.24838568506668</v>
+        <v>5.988036281522234</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3389,22 +3389,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1056544080368509</v>
+        <v>0.105630184303721</v>
       </c>
       <c r="C26">
-        <v>46327.91446005364</v>
+        <v>45744.19586537618</v>
       </c>
       <c r="D26">
-        <v>49823.09145738332</v>
+        <v>49843.26357092794</v>
       </c>
       <c r="E26">
-        <v>-19473.89382487735</v>
+        <v>-18870.00311665528</v>
       </c>
       <c r="F26">
-        <v>14493.37699732969</v>
+        <v>15097.26770555176</v>
       </c>
       <c r="G26">
         <v>10998.2</v>
@@ -3425,28 +3425,28 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M26">
-        <v>1004.8399983671</v>
+        <v>1046.708331632396</v>
       </c>
       <c r="N26">
-        <v>5012.178368979839</v>
+        <v>4970.310035714544</v>
       </c>
       <c r="O26">
-        <v>1002.435673795968</v>
+        <v>994.0620071429089</v>
       </c>
       <c r="P26">
-        <v>4009.742695183872</v>
+        <v>3976.248028571635</v>
       </c>
       <c r="Q26">
-        <v>8853.642695183871</v>
+        <v>8820.148028571635</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.121503763560044</v>
+        <v>0.1223519850004927</v>
       </c>
       <c r="T26">
-        <v>1.171113145591963</v>
+        <v>1.18423486150896</v>
       </c>
       <c r="U26">
         <v>0.06933097776675758</v>
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>5.988036281522234</v>
+        <v>5.748514830261345</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3471,22 +3471,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.105630184303721</v>
+        <v>0.1057723605705912</v>
       </c>
       <c r="C27">
-        <v>45744.19586537618</v>
+        <v>45022.14190535418</v>
       </c>
       <c r="D27">
-        <v>49843.26357092794</v>
+        <v>49725.10031912801</v>
       </c>
       <c r="E27">
-        <v>-18870.00311665528</v>
+        <v>-18266.1124084332</v>
       </c>
       <c r="F27">
-        <v>15097.26770555176</v>
+        <v>15701.15841377383</v>
       </c>
       <c r="G27">
         <v>10998.2</v>
@@ -3507,45 +3507,45 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M27">
-        <v>1046.708331632396</v>
+        <v>1101.137591628711</v>
       </c>
       <c r="N27">
-        <v>4970.310035714544</v>
+        <v>4915.880775718229</v>
       </c>
       <c r="O27">
-        <v>994.0620071429089</v>
+        <v>983.1761551436457</v>
       </c>
       <c r="P27">
-        <v>3976.248028571635</v>
+        <v>3932.704620574583</v>
       </c>
       <c r="Q27">
-        <v>8820.148028571635</v>
+        <v>8776.604620574582</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1223519850004927</v>
+        <v>0.1232231313447373</v>
       </c>
       <c r="T27">
-        <v>1.18423486150896</v>
+        <v>1.197711218396686</v>
       </c>
       <c r="U27">
-        <v>0.06933097776675758</v>
+        <v>0.07013097776675759</v>
       </c>
       <c r="V27">
         <v>0.2</v>
       </c>
       <c r="W27">
-        <v>0.05546478221340606</v>
+        <v>0.05610478221340607</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y27">
-        <v>5.748514830261345</v>
+        <v>5.464365591630621</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3553,22 +3553,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1057723605705912</v>
+        <v>0.1057545368374613</v>
       </c>
       <c r="C28">
-        <v>45022.14190535418</v>
+        <v>44433.03384686464</v>
       </c>
       <c r="D28">
-        <v>49725.10031912801</v>
+        <v>49739.88296886054</v>
       </c>
       <c r="E28">
-        <v>-18266.1124084332</v>
+        <v>-17662.22170021114</v>
       </c>
       <c r="F28">
-        <v>15701.15841377383</v>
+        <v>16305.0491219959</v>
       </c>
       <c r="G28">
         <v>10998.2</v>
@@ -3589,28 +3589,28 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M28">
-        <v>1101.137591628711</v>
+        <v>1143.489037460585</v>
       </c>
       <c r="N28">
-        <v>4915.880775718229</v>
+        <v>4873.529329886355</v>
       </c>
       <c r="O28">
-        <v>983.1761551436457</v>
+        <v>974.7058659772711</v>
       </c>
       <c r="P28">
-        <v>3932.704620574583</v>
+        <v>3898.823463909084</v>
       </c>
       <c r="Q28">
-        <v>8776.604620574582</v>
+        <v>8742.723463909084</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1232231313447373</v>
+        <v>0.1241181447121119</v>
       </c>
       <c r="T28">
-        <v>1.197711218396686</v>
+        <v>1.211556790541611</v>
       </c>
       <c r="U28">
         <v>0.07013097776675759</v>
@@ -3627,7 +3627,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>5.464365591630621</v>
+        <v>5.261981680829487</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3635,22 +3635,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1057545368374613</v>
+        <v>0.1057367131043314</v>
       </c>
       <c r="C29">
-        <v>44433.03384686464</v>
+        <v>43843.93458038221</v>
       </c>
       <c r="D29">
-        <v>49739.88296886054</v>
+        <v>49754.67441060018</v>
       </c>
       <c r="E29">
-        <v>-17662.22170021114</v>
+        <v>-17058.33099198906</v>
       </c>
       <c r="F29">
-        <v>16305.0491219959</v>
+        <v>16908.93983021797</v>
       </c>
       <c r="G29">
         <v>10998.2</v>
@@ -3671,28 +3671,28 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M29">
-        <v>1143.489037460585</v>
+        <v>1185.840483292458</v>
       </c>
       <c r="N29">
-        <v>4873.529329886355</v>
+        <v>4831.177884054481</v>
       </c>
       <c r="O29">
-        <v>974.7058659772711</v>
+        <v>966.2355768108963</v>
       </c>
       <c r="P29">
-        <v>3898.823463909084</v>
+        <v>3864.942307243585</v>
       </c>
       <c r="Q29">
-        <v>8742.723463909084</v>
+        <v>8708.842307243583</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1241181447121119</v>
+        <v>0.1250380195619135</v>
       </c>
       <c r="T29">
-        <v>1.211556790541611</v>
+        <v>1.225786961912783</v>
       </c>
       <c r="U29">
         <v>0.07013097776675759</v>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>5.261981680829487</v>
+        <v>5.074053763657004</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3717,22 +3717,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1057367131043314</v>
+        <v>0.1057188893712016</v>
       </c>
       <c r="C30">
-        <v>43843.93458038221</v>
+        <v>43254.8441137528</v>
       </c>
       <c r="D30">
-        <v>49754.67441060018</v>
+        <v>49769.47465219285</v>
       </c>
       <c r="E30">
-        <v>-17058.33099198906</v>
+        <v>-16454.44028376699</v>
       </c>
       <c r="F30">
-        <v>16908.93983021797</v>
+        <v>17512.83053844004</v>
       </c>
       <c r="G30">
         <v>10998.2</v>
@@ -3753,28 +3753,28 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M30">
-        <v>1185.840483292458</v>
+        <v>1228.191929124332</v>
       </c>
       <c r="N30">
-        <v>4831.177884054481</v>
+        <v>4788.826438222608</v>
       </c>
       <c r="O30">
-        <v>966.2355768108963</v>
+        <v>957.7652876445217</v>
       </c>
       <c r="P30">
-        <v>3864.942307243585</v>
+        <v>3831.061150578086</v>
       </c>
       <c r="Q30">
-        <v>8708.842307243583</v>
+        <v>8674.961150578085</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1250380195619135</v>
+        <v>0.1259838063793152</v>
       </c>
       <c r="T30">
-        <v>1.225786961912783</v>
+        <v>1.240417983181735</v>
       </c>
       <c r="U30">
         <v>0.07013097776675759</v>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>5.074053763657004</v>
+        <v>4.899086392496418</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3799,22 +3799,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1057188893712016</v>
+        <v>0.1057010656380717</v>
       </c>
       <c r="C31">
-        <v>43254.8441137528</v>
+        <v>42665.7624548317</v>
       </c>
       <c r="D31">
-        <v>49769.47465219285</v>
+        <v>49784.2837014938</v>
       </c>
       <c r="E31">
-        <v>-16454.44028376699</v>
+        <v>-15850.54957554493</v>
       </c>
       <c r="F31">
-        <v>17512.83053844004</v>
+        <v>18116.72124666211</v>
       </c>
       <c r="G31">
         <v>10998.2</v>
@@ -3835,28 +3835,28 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M31">
-        <v>1228.191929124332</v>
+        <v>1270.543374956205</v>
       </c>
       <c r="N31">
-        <v>4788.826438222608</v>
+        <v>4746.474992390735</v>
       </c>
       <c r="O31">
-        <v>957.7652876445217</v>
+        <v>949.294998478147</v>
       </c>
       <c r="P31">
-        <v>3831.061150578086</v>
+        <v>3797.179993912588</v>
       </c>
       <c r="Q31">
-        <v>8674.961150578085</v>
+        <v>8641.079993912586</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1259838063793152</v>
+        <v>0.1269566156772141</v>
       </c>
       <c r="T31">
-        <v>1.240417983181735</v>
+        <v>1.2554670336298</v>
       </c>
       <c r="U31">
         <v>0.07013097776675759</v>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>4.899086392496418</v>
+        <v>4.735783512746539</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3881,22 +3881,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1057010656380717</v>
+        <v>0.1056832419049418</v>
       </c>
       <c r="C32">
-        <v>42665.7624548317</v>
+        <v>42076.68961148353</v>
       </c>
       <c r="D32">
-        <v>49784.2837014938</v>
+        <v>49799.10156636771</v>
       </c>
       <c r="E32">
-        <v>-15850.54957554493</v>
+        <v>-15246.65886732285</v>
       </c>
       <c r="F32">
-        <v>18116.72124666211</v>
+        <v>18720.61195488418</v>
       </c>
       <c r="G32">
         <v>10998.2</v>
@@ -3917,28 +3917,28 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M32">
-        <v>1270.543374956205</v>
+        <v>1312.894820788079</v>
       </c>
       <c r="N32">
-        <v>4746.474992390735</v>
+        <v>4704.123546558862</v>
       </c>
       <c r="O32">
-        <v>949.294998478147</v>
+        <v>940.8247093117724</v>
       </c>
       <c r="P32">
-        <v>3797.179993912588</v>
+        <v>3763.298837247089</v>
       </c>
       <c r="Q32">
-        <v>8641.079993912586</v>
+        <v>8607.198837247088</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1269566156772141</v>
+        <v>0.1279576223460665</v>
       </c>
       <c r="T32">
-        <v>1.2554670336298</v>
+        <v>1.270952288438678</v>
       </c>
       <c r="U32">
         <v>0.07013097776675759</v>
@@ -3955,7 +3955,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>4.735783512746539</v>
+        <v>4.58301630265794</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3963,22 +3963,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1056832419049418</v>
+        <v>0.1056654181718119</v>
       </c>
       <c r="C33">
-        <v>42076.68961148353</v>
+        <v>41487.62559158223</v>
       </c>
       <c r="D33">
-        <v>49799.10156636771</v>
+        <v>49813.92825468848</v>
       </c>
       <c r="E33">
-        <v>-15246.65886732285</v>
+        <v>-14642.76815910078</v>
       </c>
       <c r="F33">
-        <v>18720.61195488418</v>
+        <v>19324.50266310625</v>
       </c>
       <c r="G33">
         <v>10998.2</v>
@@ -3999,28 +3999,28 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M33">
-        <v>1312.894820788079</v>
+        <v>1355.246266619952</v>
       </c>
       <c r="N33">
-        <v>4704.123546558862</v>
+        <v>4661.772100726987</v>
       </c>
       <c r="O33">
-        <v>940.8247093117724</v>
+        <v>932.3544201453975</v>
       </c>
       <c r="P33">
-        <v>3763.298837247089</v>
+        <v>3729.41768058159</v>
       </c>
       <c r="Q33">
-        <v>8607.198837247088</v>
+        <v>8573.317680581589</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1279576223460665</v>
+        <v>0.1289880703875323</v>
       </c>
       <c r="T33">
-        <v>1.270952288438678</v>
+        <v>1.286892991918406</v>
       </c>
       <c r="U33">
         <v>0.07013097776675759</v>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>4.58301630265794</v>
+        <v>4.43979704319988</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4045,22 +4045,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1056654181718119</v>
+        <v>0.105647594438682</v>
       </c>
       <c r="C34">
-        <v>41487.62559158223</v>
+        <v>40898.5704030112</v>
       </c>
       <c r="D34">
-        <v>49813.92825468848</v>
+        <v>49828.76377433951</v>
       </c>
       <c r="E34">
-        <v>-14642.76815910078</v>
+        <v>-14038.87745087871</v>
       </c>
       <c r="F34">
-        <v>19324.50266310625</v>
+        <v>19928.39337132832</v>
       </c>
       <c r="G34">
         <v>10998.2</v>
@@ -4081,28 +4081,28 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M34">
-        <v>1355.246266619952</v>
+        <v>1397.597712451826</v>
       </c>
       <c r="N34">
-        <v>4661.772100726987</v>
+        <v>4619.420654895114</v>
       </c>
       <c r="O34">
-        <v>932.3544201453975</v>
+        <v>923.8841309790229</v>
       </c>
       <c r="P34">
-        <v>3729.41768058159</v>
+        <v>3695.536523916091</v>
       </c>
       <c r="Q34">
-        <v>8573.317680581589</v>
+        <v>8539.436523916091</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1289880703875323</v>
+        <v>0.1300492780720269</v>
       </c>
       <c r="T34">
-        <v>1.286892991918406</v>
+        <v>1.30330953729305</v>
       </c>
       <c r="U34">
         <v>0.07013097776675759</v>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>4.43979704319988</v>
+        <v>4.305257738860489</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4127,22 +4127,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.105647594438682</v>
+        <v>0.1059017707055522</v>
       </c>
       <c r="C35">
-        <v>40898.5704030112</v>
+        <v>40083.94897903429</v>
       </c>
       <c r="D35">
-        <v>49828.76377433951</v>
+        <v>49618.03305858468</v>
       </c>
       <c r="E35">
-        <v>-14038.87745087871</v>
+        <v>-13434.98674265664</v>
       </c>
       <c r="F35">
-        <v>19928.39337132832</v>
+        <v>20532.28407955039</v>
       </c>
       <c r="G35">
         <v>10998.2</v>
@@ -4163,45 +4163,45 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M35">
-        <v>1397.597712451826</v>
+        <v>1460.48144236325</v>
       </c>
       <c r="N35">
-        <v>4619.420654895114</v>
+        <v>4556.53692498369</v>
       </c>
       <c r="O35">
-        <v>923.8841309790229</v>
+        <v>911.3073849967382</v>
       </c>
       <c r="P35">
-        <v>3695.536523916091</v>
+        <v>3645.229539986952</v>
       </c>
       <c r="Q35">
-        <v>8539.436523916091</v>
+        <v>8489.129539986952</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1300492780720269</v>
+        <v>0.1311426435651426</v>
       </c>
       <c r="T35">
-        <v>1.30330953729305</v>
+        <v>1.320223553739654</v>
       </c>
       <c r="U35">
-        <v>0.07013097776675759</v>
+        <v>0.07113097776675759</v>
       </c>
       <c r="V35">
         <v>0.2</v>
       </c>
       <c r="W35">
-        <v>0.05610478221340607</v>
+        <v>0.05690478221340607</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y35">
-        <v>4.305257738860489</v>
+        <v>4.119886903602566</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4209,22 +4209,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1059017707055522</v>
+        <v>0.1058919469724223</v>
       </c>
       <c r="C36">
-        <v>40083.94897903429</v>
+        <v>39488.16974563961</v>
       </c>
       <c r="D36">
-        <v>49618.03305858468</v>
+        <v>49626.14453341207</v>
       </c>
       <c r="E36">
-        <v>-13434.98674265664</v>
+        <v>-12831.09603443457</v>
       </c>
       <c r="F36">
-        <v>20532.28407955039</v>
+        <v>21136.17478777247</v>
       </c>
       <c r="G36">
         <v>10998.2</v>
@@ -4245,28 +4245,28 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M36">
-        <v>1460.48144236325</v>
+        <v>1503.436778903346</v>
       </c>
       <c r="N36">
-        <v>4556.53692498369</v>
+        <v>4513.581588443594</v>
       </c>
       <c r="O36">
-        <v>911.3073849967382</v>
+        <v>902.7163176887188</v>
       </c>
       <c r="P36">
-        <v>3645.229539986952</v>
+        <v>3610.865270754875</v>
       </c>
       <c r="Q36">
-        <v>8489.129539986952</v>
+        <v>8454.765270754875</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1311426435651426</v>
+        <v>0.132269651073431</v>
       </c>
       <c r="T36">
-        <v>1.320223553739654</v>
+        <v>1.337658001461538</v>
       </c>
       <c r="U36">
         <v>0.07113097776675759</v>
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>4.119886903602566</v>
+        <v>4.002175849213922</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1058919469724223</v>
+        <v>0.1058821232392924</v>
       </c>
       <c r="C37">
-        <v>39488.16974563961</v>
+        <v>38892.39316477983</v>
       </c>
       <c r="D37">
-        <v>49626.14453341207</v>
+        <v>49634.25866077437</v>
       </c>
       <c r="E37">
-        <v>-12831.09603443457</v>
+        <v>-12227.2053262125</v>
       </c>
       <c r="F37">
-        <v>21136.17478777247</v>
+        <v>21740.06549599454</v>
       </c>
       <c r="G37">
         <v>10998.2</v>
@@ -4327,28 +4327,28 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M37">
-        <v>1503.436778903346</v>
+        <v>1546.392115443441</v>
       </c>
       <c r="N37">
-        <v>4513.581588443594</v>
+        <v>4470.626251903499</v>
       </c>
       <c r="O37">
-        <v>902.7163176887188</v>
+        <v>894.1252503806999</v>
       </c>
       <c r="P37">
-        <v>3610.865270754875</v>
+        <v>3576.501001522799</v>
       </c>
       <c r="Q37">
-        <v>8454.765270754875</v>
+        <v>8420.401001522798</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.132269651073431</v>
+        <v>0.1334318775663535</v>
       </c>
       <c r="T37">
-        <v>1.337658001461538</v>
+        <v>1.355637275674731</v>
       </c>
       <c r="U37">
         <v>0.07113097776675759</v>
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>4.002175849213922</v>
+        <v>3.891004297846869</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4373,22 +4373,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1058821232392924</v>
+        <v>0.1058722995061625</v>
       </c>
       <c r="C38">
-        <v>38892.39316477982</v>
+        <v>38296.61923775627</v>
       </c>
       <c r="D38">
-        <v>49634.25866077436</v>
+        <v>49642.37544197287</v>
       </c>
       <c r="E38">
-        <v>-12227.2053262125</v>
+        <v>-11623.31461799043</v>
       </c>
       <c r="F38">
-        <v>21740.06549599453</v>
+        <v>22343.9562042166</v>
       </c>
       <c r="G38">
         <v>10998.2</v>
@@ -4409,28 +4409,28 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M38">
-        <v>1546.392115443441</v>
+        <v>1589.347451983537</v>
       </c>
       <c r="N38">
-        <v>4470.626251903499</v>
+        <v>4427.670915363404</v>
       </c>
       <c r="O38">
-        <v>894.1252503806999</v>
+        <v>885.5341830726808</v>
       </c>
       <c r="P38">
-        <v>3576.501001522799</v>
+        <v>3542.136732290723</v>
       </c>
       <c r="Q38">
-        <v>8420.401001522798</v>
+        <v>8386.036732290722</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1334318775663535</v>
+        <v>0.1346310001384164</v>
       </c>
       <c r="T38">
-        <v>1.355637275674731</v>
+        <v>1.374187320497866</v>
       </c>
       <c r="U38">
         <v>0.07113097776675759</v>
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>3.891004297846869</v>
+        <v>3.785842019526684</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4455,22 +4455,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1058722995061625</v>
+        <v>0.1058624757730327</v>
       </c>
       <c r="C39">
-        <v>38296.61923775627</v>
+        <v>37700.84796587109</v>
       </c>
       <c r="D39">
-        <v>49642.37544197287</v>
+        <v>49650.49487830976</v>
       </c>
       <c r="E39">
-        <v>-11623.31461799043</v>
+        <v>-11019.42390976836</v>
       </c>
       <c r="F39">
-        <v>22343.9562042166</v>
+        <v>22947.84691243868</v>
       </c>
       <c r="G39">
         <v>10998.2</v>
@@ -4491,28 +4491,28 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M39">
-        <v>1589.347451983537</v>
+        <v>1632.302788523632</v>
       </c>
       <c r="N39">
-        <v>4427.670915363404</v>
+        <v>4384.715578823308</v>
       </c>
       <c r="O39">
-        <v>885.5341830726808</v>
+        <v>876.9431157646616</v>
       </c>
       <c r="P39">
-        <v>3542.136732290723</v>
+        <v>3507.772463058646</v>
       </c>
       <c r="Q39">
-        <v>8386.036732290722</v>
+        <v>8351.672463058647</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1346310001384164</v>
+        <v>0.1358688040837716</v>
       </c>
       <c r="T39">
-        <v>1.374187320497866</v>
+        <v>1.393335753863683</v>
       </c>
       <c r="U39">
         <v>0.07113097776675759</v>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>3.785842019526684</v>
+        <v>3.686214597960191</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4537,22 +4537,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1058624757730327</v>
+        <v>0.1058526520399028</v>
       </c>
       <c r="C40">
-        <v>37700.84796587109</v>
+        <v>37105.07935042732</v>
       </c>
       <c r="D40">
-        <v>49650.49487830976</v>
+        <v>49658.61697108806</v>
       </c>
       <c r="E40">
-        <v>-11019.42390976836</v>
+        <v>-10415.53320154629</v>
       </c>
       <c r="F40">
-        <v>22947.84691243868</v>
+        <v>23551.73762066075</v>
       </c>
       <c r="G40">
         <v>10998.2</v>
@@ -4573,28 +4573,28 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M40">
-        <v>1632.302788523632</v>
+        <v>1675.258125063728</v>
       </c>
       <c r="N40">
-        <v>4384.715578823308</v>
+        <v>4341.760242283212</v>
       </c>
       <c r="O40">
-        <v>876.9431157646616</v>
+        <v>868.3520484566425</v>
       </c>
       <c r="P40">
-        <v>3507.772463058646</v>
+        <v>3473.40819382657</v>
       </c>
       <c r="Q40">
-        <v>8351.672463058647</v>
+        <v>8317.30819382657</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1358688040837716</v>
+        <v>0.13714719176504</v>
       </c>
       <c r="T40">
-        <v>1.393335753863683</v>
+        <v>1.413112004716904</v>
       </c>
       <c r="U40">
         <v>0.07113097776675759</v>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>3.686214597960191</v>
+        <v>3.591696274935571</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4619,22 +4619,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1058526520399028</v>
+        <v>0.1058428283067729</v>
       </c>
       <c r="C41">
-        <v>37105.07935042732</v>
+        <v>36509.31339272881</v>
       </c>
       <c r="D41">
-        <v>49658.61697108806</v>
+        <v>49666.74172161163</v>
       </c>
       <c r="E41">
-        <v>-10415.53320154629</v>
+        <v>-9811.64249332422</v>
       </c>
       <c r="F41">
-        <v>23551.73762066075</v>
+        <v>24155.62832888282</v>
       </c>
       <c r="G41">
         <v>10998.2</v>
@@ -4655,28 +4655,28 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M41">
-        <v>1675.258125063728</v>
+        <v>1718.213461603823</v>
       </c>
       <c r="N41">
-        <v>4341.760242283212</v>
+        <v>4298.804905743116</v>
       </c>
       <c r="O41">
-        <v>868.3520484566425</v>
+        <v>859.7609811486233</v>
       </c>
       <c r="P41">
-        <v>3473.40819382657</v>
+        <v>3439.043924594493</v>
       </c>
       <c r="Q41">
-        <v>8317.30819382657</v>
+        <v>8282.943924594492</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.13714719176504</v>
+        <v>0.1384681923690175</v>
       </c>
       <c r="T41">
-        <v>1.413112004716904</v>
+        <v>1.433547463931899</v>
       </c>
       <c r="U41">
         <v>0.07113097776675759</v>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>3.591696274935571</v>
+        <v>3.501903868062182</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4701,22 +4701,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1058428283067729</v>
+        <v>0.105833004573643</v>
       </c>
       <c r="C42">
-        <v>36509.31339272881</v>
+        <v>35913.55009408034</v>
       </c>
       <c r="D42">
-        <v>49666.74172161163</v>
+        <v>49674.86913118523</v>
       </c>
       <c r="E42">
-        <v>-9811.64249332422</v>
+        <v>-9207.751785102148</v>
       </c>
       <c r="F42">
-        <v>24155.62832888282</v>
+        <v>24759.51903710489</v>
       </c>
       <c r="G42">
         <v>10998.2</v>
@@ -4737,28 +4737,28 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M42">
-        <v>1718.213461603823</v>
+        <v>1761.168798143919</v>
       </c>
       <c r="N42">
-        <v>4298.804905743116</v>
+        <v>4255.849569203021</v>
       </c>
       <c r="O42">
-        <v>859.7609811486233</v>
+        <v>851.1699138406043</v>
       </c>
       <c r="P42">
-        <v>3439.043924594493</v>
+        <v>3404.679655362417</v>
       </c>
       <c r="Q42">
-        <v>8282.943924594492</v>
+        <v>8248.579655362417</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1384681923690175</v>
+        <v>0.1398339726544857</v>
       </c>
       <c r="T42">
-        <v>1.433547463931899</v>
+        <v>1.454675650577911</v>
       </c>
       <c r="U42">
         <v>0.07113097776675759</v>
@@ -4775,7 +4775,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>3.501903868062182</v>
+        <v>3.41649157859725</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4783,22 +4783,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.105833004573643</v>
+        <v>0.1058231808405132</v>
       </c>
       <c r="C43">
-        <v>35913.55009408034</v>
+        <v>35317.78945578747</v>
       </c>
       <c r="D43">
-        <v>49674.86913118523</v>
+        <v>49682.99920111443</v>
       </c>
       <c r="E43">
-        <v>-9207.751785102148</v>
+        <v>-8603.861076880075</v>
       </c>
       <c r="F43">
-        <v>24759.51903710489</v>
+        <v>25363.40974532696</v>
       </c>
       <c r="G43">
         <v>10998.2</v>
@@ -4819,28 +4819,28 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M43">
-        <v>1761.168798143919</v>
+        <v>1804.124134684015</v>
       </c>
       <c r="N43">
-        <v>4255.849569203021</v>
+        <v>4212.894232662926</v>
       </c>
       <c r="O43">
-        <v>851.1699138406043</v>
+        <v>842.5788465325852</v>
       </c>
       <c r="P43">
-        <v>3404.679655362417</v>
+        <v>3370.315386130341</v>
       </c>
       <c r="Q43">
-        <v>8248.579655362417</v>
+        <v>8214.215386130341</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1398339726544857</v>
+        <v>0.1412468488118666</v>
       </c>
       <c r="T43">
-        <v>1.454675650577911</v>
+        <v>1.47653239538413</v>
       </c>
       <c r="U43">
         <v>0.07113097776675759</v>
@@ -4857,7 +4857,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>3.41649157859725</v>
+        <v>3.335146541011602</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4865,22 +4865,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1058231808405132</v>
+        <v>0.1058133571073833</v>
       </c>
       <c r="C44">
-        <v>35317.78945578746</v>
+        <v>34722.03147915663</v>
       </c>
       <c r="D44">
-        <v>49682.99920111442</v>
+        <v>49691.13193270566</v>
       </c>
       <c r="E44">
-        <v>-8603.861076880079</v>
+        <v>-7999.970368658011</v>
       </c>
       <c r="F44">
-        <v>25363.40974532696</v>
+        <v>25967.30045354903</v>
       </c>
       <c r="G44">
         <v>10998.2</v>
@@ -4901,28 +4901,28 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M44">
-        <v>1804.124134684015</v>
+        <v>1847.07947122411</v>
       </c>
       <c r="N44">
-        <v>4212.894232662926</v>
+        <v>4169.938896122831</v>
       </c>
       <c r="O44">
-        <v>842.5788465325852</v>
+        <v>833.9877792245661</v>
       </c>
       <c r="P44">
-        <v>3370.315386130341</v>
+        <v>3335.951116898264</v>
       </c>
       <c r="Q44">
-        <v>8214.215386130341</v>
+        <v>8179.851116898264</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1412468488118666</v>
+        <v>0.1427092995712609</v>
       </c>
       <c r="T44">
-        <v>1.47653239538413</v>
+        <v>1.499156043516883</v>
       </c>
       <c r="U44">
         <v>0.07113097776675759</v>
@@ -4939,7 +4939,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>3.335146541011602</v>
+        <v>3.257584993546216</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4947,22 +4947,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1058133571073833</v>
+        <v>0.1058035333742534</v>
       </c>
       <c r="C45">
-        <v>34722.03147915663</v>
+        <v>34126.27616549515</v>
       </c>
       <c r="D45">
-        <v>49691.13193270566</v>
+        <v>49699.26732726624</v>
       </c>
       <c r="E45">
-        <v>-7999.970368658011</v>
+        <v>-7396.079660435938</v>
       </c>
       <c r="F45">
-        <v>25967.30045354903</v>
+        <v>26571.1911617711</v>
       </c>
       <c r="G45">
         <v>10998.2</v>
@@ -4983,28 +4983,28 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M45">
-        <v>1847.07947122411</v>
+        <v>1890.034807764206</v>
       </c>
       <c r="N45">
-        <v>4169.938896122831</v>
+        <v>4126.983559582734</v>
       </c>
       <c r="O45">
-        <v>833.9877792245661</v>
+        <v>825.3967119165469</v>
       </c>
       <c r="P45">
-        <v>3335.951116898264</v>
+        <v>3301.586847666188</v>
       </c>
       <c r="Q45">
-        <v>8179.851116898264</v>
+        <v>8145.486847666187</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1427092995712609</v>
+        <v>0.1442239807149192</v>
       </c>
       <c r="T45">
-        <v>1.499156043516883</v>
+        <v>1.522587679082949</v>
       </c>
       <c r="U45">
         <v>0.07113097776675759</v>
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>3.257584993546216</v>
+        <v>3.18354897096562</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5029,22 +5029,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1058035333742534</v>
+        <v>0.1057937096411235</v>
       </c>
       <c r="C46">
-        <v>34126.27616549515</v>
+        <v>33530.52351611115</v>
       </c>
       <c r="D46">
-        <v>49699.26732726624</v>
+        <v>49707.40538610431</v>
       </c>
       <c r="E46">
-        <v>-7396.079660435938</v>
+        <v>-6792.188952213866</v>
       </c>
       <c r="F46">
-        <v>26571.1911617711</v>
+        <v>27175.08186999317</v>
       </c>
       <c r="G46">
         <v>10998.2</v>
@@ -5065,28 +5065,28 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M46">
-        <v>1890.034807764206</v>
+        <v>1932.990144304301</v>
       </c>
       <c r="N46">
-        <v>4126.983559582734</v>
+        <v>4084.028223042639</v>
       </c>
       <c r="O46">
-        <v>825.3967119165469</v>
+        <v>816.8056446085278</v>
       </c>
       <c r="P46">
-        <v>3301.586847666188</v>
+        <v>3267.222578434111</v>
       </c>
       <c r="Q46">
-        <v>8145.486847666187</v>
+        <v>8111.12257843411</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1442239807149192</v>
+        <v>0.1457937411728924</v>
       </c>
       <c r="T46">
-        <v>1.522587679082949</v>
+        <v>1.546871374124144</v>
       </c>
       <c r="U46">
         <v>0.07113097776675759</v>
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>3.18354897096562</v>
+        <v>3.112803438277495</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5111,22 +5111,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1057937096411235</v>
+        <v>0.1057838859079937</v>
       </c>
       <c r="C47">
-        <v>33530.52351611115</v>
+        <v>32934.77353231363</v>
       </c>
       <c r="D47">
-        <v>49707.40538610431</v>
+        <v>49715.54611052887</v>
       </c>
       <c r="E47">
-        <v>-6792.188952213866</v>
+        <v>-6188.298243991798</v>
       </c>
       <c r="F47">
-        <v>27175.08186999317</v>
+        <v>27778.97257821524</v>
       </c>
       <c r="G47">
         <v>10998.2</v>
@@ -5147,28 +5147,28 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M47">
-        <v>1932.990144304301</v>
+        <v>1975.945480844397</v>
       </c>
       <c r="N47">
-        <v>4084.028223042639</v>
+        <v>4041.072886502543</v>
       </c>
       <c r="O47">
-        <v>816.8056446085278</v>
+        <v>808.2145773005086</v>
       </c>
       <c r="P47">
-        <v>3267.222578434111</v>
+        <v>3232.858309202034</v>
       </c>
       <c r="Q47">
-        <v>8111.12257843411</v>
+        <v>8076.758309202034</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1457937411728924</v>
+        <v>0.1474216409070868</v>
       </c>
       <c r="T47">
-        <v>1.546871374124144</v>
+        <v>1.572054465277976</v>
       </c>
       <c r="U47">
         <v>0.07113097776675759</v>
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>3.112803438277495</v>
+        <v>3.045133798314941</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5193,22 +5193,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1057838859079937</v>
+        <v>0.1067140621748638</v>
       </c>
       <c r="C48">
-        <v>32934.77353231363</v>
+        <v>31571.71130547326</v>
       </c>
       <c r="D48">
-        <v>49715.54611052887</v>
+        <v>48956.37459191057</v>
       </c>
       <c r="E48">
-        <v>-6188.298243991798</v>
+        <v>-5584.407535769726</v>
       </c>
       <c r="F48">
-        <v>27778.97257821524</v>
+        <v>28382.86328643731</v>
       </c>
       <c r="G48">
         <v>10998.2</v>
@@ -5229,45 +5229,45 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M48">
-        <v>1975.945480844397</v>
+        <v>2089.857975600586</v>
       </c>
       <c r="N48">
-        <v>4041.072886502543</v>
+        <v>3927.160391746354</v>
       </c>
       <c r="O48">
-        <v>808.2145773005086</v>
+        <v>785.4320783492709</v>
       </c>
       <c r="P48">
-        <v>3232.858309202034</v>
+        <v>3141.728313397084</v>
       </c>
       <c r="Q48">
-        <v>8076.758309202034</v>
+        <v>7985.628313397083</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1474216409070868</v>
+        <v>0.1491109708199301</v>
       </c>
       <c r="T48">
-        <v>1.572054465277976</v>
+        <v>1.598187861758368</v>
       </c>
       <c r="U48">
-        <v>0.07113097776675759</v>
+        <v>0.07363097776675757</v>
       </c>
       <c r="V48">
         <v>0.2</v>
       </c>
       <c r="W48">
-        <v>0.05690478221340607</v>
+        <v>0.05890478221340606</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y48">
-        <v>3.045133798314941</v>
+        <v>2.879151807250329</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5275,22 +5275,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1067140621748638</v>
+        <v>0.1067242384417339</v>
       </c>
       <c r="C49">
-        <v>31571.71130547326</v>
+        <v>30959.64334061929</v>
       </c>
       <c r="D49">
-        <v>48956.37459191057</v>
+        <v>48948.19733527867</v>
       </c>
       <c r="E49">
-        <v>-5584.407535769726</v>
+        <v>-4980.516827547654</v>
       </c>
       <c r="F49">
-        <v>28382.86328643731</v>
+        <v>28986.75399465938</v>
       </c>
       <c r="G49">
         <v>10998.2</v>
@@ -5311,28 +5311,28 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M49">
-        <v>2089.857975600586</v>
+        <v>2134.323038911236</v>
       </c>
       <c r="N49">
-        <v>3927.160391746354</v>
+        <v>3882.695328435704</v>
       </c>
       <c r="O49">
-        <v>785.4320783492709</v>
+        <v>776.5390656871408</v>
       </c>
       <c r="P49">
-        <v>3141.728313397084</v>
+        <v>3106.156262748563</v>
       </c>
       <c r="Q49">
-        <v>7985.628313397083</v>
+        <v>7950.056262748562</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1491109708199301</v>
+        <v>0.1508652749601904</v>
       </c>
       <c r="T49">
-        <v>1.598187861758368</v>
+        <v>1.625326388872621</v>
       </c>
       <c r="U49">
         <v>0.07363097776675757</v>
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>2.879151807250329</v>
+        <v>2.819169477932614</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1067242384417339</v>
+        <v>0.106734414708604</v>
       </c>
       <c r="C50">
-        <v>30959.64334061929</v>
+        <v>30347.578107028</v>
       </c>
       <c r="D50">
-        <v>48948.19733527867</v>
+        <v>48940.02280990945</v>
       </c>
       <c r="E50">
-        <v>-4980.516827547657</v>
+        <v>-4376.626119325589</v>
       </c>
       <c r="F50">
-        <v>28986.75399465938</v>
+        <v>29590.64470288145</v>
       </c>
       <c r="G50">
         <v>10998.2</v>
@@ -5393,28 +5393,28 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M50">
-        <v>2134.323038911236</v>
+        <v>2178.788102221887</v>
       </c>
       <c r="N50">
-        <v>3882.695328435704</v>
+        <v>3838.230265125053</v>
       </c>
       <c r="O50">
-        <v>776.5390656871409</v>
+        <v>767.6460530250107</v>
       </c>
       <c r="P50">
-        <v>3106.156262748563</v>
+        <v>3070.584212100043</v>
       </c>
       <c r="Q50">
-        <v>7950.056262748563</v>
+        <v>7914.484212100042</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1508652749601904</v>
+        <v>0.1526883753412452</v>
       </c>
       <c r="T50">
-        <v>1.625326388872621</v>
+        <v>1.653529171952139</v>
       </c>
       <c r="U50">
         <v>0.07363097776675757</v>
@@ -5431,7 +5431,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>2.819169477932614</v>
+        <v>2.761635406954398</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5439,22 +5439,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.106734414708604</v>
+        <v>0.1067445909754742</v>
       </c>
       <c r="C51">
-        <v>30347.578107028</v>
+        <v>29735.51560333117</v>
       </c>
       <c r="D51">
-        <v>48940.02280990945</v>
+        <v>48931.85101443469</v>
       </c>
       <c r="E51">
-        <v>-4376.626119325589</v>
+        <v>-3772.735411103517</v>
       </c>
       <c r="F51">
-        <v>29590.64470288145</v>
+        <v>30194.53541110352</v>
       </c>
       <c r="G51">
         <v>10998.2</v>
@@ -5475,28 +5475,28 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M51">
-        <v>2178.788102221887</v>
+        <v>2223.253165532537</v>
       </c>
       <c r="N51">
-        <v>3838.230265125053</v>
+        <v>3793.765201814403</v>
       </c>
       <c r="O51">
-        <v>767.6460530250107</v>
+        <v>758.7530403628806</v>
       </c>
       <c r="P51">
-        <v>3070.584212100043</v>
+        <v>3035.012161451522</v>
       </c>
       <c r="Q51">
-        <v>7914.484212100042</v>
+        <v>7878.912161451522</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1526883753412452</v>
+        <v>0.1545843997375423</v>
       </c>
       <c r="T51">
-        <v>1.653529171952139</v>
+        <v>1.682860066354838</v>
       </c>
       <c r="U51">
         <v>0.07363097776675757</v>
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>2.761635406954398</v>
+        <v>2.70640269881531</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5521,22 +5521,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1067445909754742</v>
+        <v>0.1067547672423443</v>
       </c>
       <c r="C52">
-        <v>29735.51560333117</v>
+        <v>29123.45582816158</v>
       </c>
       <c r="D52">
-        <v>48931.85101443469</v>
+        <v>48923.68194748717</v>
       </c>
       <c r="E52">
-        <v>-3772.735411103517</v>
+        <v>-3168.844702881444</v>
       </c>
       <c r="F52">
-        <v>30194.53541110352</v>
+        <v>30798.42611932559</v>
       </c>
       <c r="G52">
         <v>10998.2</v>
@@ -5557,28 +5557,28 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M52">
-        <v>2223.253165532537</v>
+        <v>2267.718228843188</v>
       </c>
       <c r="N52">
-        <v>3793.765201814403</v>
+        <v>3749.300138503752</v>
       </c>
       <c r="O52">
-        <v>758.7530403628806</v>
+        <v>749.8600277007504</v>
       </c>
       <c r="P52">
-        <v>3035.012161451522</v>
+        <v>2999.440110803002</v>
       </c>
       <c r="Q52">
-        <v>7878.912161451522</v>
+        <v>7843.340110803001</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1545843997375423</v>
+        <v>0.1565578128847086</v>
       </c>
       <c r="T52">
-        <v>1.682860066354838</v>
+        <v>1.713388140120912</v>
       </c>
       <c r="U52">
         <v>0.07363097776675757</v>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>2.70640269881531</v>
+        <v>2.653335979230696</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5603,22 +5603,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1067547672423443</v>
+        <v>0.1067649435092144</v>
       </c>
       <c r="C53">
-        <v>29123.45582816158</v>
+        <v>28511.39878015293</v>
       </c>
       <c r="D53">
-        <v>48923.68194748717</v>
+        <v>48915.51560770059</v>
       </c>
       <c r="E53">
-        <v>-3168.844702881444</v>
+        <v>-2564.953994659376</v>
       </c>
       <c r="F53">
-        <v>30798.42611932559</v>
+        <v>31402.31682754766</v>
       </c>
       <c r="G53">
         <v>10998.2</v>
@@ -5639,28 +5639,28 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M53">
-        <v>2267.718228843188</v>
+        <v>2312.183292153839</v>
       </c>
       <c r="N53">
-        <v>3749.300138503752</v>
+        <v>3704.835075193101</v>
       </c>
       <c r="O53">
-        <v>749.8600277007504</v>
+        <v>740.9670150386203</v>
       </c>
       <c r="P53">
-        <v>2999.440110803002</v>
+        <v>2963.868060154481</v>
       </c>
       <c r="Q53">
-        <v>7843.340110803001</v>
+        <v>7807.768060154481</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1565578128847086</v>
+        <v>0.1586134515796735</v>
       </c>
       <c r="T53">
-        <v>1.713388140120912</v>
+        <v>1.745188216960573</v>
       </c>
       <c r="U53">
         <v>0.07363097776675757</v>
@@ -5677,7 +5677,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>2.653335979230696</v>
+        <v>2.602310287322413</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5685,22 +5685,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1067649435092144</v>
+        <v>0.1067751197760845</v>
       </c>
       <c r="C54">
-        <v>28511.39878015293</v>
+        <v>27899.34445793975</v>
       </c>
       <c r="D54">
-        <v>48915.51560770059</v>
+        <v>48907.35199370948</v>
       </c>
       <c r="E54">
-        <v>-2564.953994659376</v>
+        <v>-1961.063286437304</v>
       </c>
       <c r="F54">
-        <v>31402.31682754766</v>
+        <v>32006.20753576973</v>
       </c>
       <c r="G54">
         <v>10998.2</v>
@@ -5721,28 +5721,28 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M54">
-        <v>2312.183292153839</v>
+        <v>2356.64835546449</v>
       </c>
       <c r="N54">
-        <v>3704.835075193101</v>
+        <v>3660.37001188245</v>
       </c>
       <c r="O54">
-        <v>740.9670150386203</v>
+        <v>732.0740023764902</v>
       </c>
       <c r="P54">
-        <v>2963.868060154481</v>
+        <v>2928.29600950596</v>
       </c>
       <c r="Q54">
-        <v>7807.768060154481</v>
+        <v>7772.19600950596</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1586134515796735</v>
+        <v>0.1607565642616582</v>
       </c>
       <c r="T54">
-        <v>1.745188216960573</v>
+        <v>1.778341488559368</v>
       </c>
       <c r="U54">
         <v>0.07363097776675757</v>
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>2.602310287322413</v>
+        <v>2.55321009322199</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5767,22 +5767,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1067751197760845</v>
+        <v>0.1067852960429547</v>
       </c>
       <c r="C55">
-        <v>27899.34445793975</v>
+        <v>27287.29286015754</v>
       </c>
       <c r="D55">
-        <v>48907.35199370948</v>
+        <v>48899.19110414934</v>
       </c>
       <c r="E55">
-        <v>-1961.063286437304</v>
+        <v>-1357.172578215232</v>
       </c>
       <c r="F55">
-        <v>32006.20753576973</v>
+        <v>32610.0982439918</v>
       </c>
       <c r="G55">
         <v>10998.2</v>
@@ -5803,28 +5803,28 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M55">
-        <v>2356.64835546449</v>
+        <v>2401.113418775141</v>
       </c>
       <c r="N55">
-        <v>3660.37001188245</v>
+        <v>3615.904948571799</v>
       </c>
       <c r="O55">
-        <v>732.0740023764902</v>
+        <v>723.1809897143598</v>
       </c>
       <c r="P55">
-        <v>2928.29600950596</v>
+        <v>2892.723958857439</v>
       </c>
       <c r="Q55">
-        <v>7772.19600950596</v>
+        <v>7736.623958857439</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1607565642616582</v>
+        <v>0.162992855755903</v>
       </c>
       <c r="T55">
-        <v>1.778341488559368</v>
+        <v>1.812936206749415</v>
       </c>
       <c r="U55">
         <v>0.07363097776675757</v>
@@ -5841,7 +5841,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>2.55321009322199</v>
+        <v>2.50592842482899</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5849,22 +5849,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1067852960429547</v>
+        <v>0.1083354723098248</v>
       </c>
       <c r="C56">
-        <v>27287.29286015754</v>
+        <v>25471.25226773462</v>
       </c>
       <c r="D56">
-        <v>48899.19110414934</v>
+        <v>47687.04121994849</v>
       </c>
       <c r="E56">
-        <v>-1357.172578215232</v>
+        <v>-753.2818699931595</v>
       </c>
       <c r="F56">
-        <v>32610.0982439918</v>
+        <v>33213.98895221388</v>
       </c>
       <c r="G56">
         <v>10998.2</v>
@@ -5885,45 +5885,45 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M56">
-        <v>2401.113418775141</v>
+        <v>2561.82744341854</v>
       </c>
       <c r="N56">
-        <v>3615.904948571799</v>
+        <v>3455.1909239284</v>
       </c>
       <c r="O56">
-        <v>723.1809897143598</v>
+        <v>691.03818478568</v>
       </c>
       <c r="P56">
-        <v>2892.723958857439</v>
+        <v>2764.15273914272</v>
       </c>
       <c r="Q56">
-        <v>7736.623958857439</v>
+        <v>7608.052739142719</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.162992855755903</v>
+        <v>0.1653285379832255</v>
       </c>
       <c r="T56">
-        <v>1.812936206749415</v>
+        <v>1.849068467970131</v>
       </c>
       <c r="U56">
-        <v>0.07363097776675757</v>
+        <v>0.07713097776675758</v>
       </c>
       <c r="V56">
         <v>0.2</v>
       </c>
       <c r="W56">
-        <v>0.05890478221340606</v>
+        <v>0.06170478221340606</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y56">
-        <v>2.50592842482899</v>
+        <v>2.34872117667603</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5931,22 +5931,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1083354723098248</v>
+        <v>0.1083736485766949</v>
       </c>
       <c r="C57">
-        <v>25471.25226773462</v>
+        <v>24838.26763174474</v>
       </c>
       <c r="D57">
-        <v>47687.04121994849</v>
+        <v>47657.94729218069</v>
       </c>
       <c r="E57">
-        <v>-753.2818699931595</v>
+        <v>-149.391161771091</v>
       </c>
       <c r="F57">
-        <v>33213.98895221388</v>
+        <v>33817.87966043594</v>
       </c>
       <c r="G57">
         <v>10998.2</v>
@@ -5967,28 +5967,28 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M57">
-        <v>2561.82744341854</v>
+        <v>2608.406124207968</v>
       </c>
       <c r="N57">
-        <v>3455.1909239284</v>
+        <v>3408.612243138972</v>
       </c>
       <c r="O57">
-        <v>691.03818478568</v>
+        <v>681.7224486277944</v>
       </c>
       <c r="P57">
-        <v>2764.15273914272</v>
+        <v>2726.889794511178</v>
       </c>
       <c r="Q57">
-        <v>7608.052739142719</v>
+        <v>7570.789794511177</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1653285379832255</v>
+        <v>0.1677703875845171</v>
       </c>
       <c r="T57">
-        <v>1.849068467970131</v>
+        <v>1.886843104700879</v>
       </c>
       <c r="U57">
         <v>0.07713097776675758</v>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>2.34872117667603</v>
+        <v>2.30677972709253</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6013,22 +6013,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1083736485766949</v>
+        <v>0.108411824843565</v>
       </c>
       <c r="C58">
-        <v>24838.26763174474</v>
+        <v>24205.3184745978</v>
       </c>
       <c r="D58">
-        <v>47657.94729218069</v>
+        <v>47628.88884325582</v>
       </c>
       <c r="E58">
-        <v>-149.391161771091</v>
+        <v>454.4995464509775</v>
       </c>
       <c r="F58">
-        <v>33817.87966043594</v>
+        <v>34421.77036865801</v>
       </c>
       <c r="G58">
         <v>10998.2</v>
@@ -6049,28 +6049,28 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M58">
-        <v>2608.406124207968</v>
+        <v>2654.984804997396</v>
       </c>
       <c r="N58">
-        <v>3408.612243138972</v>
+        <v>3362.033562349544</v>
       </c>
       <c r="O58">
-        <v>681.7224486277944</v>
+        <v>672.4067124699088</v>
       </c>
       <c r="P58">
-        <v>2726.889794511178</v>
+        <v>2689.626849879635</v>
       </c>
       <c r="Q58">
-        <v>7570.789794511177</v>
+        <v>7533.526849879635</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1677703875845171</v>
+        <v>0.1703258115858688</v>
       </c>
       <c r="T58">
-        <v>1.886843104700879</v>
+        <v>1.926374701279569</v>
       </c>
       <c r="U58">
         <v>0.07713097776675758</v>
@@ -6087,7 +6087,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>2.30677972709253</v>
+        <v>2.266309907318977</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6095,22 +6095,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.108411824843565</v>
+        <v>0.1097492011104352</v>
       </c>
       <c r="C59">
-        <v>24205.3184745978</v>
+        <v>22605.35988045538</v>
       </c>
       <c r="D59">
-        <v>47628.88884325582</v>
+        <v>46632.82095733547</v>
       </c>
       <c r="E59">
-        <v>454.4995464509775</v>
+        <v>1058.390254673053</v>
       </c>
       <c r="F59">
-        <v>34421.77036865801</v>
+        <v>35025.66107688009</v>
       </c>
       <c r="G59">
         <v>10998.2</v>
@@ -6131,45 +6131,45 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M59">
-        <v>2654.984804997396</v>
+        <v>2799.635336802089</v>
       </c>
       <c r="N59">
-        <v>3362.033562349544</v>
+        <v>3217.383030544851</v>
       </c>
       <c r="O59">
-        <v>672.4067124699088</v>
+        <v>643.4766061089703</v>
       </c>
       <c r="P59">
-        <v>2689.626849879635</v>
+        <v>2573.906424435881</v>
       </c>
       <c r="Q59">
-        <v>7533.526849879635</v>
+        <v>7417.80642443588</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1703258115858688</v>
+        <v>0.1730029224444278</v>
       </c>
       <c r="T59">
-        <v>1.926374701279569</v>
+        <v>1.967788754838197</v>
       </c>
       <c r="U59">
-        <v>0.07713097776675758</v>
+        <v>0.07993097776675759</v>
       </c>
       <c r="V59">
         <v>0.2</v>
       </c>
       <c r="W59">
-        <v>0.06170478221340606</v>
+        <v>0.06394478221340608</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y59">
-        <v>2.266309907318977</v>
+        <v>2.149215038205632</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6177,22 +6177,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1097492011104352</v>
+        <v>0.1098097773773053</v>
       </c>
       <c r="C60">
-        <v>22605.35988045541</v>
+        <v>21957.33775476929</v>
       </c>
       <c r="D60">
-        <v>46632.82095733549</v>
+        <v>46588.68953987143</v>
       </c>
       <c r="E60">
-        <v>1058.390254673046</v>
+        <v>1662.280962895114</v>
       </c>
       <c r="F60">
-        <v>35025.66107688008</v>
+        <v>35629.55178510215</v>
       </c>
       <c r="G60">
         <v>10998.2</v>
@@ -6213,28 +6213,28 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M60">
-        <v>2799.635336802089</v>
+        <v>2847.904911574538</v>
       </c>
       <c r="N60">
-        <v>3217.383030544851</v>
+        <v>3169.113455772402</v>
       </c>
       <c r="O60">
-        <v>643.4766061089704</v>
+        <v>633.8226911544804</v>
       </c>
       <c r="P60">
-        <v>2573.906424435881</v>
+        <v>2535.290764617921</v>
       </c>
       <c r="Q60">
-        <v>7417.806424435881</v>
+        <v>7379.190764617921</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1730029224444277</v>
+        <v>0.1758106240765749</v>
       </c>
       <c r="T60">
-        <v>1.967788754838196</v>
+        <v>2.011223006131392</v>
       </c>
       <c r="U60">
         <v>0.07993097776675759</v>
@@ -6251,7 +6251,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>2.149215038205632</v>
+        <v>2.112787664676723</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6259,22 +6259,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1098097773773053</v>
+        <v>0.1098703536441754</v>
       </c>
       <c r="C61">
-        <v>21957.33775476929</v>
+        <v>21309.39907849057</v>
       </c>
       <c r="D61">
-        <v>46588.68953987143</v>
+        <v>46544.64157181479</v>
       </c>
       <c r="E61">
-        <v>1662.280962895114</v>
+        <v>2266.171671117183</v>
       </c>
       <c r="F61">
-        <v>35629.55178510215</v>
+        <v>36233.44249332422</v>
       </c>
       <c r="G61">
         <v>10998.2</v>
@@ -6295,28 +6295,28 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M61">
-        <v>2847.904911574538</v>
+        <v>2896.174486346988</v>
       </c>
       <c r="N61">
-        <v>3169.113455772402</v>
+        <v>3120.843880999952</v>
       </c>
       <c r="O61">
-        <v>633.8226911544804</v>
+        <v>624.1687761999906</v>
       </c>
       <c r="P61">
-        <v>2535.290764617921</v>
+        <v>2496.675104799962</v>
       </c>
       <c r="Q61">
-        <v>7379.190764617921</v>
+        <v>7340.575104799962</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1758106240765749</v>
+        <v>0.1787587107903295</v>
       </c>
       <c r="T61">
-        <v>2.011223006131392</v>
+        <v>2.056828969989247</v>
       </c>
       <c r="U61">
         <v>0.07993097776675759</v>
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>2.112787664676723</v>
+        <v>2.077574536932112</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6341,22 +6341,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1098703536441754</v>
+        <v>0.1099309299110456</v>
       </c>
       <c r="C62">
-        <v>21309.39907849057</v>
+        <v>20661.54361514737</v>
       </c>
       <c r="D62">
-        <v>46544.64157181479</v>
+        <v>46500.67681669367</v>
       </c>
       <c r="E62">
-        <v>2266.171671117183</v>
+        <v>2870.062379339259</v>
       </c>
       <c r="F62">
-        <v>36233.44249332422</v>
+        <v>36837.33320154629</v>
       </c>
       <c r="G62">
         <v>10998.2</v>
@@ -6377,28 +6377,28 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M62">
-        <v>2896.174486346988</v>
+        <v>2944.444061119438</v>
       </c>
       <c r="N62">
-        <v>3120.843880999952</v>
+        <v>3072.574306227502</v>
       </c>
       <c r="O62">
-        <v>624.1687761999906</v>
+        <v>614.5148612455005</v>
       </c>
       <c r="P62">
-        <v>2496.675104799962</v>
+        <v>2458.059444982001</v>
       </c>
       <c r="Q62">
-        <v>7340.575104799962</v>
+        <v>7301.959444982002</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1787587107903295</v>
+        <v>0.1818579814381227</v>
       </c>
       <c r="T62">
-        <v>2.056828969989247</v>
+        <v>2.104773701224427</v>
       </c>
       <c r="U62">
         <v>0.07993097776675759</v>
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>2.077574536932112</v>
+        <v>2.043515937966011</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1099309299110456</v>
+        <v>0.1099915061779157</v>
       </c>
       <c r="C63">
-        <v>20661.54361514737</v>
+        <v>20013.77112916048</v>
       </c>
       <c r="D63">
-        <v>46500.67681669367</v>
+        <v>46456.79503892884</v>
       </c>
       <c r="E63">
-        <v>2870.062379339259</v>
+        <v>3473.953087561327</v>
       </c>
       <c r="F63">
-        <v>36837.33320154629</v>
+        <v>37441.22390976836</v>
       </c>
       <c r="G63">
         <v>10998.2</v>
@@ -6459,28 +6459,28 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M63">
-        <v>2944.444061119438</v>
+        <v>2992.713635891888</v>
       </c>
       <c r="N63">
-        <v>3072.574306227502</v>
+        <v>3024.304731455052</v>
       </c>
       <c r="O63">
-        <v>614.5148612455005</v>
+        <v>604.8609462910105</v>
       </c>
       <c r="P63">
-        <v>2458.059444982001</v>
+        <v>2419.443785164042</v>
       </c>
       <c r="Q63">
-        <v>7301.959444982002</v>
+        <v>7263.343785164041</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1818579814381227</v>
+        <v>0.1851203715936945</v>
       </c>
       <c r="T63">
-        <v>2.104773701224427</v>
+        <v>2.155241839366723</v>
       </c>
       <c r="U63">
         <v>0.07993097776675759</v>
@@ -6497,7 +6497,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>2.043515937966011</v>
+        <v>2.010556003482689</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6505,22 +6505,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1099915061779157</v>
+        <v>0.1139832824447858</v>
       </c>
       <c r="C64">
-        <v>20013.77112916048</v>
+        <v>16690.07689693796</v>
       </c>
       <c r="D64">
-        <v>46456.79503892884</v>
+        <v>43736.99151492839</v>
       </c>
       <c r="E64">
-        <v>3473.953087561327</v>
+        <v>4077.843795783396</v>
       </c>
       <c r="F64">
-        <v>37441.22390976836</v>
+        <v>38045.11461799043</v>
       </c>
       <c r="G64">
         <v>10998.2</v>
@@ -6541,45 +6541,45 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M64">
-        <v>2992.713635891888</v>
+        <v>3337.735104684663</v>
       </c>
       <c r="N64">
-        <v>3024.304731455052</v>
+        <v>2679.283262662277</v>
       </c>
       <c r="O64">
-        <v>604.8609462910105</v>
+        <v>535.8566525324554</v>
       </c>
       <c r="P64">
-        <v>2419.443785164042</v>
+        <v>2143.426610129822</v>
       </c>
       <c r="Q64">
-        <v>7263.343785164041</v>
+        <v>6987.326610129821</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1851203715936945</v>
+        <v>0.188559107163081</v>
       </c>
       <c r="T64">
-        <v>2.155241839366723</v>
+        <v>2.208437984976169</v>
       </c>
       <c r="U64">
-        <v>0.07993097776675759</v>
+        <v>0.08773097776675759</v>
       </c>
       <c r="V64">
         <v>0.2</v>
       </c>
       <c r="W64">
-        <v>0.06394478221340608</v>
+        <v>0.07018478221340607</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y64">
-        <v>2.010556003482689</v>
+        <v>1.802724955285331</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6587,22 +6587,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1139832824447858</v>
+        <v>0.1141062587116559</v>
       </c>
       <c r="C65">
-        <v>16690.07689693796</v>
+        <v>16007.44359554677</v>
       </c>
       <c r="D65">
-        <v>43736.99151492839</v>
+        <v>43658.24892175928</v>
       </c>
       <c r="E65">
-        <v>4077.843795783396</v>
+        <v>4681.734504005472</v>
       </c>
       <c r="F65">
-        <v>38045.11461799043</v>
+        <v>38649.00532621251</v>
       </c>
       <c r="G65">
         <v>10998.2</v>
@@ -6623,28 +6623,28 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M65">
-        <v>3337.735104684663</v>
+        <v>3390.715026981245</v>
       </c>
       <c r="N65">
-        <v>2679.283262662277</v>
+        <v>2626.303340365695</v>
       </c>
       <c r="O65">
-        <v>535.8566525324554</v>
+        <v>525.2606680731391</v>
       </c>
       <c r="P65">
-        <v>2143.426610129822</v>
+        <v>2101.042672292556</v>
       </c>
       <c r="Q65">
-        <v>6987.326610129821</v>
+        <v>6944.942672292555</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.188559107163081</v>
+        <v>0.1921888835974334</v>
       </c>
       <c r="T65">
-        <v>2.208437984976169</v>
+        <v>2.264589472008363</v>
       </c>
       <c r="U65">
         <v>0.08773097776675759</v>
@@ -6661,7 +6661,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>1.802724955285331</v>
+        <v>1.774557377858998</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6669,22 +6669,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1141062587116559</v>
+        <v>0.1162572349785261</v>
       </c>
       <c r="C66">
-        <v>16007.44359554677</v>
+        <v>14070.71805052712</v>
       </c>
       <c r="D66">
-        <v>43658.24892175928</v>
+        <v>42325.4140849617</v>
       </c>
       <c r="E66">
-        <v>4681.734504005472</v>
+        <v>5285.62521222754</v>
       </c>
       <c r="F66">
-        <v>38649.00532621251</v>
+        <v>39252.89603443458</v>
       </c>
       <c r="G66">
         <v>10998.2</v>
@@ -6705,45 +6705,45 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M66">
-        <v>3390.715026981245</v>
+        <v>3596.781243812121</v>
       </c>
       <c r="N66">
-        <v>2626.303340365695</v>
+        <v>2420.237123534819</v>
       </c>
       <c r="O66">
-        <v>525.2606680731391</v>
+        <v>484.0474247069637</v>
       </c>
       <c r="P66">
-        <v>2101.042672292556</v>
+        <v>1936.189698827855</v>
       </c>
       <c r="Q66">
-        <v>6944.942672292555</v>
+        <v>6780.089698827855</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1921888835974334</v>
+        <v>0.1960260758280346</v>
       </c>
       <c r="T66">
-        <v>2.264589472008363</v>
+        <v>2.323949615442396</v>
       </c>
       <c r="U66">
-        <v>0.08773097776675759</v>
+        <v>0.09163097776675758</v>
       </c>
       <c r="V66">
         <v>0.2</v>
       </c>
       <c r="W66">
-        <v>0.07018478221340607</v>
+        <v>0.07330478221340607</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y66">
-        <v>1.774557377858998</v>
+        <v>1.672889719856769</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6751,22 +6751,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1162572349785261</v>
+        <v>0.1164114112453962</v>
       </c>
       <c r="C67">
-        <v>14070.71805052712</v>
+        <v>13374.41204820092</v>
       </c>
       <c r="D67">
-        <v>42325.4140849617</v>
+        <v>42232.99879085756</v>
       </c>
       <c r="E67">
-        <v>5285.62521222754</v>
+        <v>5889.515920449609</v>
       </c>
       <c r="F67">
-        <v>39252.89603443458</v>
+        <v>39856.78674265664</v>
       </c>
       <c r="G67">
         <v>10998.2</v>
@@ -6787,28 +6787,28 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M67">
-        <v>3596.781243812121</v>
+        <v>3652.116339870769</v>
       </c>
       <c r="N67">
-        <v>2420.237123534819</v>
+        <v>2364.902027476171</v>
       </c>
       <c r="O67">
-        <v>484.0474247069637</v>
+        <v>472.9804054952342</v>
       </c>
       <c r="P67">
-        <v>1936.189698827855</v>
+        <v>1891.921621980937</v>
       </c>
       <c r="Q67">
-        <v>6780.089698827855</v>
+        <v>6735.821621980936</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1960260758280346</v>
+        <v>0.2000889852486711</v>
       </c>
       <c r="T67">
-        <v>2.323949615442396</v>
+        <v>2.386801532019607</v>
       </c>
       <c r="U67">
         <v>0.09163097776675758</v>
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>1.672889719856769</v>
+        <v>1.647542905919545</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6833,22 +6833,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1164114112453962</v>
+        <v>0.1165655875122663</v>
       </c>
       <c r="C68">
-        <v>13374.41204820092</v>
+        <v>12678.50873440022</v>
       </c>
       <c r="D68">
-        <v>42232.99879085756</v>
+        <v>42140.98618527894</v>
       </c>
       <c r="E68">
-        <v>5889.515920449609</v>
+        <v>6493.406628671684</v>
       </c>
       <c r="F68">
-        <v>39856.78674265664</v>
+        <v>40460.67745087872</v>
       </c>
       <c r="G68">
         <v>10998.2</v>
@@ -6869,28 +6869,28 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M68">
-        <v>3652.116339870769</v>
+        <v>3707.451435929418</v>
       </c>
       <c r="N68">
-        <v>2364.902027476171</v>
+        <v>2309.566931417522</v>
       </c>
       <c r="O68">
-        <v>472.9804054952342</v>
+        <v>461.9133862835045</v>
       </c>
       <c r="P68">
-        <v>1891.921621980937</v>
+        <v>1847.653545134018</v>
       </c>
       <c r="Q68">
-        <v>6735.821621980936</v>
+        <v>6691.553545134017</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2000889852486711</v>
+        <v>0.2043981316038916</v>
       </c>
       <c r="T68">
-        <v>2.386801532019607</v>
+        <v>2.453462655662105</v>
       </c>
       <c r="U68">
         <v>0.09163097776675758</v>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>1.647542905919545</v>
+        <v>1.62295271329388</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6915,22 +6915,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1165655875122663</v>
+        <v>0.1167197637791364</v>
       </c>
       <c r="C69">
-        <v>12678.50873440022</v>
+        <v>11983.00548284673</v>
       </c>
       <c r="D69">
-        <v>42140.98618527894</v>
+        <v>42049.37364194751</v>
       </c>
       <c r="E69">
-        <v>6493.406628671684</v>
+        <v>7097.297336893753</v>
       </c>
       <c r="F69">
-        <v>40460.67745087872</v>
+        <v>41064.56815910079</v>
       </c>
       <c r="G69">
         <v>10998.2</v>
@@ -6951,28 +6951,28 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M69">
-        <v>3707.451435929418</v>
+        <v>3762.786531988066</v>
       </c>
       <c r="N69">
-        <v>2309.566931417522</v>
+        <v>2254.231835358874</v>
       </c>
       <c r="O69">
-        <v>461.9133862835045</v>
+        <v>450.8463670717749</v>
       </c>
       <c r="P69">
-        <v>1847.653545134018</v>
+        <v>1803.385468287099</v>
       </c>
       <c r="Q69">
-        <v>6691.553545134017</v>
+        <v>6647.285468287099</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2043981316038916</v>
+        <v>0.2089765996063134</v>
       </c>
       <c r="T69">
-        <v>2.453462655662105</v>
+        <v>2.524290099532257</v>
       </c>
       <c r="U69">
         <v>0.09163097776675758</v>
@@ -6989,7 +6989,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>1.62295271329388</v>
+        <v>1.599085761627794</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6997,22 +6997,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1167197637791364</v>
+        <v>0.1168739400460065</v>
       </c>
       <c r="C70">
-        <v>11983.00548284673</v>
+        <v>11287.89969005011</v>
       </c>
       <c r="D70">
-        <v>42049.37364194751</v>
+        <v>41958.15855737297</v>
       </c>
       <c r="E70">
-        <v>7097.297336893753</v>
+        <v>7701.188045115821</v>
       </c>
       <c r="F70">
-        <v>41064.56815910079</v>
+        <v>41668.45886732286</v>
       </c>
       <c r="G70">
         <v>10998.2</v>
@@ -7033,28 +7033,28 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M70">
-        <v>3762.786531988066</v>
+        <v>3818.121628046713</v>
       </c>
       <c r="N70">
-        <v>2254.231835358874</v>
+        <v>2198.896739300227</v>
       </c>
       <c r="O70">
-        <v>450.8463670717749</v>
+        <v>439.7793478600454</v>
       </c>
       <c r="P70">
-        <v>1803.385468287099</v>
+        <v>1759.117391440181</v>
       </c>
       <c r="Q70">
-        <v>6647.285468287099</v>
+        <v>6603.017391440181</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2089765996063134</v>
+        <v>0.2138504526411495</v>
       </c>
       <c r="T70">
-        <v>2.524290099532257</v>
+        <v>2.599687055910163</v>
       </c>
       <c r="U70">
         <v>0.09163097776675758</v>
@@ -7071,7 +7071,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>1.599085761627794</v>
+        <v>1.575910605662174</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7079,22 +7079,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1168739400460065</v>
+        <v>0.1170281163128767</v>
       </c>
       <c r="C71">
-        <v>11287.89969005011</v>
+        <v>10593.18877506158</v>
       </c>
       <c r="D71">
-        <v>41958.15855737297</v>
+        <v>41867.33835060651</v>
       </c>
       <c r="E71">
-        <v>7701.188045115821</v>
+        <v>8305.078753337897</v>
       </c>
       <c r="F71">
-        <v>41668.45886732286</v>
+        <v>42272.34957554493</v>
       </c>
       <c r="G71">
         <v>10998.2</v>
@@ -7115,28 +7115,28 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M71">
-        <v>3818.121628046713</v>
+        <v>3873.456724105362</v>
       </c>
       <c r="N71">
-        <v>2198.896739300227</v>
+        <v>2143.561643241578</v>
       </c>
       <c r="O71">
-        <v>439.7793478600454</v>
+        <v>428.7123286483156</v>
       </c>
       <c r="P71">
-        <v>1759.117391440181</v>
+        <v>1714.849314593263</v>
       </c>
       <c r="Q71">
-        <v>6603.017391440181</v>
+        <v>6558.749314593262</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2138504526411495</v>
+        <v>0.2190492292116414</v>
       </c>
       <c r="T71">
-        <v>2.599687055910163</v>
+        <v>2.680110476046594</v>
       </c>
       <c r="U71">
         <v>0.09163097776675758</v>
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>1.575910605662174</v>
+        <v>1.553397597009857</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7161,22 +7161,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1170281163128767</v>
+        <v>0.1171822925797468</v>
       </c>
       <c r="C72">
-        <v>10593.18877506158</v>
+        <v>9898.870179230355</v>
       </c>
       <c r="D72">
-        <v>41867.33835060651</v>
+        <v>41776.91046299735</v>
       </c>
       <c r="E72">
-        <v>8305.078753337897</v>
+        <v>8908.969461559966</v>
       </c>
       <c r="F72">
-        <v>42272.34957554493</v>
+        <v>42876.240283767</v>
       </c>
       <c r="G72">
         <v>10998.2</v>
@@ -7197,28 +7197,28 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M72">
-        <v>3873.456724105362</v>
+        <v>3928.79182016401</v>
       </c>
       <c r="N72">
-        <v>2143.561643241578</v>
+        <v>2088.226547182931</v>
       </c>
       <c r="O72">
-        <v>428.7123286483156</v>
+        <v>417.6453094365861</v>
       </c>
       <c r="P72">
-        <v>1714.849314593263</v>
+        <v>1670.581237746344</v>
       </c>
       <c r="Q72">
-        <v>6558.749314593262</v>
+        <v>6514.481237746344</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2190492292116414</v>
+        <v>0.2246065420973397</v>
       </c>
       <c r="T72">
-        <v>2.680110476046594</v>
+        <v>2.766080338951057</v>
       </c>
       <c r="U72">
         <v>0.09163097776675758</v>
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>1.553397597009857</v>
+        <v>1.531518757615352</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7243,22 +7243,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1171822925797468</v>
+        <v>0.1173364688466169</v>
       </c>
       <c r="C73">
-        <v>9898.870179230362</v>
+        <v>9204.941365963401</v>
       </c>
       <c r="D73">
-        <v>41776.91046299735</v>
+        <v>41686.87235795247</v>
       </c>
       <c r="E73">
-        <v>8908.969461559958</v>
+        <v>9512.860169782027</v>
       </c>
       <c r="F73">
-        <v>42876.24028376699</v>
+        <v>43480.13099198906</v>
       </c>
       <c r="G73">
         <v>10998.2</v>
@@ -7279,28 +7279,28 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M73">
-        <v>3928.791820164009</v>
+        <v>3984.126916222657</v>
       </c>
       <c r="N73">
-        <v>2088.226547182931</v>
+        <v>2032.891451124283</v>
       </c>
       <c r="O73">
-        <v>417.6453094365862</v>
+        <v>406.5782902248567</v>
       </c>
       <c r="P73">
-        <v>1670.581237746345</v>
+        <v>1626.313160899427</v>
       </c>
       <c r="Q73">
-        <v>6514.481237746344</v>
+        <v>6470.213160899426</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2246065420973396</v>
+        <v>0.2305608059034448</v>
       </c>
       <c r="T73">
-        <v>2.766080338951055</v>
+        <v>2.858190906348693</v>
       </c>
       <c r="U73">
         <v>0.09163097776675758</v>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>1.531518757615352</v>
+        <v>1.510247663759583</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7325,22 +7325,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1173364688466169</v>
+        <v>0.125783445113487</v>
       </c>
       <c r="C74">
-        <v>9204.941365963401</v>
+        <v>4198.539351207328</v>
       </c>
       <c r="D74">
-        <v>41686.87235795247</v>
+        <v>37284.36105141846</v>
       </c>
       <c r="E74">
-        <v>9512.860169782027</v>
+        <v>10116.7508780041</v>
       </c>
       <c r="F74">
-        <v>43480.13099198906</v>
+        <v>44084.02170021114</v>
       </c>
       <c r="G74">
         <v>10998.2</v>
@@ -7361,45 +7361,45 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M74">
-        <v>3984.126916222657</v>
+        <v>4665.455120424303</v>
       </c>
       <c r="N74">
-        <v>2032.891451124283</v>
+        <v>1351.563246922637</v>
       </c>
       <c r="O74">
-        <v>406.5782902248567</v>
+        <v>270.3126493845273</v>
       </c>
       <c r="P74">
-        <v>1626.313160899427</v>
+        <v>1081.250597538109</v>
       </c>
       <c r="Q74">
-        <v>6470.213160899426</v>
+        <v>5925.150597538109</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2305608059034448</v>
+        <v>0.23695612628778</v>
       </c>
       <c r="T74">
-        <v>2.858190906348693</v>
+        <v>2.957124478738748</v>
       </c>
       <c r="U74">
-        <v>0.09163097776675758</v>
+        <v>0.1058309777667576</v>
       </c>
       <c r="V74">
         <v>0.2</v>
       </c>
       <c r="W74">
-        <v>0.07330478221340607</v>
+        <v>0.08466478221340606</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y74">
-        <v>1.510247663759583</v>
+        <v>1.289695905766149</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7407,22 +7407,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.125783445113487</v>
+        <v>0.1260512213803572</v>
       </c>
       <c r="C75">
-        <v>4198.539351207328</v>
+        <v>3470.240978612557</v>
       </c>
       <c r="D75">
-        <v>37284.36105141846</v>
+        <v>37159.95338704577</v>
       </c>
       <c r="E75">
-        <v>10116.7508780041</v>
+        <v>10720.64158622617</v>
       </c>
       <c r="F75">
-        <v>44084.02170021114</v>
+        <v>44687.91240843321</v>
       </c>
       <c r="G75">
         <v>10998.2</v>
@@ -7443,28 +7443,28 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M75">
-        <v>4665.455120424303</v>
+        <v>4729.365464539705</v>
       </c>
       <c r="N75">
-        <v>1351.563246922637</v>
+        <v>1287.652902807235</v>
       </c>
       <c r="O75">
-        <v>270.3126493845273</v>
+        <v>257.5305805614471</v>
       </c>
       <c r="P75">
-        <v>1081.250597538109</v>
+        <v>1030.122322245788</v>
       </c>
       <c r="Q75">
-        <v>5925.150597538109</v>
+        <v>5874.022322245788</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.23695612628778</v>
+        <v>0.2438433943939872</v>
       </c>
       <c r="T75">
-        <v>2.957124478738748</v>
+        <v>3.063668325928038</v>
       </c>
       <c r="U75">
         <v>0.1058309777667576</v>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>1.289695905766149</v>
+        <v>1.272267582715255</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7489,22 +7489,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1260512213803572</v>
+        <v>0.1263189976472273</v>
       </c>
       <c r="C76">
-        <v>3470.240978612557</v>
+        <v>2742.770073346226</v>
       </c>
       <c r="D76">
-        <v>37159.95338704577</v>
+        <v>37036.3731900015</v>
       </c>
       <c r="E76">
-        <v>10720.64158622617</v>
+        <v>11324.53229444825</v>
       </c>
       <c r="F76">
-        <v>44687.91240843321</v>
+        <v>45291.80311665528</v>
       </c>
       <c r="G76">
         <v>10998.2</v>
@@ -7525,28 +7525,28 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M76">
-        <v>4729.365464539705</v>
+        <v>4793.275808655107</v>
       </c>
       <c r="N76">
-        <v>1287.652902807235</v>
+        <v>1223.742558691833</v>
       </c>
       <c r="O76">
-        <v>257.5305805614471</v>
+        <v>244.7485117383667</v>
       </c>
       <c r="P76">
-        <v>1030.122322245788</v>
+        <v>978.9940469534667</v>
       </c>
       <c r="Q76">
-        <v>5874.022322245788</v>
+        <v>5822.894046953466</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2438433943939872</v>
+        <v>0.251281643948691</v>
       </c>
       <c r="T76">
-        <v>3.063668325928038</v>
+        <v>3.178735680892472</v>
       </c>
       <c r="U76">
         <v>0.1058309777667576</v>
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>1.272267582715255</v>
+        <v>1.255304014945718</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7571,22 +7571,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1263189976472273</v>
+        <v>0.1447090563326442</v>
       </c>
       <c r="C77">
-        <v>2742.770073346226</v>
+        <v>-4747.255248965157</v>
       </c>
       <c r="D77">
-        <v>37036.3731900015</v>
+        <v>30150.23857591219</v>
       </c>
       <c r="E77">
-        <v>11324.53229444825</v>
+        <v>11928.42300267032</v>
       </c>
       <c r="F77">
-        <v>45291.80311665528</v>
+        <v>45895.69382487735</v>
       </c>
       <c r="G77">
         <v>10998.2</v>
@@ -7607,45 +7607,45 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M77">
-        <v>4793.275808655107</v>
+        <v>6169.802996162</v>
       </c>
       <c r="N77">
-        <v>1223.742558691833</v>
+        <v>-152.7846288150604</v>
       </c>
       <c r="O77">
-        <v>244.7485117383667</v>
+        <v>-30.55692576301208</v>
       </c>
       <c r="P77">
-        <v>978.9940469534667</v>
+        <v>-122.2277030520483</v>
       </c>
       <c r="Q77">
-        <v>5822.894046953466</v>
+        <v>4721.672296947952</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.251281643948691</v>
+        <v>0.2602875871847698</v>
       </c>
       <c r="T77">
-        <v>3.178735680892472</v>
+        <v>3.318054758521442</v>
       </c>
       <c r="U77">
-        <v>0.1058309777667576</v>
+        <v>0.1344309777667576</v>
       </c>
       <c r="V77">
-        <v>0.2</v>
+        <v>0.1950473417413781</v>
       </c>
       <c r="W77">
-        <v>0.08466478221340606</v>
+        <v>0.1082105729056572</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y77">
-        <v>1.255304014945718</v>
+        <v>0.9752367087068904</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7653,22 +7653,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1447090563326442</v>
+        <v>0.1455953661103118</v>
       </c>
       <c r="C78">
-        <v>-4747.255248965157</v>
+        <v>-5618.918422887713</v>
       </c>
       <c r="D78">
-        <v>30150.23857591219</v>
+        <v>29882.46611021171</v>
       </c>
       <c r="E78">
-        <v>11928.42300267032</v>
+        <v>12532.31371089238</v>
       </c>
       <c r="F78">
-        <v>45895.69382487735</v>
+        <v>46499.58453309942</v>
       </c>
       <c r="G78">
         <v>10998.2</v>
@@ -7689,37 +7689,37 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M78">
-        <v>6169.802996162</v>
+        <v>6250.984614532553</v>
       </c>
       <c r="N78">
-        <v>-152.7846288150604</v>
+        <v>-233.9662471856127</v>
       </c>
       <c r="O78">
-        <v>-30.55692576301208</v>
+        <v>-46.79324943712254</v>
       </c>
       <c r="P78">
-        <v>-122.2277030520483</v>
+        <v>-187.1729977484902</v>
       </c>
       <c r="Q78">
-        <v>4721.672296947952</v>
+        <v>4656.727002251509</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2602875871847698</v>
+        <v>0.2696131344536729</v>
       </c>
       <c r="T78">
-        <v>3.318054758521442</v>
+        <v>3.46231800889194</v>
       </c>
       <c r="U78">
         <v>0.1344309777667576</v>
       </c>
       <c r="V78">
-        <v>0.1950473417413781</v>
+        <v>0.1925142593811004</v>
       </c>
       <c r="W78">
-        <v>0.1082105729056572</v>
+        <v>0.1085510976441131</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.9752367087068904</v>
+        <v>0.9625712969055022</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7735,22 +7735,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1455953661103118</v>
+        <v>0.1464816758879794</v>
       </c>
       <c r="C79">
-        <v>-5618.918422887713</v>
+        <v>-6485.867146987162</v>
       </c>
       <c r="D79">
-        <v>29882.46611021171</v>
+        <v>29619.40809433433</v>
       </c>
       <c r="E79">
-        <v>12532.31371089238</v>
+        <v>13136.20441911446</v>
       </c>
       <c r="F79">
-        <v>46499.58453309942</v>
+        <v>47103.4752413215</v>
       </c>
       <c r="G79">
         <v>10998.2</v>
@@ -7771,37 +7771,37 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M79">
-        <v>6250.984614532553</v>
+        <v>6332.166232903106</v>
       </c>
       <c r="N79">
-        <v>-233.9662471856127</v>
+        <v>-315.1478655561659</v>
       </c>
       <c r="O79">
-        <v>-46.79324943712254</v>
+        <v>-63.02957311123319</v>
       </c>
       <c r="P79">
-        <v>-187.1729977484902</v>
+        <v>-252.1182924449327</v>
       </c>
       <c r="Q79">
-        <v>4656.727002251509</v>
+        <v>4591.781707555067</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2696131344536729</v>
+        <v>0.2797864587470216</v>
       </c>
       <c r="T79">
-        <v>3.46231800889194</v>
+        <v>3.61969610020521</v>
       </c>
       <c r="U79">
         <v>0.1344309777667576</v>
       </c>
       <c r="V79">
-        <v>0.1925142593811004</v>
+        <v>0.1900461278505735</v>
       </c>
       <c r="W79">
-        <v>0.1085510976441131</v>
+        <v>0.1088828909790188</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.9625712969055022</v>
+        <v>0.9502306392528674</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7817,22 +7817,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1464816758879794</v>
+        <v>0.147367985665647</v>
       </c>
       <c r="C80">
-        <v>-6485.867146987162</v>
+        <v>-7348.224839965165</v>
       </c>
       <c r="D80">
-        <v>29619.40809433433</v>
+        <v>29360.94110957839</v>
       </c>
       <c r="E80">
-        <v>13136.20441911446</v>
+        <v>13740.09512733653</v>
       </c>
       <c r="F80">
-        <v>47103.4752413215</v>
+        <v>47707.36594954356</v>
       </c>
       <c r="G80">
         <v>10998.2</v>
@@ -7853,37 +7853,37 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M80">
-        <v>6332.166232903106</v>
+        <v>6413.347851273658</v>
       </c>
       <c r="N80">
-        <v>-315.1478655561659</v>
+        <v>-396.3294839267182</v>
       </c>
       <c r="O80">
-        <v>-63.02957311123319</v>
+        <v>-79.26589678534366</v>
       </c>
       <c r="P80">
-        <v>-252.1182924449327</v>
+        <v>-317.0635871413746</v>
       </c>
       <c r="Q80">
-        <v>4591.781707555067</v>
+        <v>4526.836412858625</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2797864587470216</v>
+        <v>0.2909286710683084</v>
       </c>
       <c r="T80">
-        <v>3.61969610020521</v>
+        <v>3.792062581167363</v>
       </c>
       <c r="U80">
         <v>0.1344309777667576</v>
       </c>
       <c r="V80">
-        <v>0.1900461278505735</v>
+        <v>0.1876404806625916</v>
       </c>
       <c r="W80">
-        <v>0.1088828909790188</v>
+        <v>0.109206284482661</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.9502306392528674</v>
+        <v>0.9382024033129578</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7899,22 +7899,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.147367985665647</v>
+        <v>0.1482542954433145</v>
       </c>
       <c r="C81">
-        <v>-7348.224839965165</v>
+        <v>-8206.1106498503</v>
       </c>
       <c r="D81">
-        <v>29360.94110957839</v>
+        <v>29106.94600791534</v>
       </c>
       <c r="E81">
-        <v>13740.09512733653</v>
+        <v>14343.9858355586</v>
       </c>
       <c r="F81">
-        <v>47707.36594954356</v>
+        <v>48311.25665776563</v>
       </c>
       <c r="G81">
         <v>10998.2</v>
@@ -7935,37 +7935,37 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M81">
-        <v>6413.347851273658</v>
+        <v>6494.529469644211</v>
       </c>
       <c r="N81">
-        <v>-396.3294839267182</v>
+        <v>-477.5111022972706</v>
       </c>
       <c r="O81">
-        <v>-79.26589678534366</v>
+        <v>-95.50222045945412</v>
       </c>
       <c r="P81">
-        <v>-317.0635871413746</v>
+        <v>-382.0088818378164</v>
       </c>
       <c r="Q81">
-        <v>4526.836412858625</v>
+        <v>4461.891118162183</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2909286710683084</v>
+        <v>0.3031851046217238</v>
       </c>
       <c r="T81">
-        <v>3.792062581167363</v>
+        <v>3.981665710225731</v>
       </c>
       <c r="U81">
         <v>0.1344309777667576</v>
       </c>
       <c r="V81">
-        <v>0.1876404806625916</v>
+        <v>0.1852949746543092</v>
       </c>
       <c r="W81">
-        <v>0.109206284482661</v>
+        <v>0.1095215931487122</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.9382024033129578</v>
+        <v>0.9264748732715459</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7981,22 +7981,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1482542954433145</v>
+        <v>0.1491406052209821</v>
       </c>
       <c r="C82">
-        <v>-8206.1106498503</v>
+        <v>-9059.639637136948</v>
       </c>
       <c r="D82">
-        <v>29106.94600791534</v>
+        <v>28857.30772885076</v>
       </c>
       <c r="E82">
-        <v>14343.9858355586</v>
+        <v>14947.87654378067</v>
       </c>
       <c r="F82">
-        <v>48311.25665776563</v>
+        <v>48915.14736598771</v>
       </c>
       <c r="G82">
         <v>10998.2</v>
@@ -8017,37 +8017,37 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M82">
-        <v>6494.529469644211</v>
+        <v>6575.711088014764</v>
       </c>
       <c r="N82">
-        <v>-477.5111022972706</v>
+        <v>-558.6927206678238</v>
       </c>
       <c r="O82">
-        <v>-95.50222045945412</v>
+        <v>-111.7385441335648</v>
       </c>
       <c r="P82">
-        <v>-382.0088818378164</v>
+        <v>-446.954176534259</v>
       </c>
       <c r="Q82">
-        <v>4461.891118162183</v>
+        <v>4396.94582346574</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3031851046217238</v>
+        <v>0.3167316890754987</v>
       </c>
       <c r="T82">
-        <v>3.981665710225731</v>
+        <v>4.191227063395506</v>
       </c>
       <c r="U82">
         <v>0.1344309777667576</v>
       </c>
       <c r="V82">
-        <v>0.1852949746543092</v>
+        <v>0.1830073823746263</v>
       </c>
       <c r="W82">
-        <v>0.1095215931487122</v>
+        <v>0.1098291164156017</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.9264748732715459</v>
+        <v>0.9150369118731316</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8063,22 +8063,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1491406052209821</v>
+        <v>0.1500269149986497</v>
       </c>
       <c r="C83">
-        <v>-9059.639637136948</v>
+        <v>-9908.922948580308</v>
       </c>
       <c r="D83">
-        <v>28857.30772885076</v>
+        <v>28611.91512562947</v>
       </c>
       <c r="E83">
-        <v>14947.87654378067</v>
+        <v>15551.76725200274</v>
       </c>
       <c r="F83">
-        <v>48915.14736598771</v>
+        <v>49519.03807420978</v>
       </c>
       <c r="G83">
         <v>10998.2</v>
@@ -8099,37 +8099,37 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M83">
-        <v>6575.711088014764</v>
+        <v>6656.892706385317</v>
       </c>
       <c r="N83">
-        <v>-558.6927206678238</v>
+        <v>-639.874339038377</v>
       </c>
       <c r="O83">
-        <v>-111.7385441335648</v>
+        <v>-127.9748678076754</v>
       </c>
       <c r="P83">
-        <v>-446.954176534259</v>
+        <v>-511.8994712307016</v>
       </c>
       <c r="Q83">
-        <v>4396.94582346574</v>
+        <v>4332.000528769298</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3167316890754987</v>
+        <v>0.3317834495796932</v>
       </c>
       <c r="T83">
-        <v>4.191227063395506</v>
+        <v>4.424073011361925</v>
       </c>
       <c r="U83">
         <v>0.1344309777667576</v>
       </c>
       <c r="V83">
-        <v>0.1830073823746263</v>
+        <v>0.1807755850285943</v>
       </c>
       <c r="W83">
-        <v>0.1098291164156017</v>
+        <v>0.110129139115006</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.9150369118731316</v>
+        <v>0.9038779251429714</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8145,22 +8145,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1500269149986497</v>
+        <v>0.1509132247763173</v>
       </c>
       <c r="C84">
-        <v>-9908.922948580308</v>
+        <v>-10754.06798219868</v>
       </c>
       <c r="D84">
-        <v>28611.91512562947</v>
+        <v>28370.66080023317</v>
       </c>
       <c r="E84">
-        <v>15551.76725200274</v>
+        <v>16155.65796022481</v>
       </c>
       <c r="F84">
-        <v>49519.03807420978</v>
+        <v>50122.92878243185</v>
       </c>
       <c r="G84">
         <v>10998.2</v>
@@ -8181,37 +8181,37 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M84">
-        <v>6656.892706385317</v>
+        <v>6738.074324755869</v>
       </c>
       <c r="N84">
-        <v>-639.874339038377</v>
+        <v>-721.0559574089293</v>
       </c>
       <c r="O84">
-        <v>-127.9748678076754</v>
+        <v>-144.2111914817859</v>
       </c>
       <c r="P84">
-        <v>-511.8994712307016</v>
+        <v>-576.8447659271435</v>
       </c>
       <c r="Q84">
-        <v>4332.000528769298</v>
+        <v>4267.055234072856</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3317834495796932</v>
+        <v>0.3486060054373222</v>
       </c>
       <c r="T84">
-        <v>4.424073011361925</v>
+        <v>4.684312600265567</v>
       </c>
       <c r="U84">
         <v>0.1344309777667576</v>
       </c>
       <c r="V84">
-        <v>0.1807755850285943</v>
+        <v>0.1785975659318643</v>
       </c>
       <c r="W84">
-        <v>0.110129139115006</v>
+        <v>0.1104219323517741</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.9038779251429714</v>
+        <v>0.8929878296593212</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8227,22 +8227,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1509132247763173</v>
+        <v>0.1517995345539849</v>
       </c>
       <c r="C85">
-        <v>-10754.06798219868</v>
+        <v>-11595.17854399786</v>
       </c>
       <c r="D85">
-        <v>28370.66080023317</v>
+        <v>28133.44094665606</v>
       </c>
       <c r="E85">
-        <v>16155.65796022481</v>
+        <v>16759.54866844689</v>
       </c>
       <c r="F85">
-        <v>50122.92878243185</v>
+        <v>50726.81949065392</v>
       </c>
       <c r="G85">
         <v>10998.2</v>
@@ -8263,37 +8263,37 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M85">
-        <v>6738.074324755869</v>
+        <v>6819.255943126423</v>
       </c>
       <c r="N85">
-        <v>-721.0559574089293</v>
+        <v>-802.2375757794825</v>
       </c>
       <c r="O85">
-        <v>-144.2111914817859</v>
+        <v>-160.4475151558965</v>
       </c>
       <c r="P85">
-        <v>-576.8447659271435</v>
+        <v>-641.790060623586</v>
       </c>
       <c r="Q85">
-        <v>4267.055234072856</v>
+        <v>4202.109939376413</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3486060054373222</v>
+        <v>0.3675313807771549</v>
       </c>
       <c r="T85">
-        <v>4.684312600265567</v>
+        <v>4.977082137782166</v>
       </c>
       <c r="U85">
         <v>0.1344309777667576</v>
       </c>
       <c r="V85">
-        <v>0.1785975659318643</v>
+        <v>0.1764714044326754</v>
       </c>
       <c r="W85">
-        <v>0.1104219323517741</v>
+        <v>0.1107077543210001</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.8929878296593212</v>
+        <v>0.8823570221633769</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8309,22 +8309,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1517995345539848</v>
+        <v>0.1526858443316524</v>
       </c>
       <c r="C86">
-        <v>-11595.17854399784</v>
+        <v>-12432.35499689799</v>
       </c>
       <c r="D86">
-        <v>28133.44094665607</v>
+        <v>27900.15520197798</v>
       </c>
       <c r="E86">
-        <v>16759.54866844688</v>
+        <v>17363.43937666895</v>
       </c>
       <c r="F86">
-        <v>50726.81949065391</v>
+        <v>51330.71019887598</v>
       </c>
       <c r="G86">
         <v>10998.2</v>
@@ -8345,37 +8345,37 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M86">
-        <v>6819.255943126422</v>
+        <v>6900.437561496974</v>
       </c>
       <c r="N86">
-        <v>-802.2375757794816</v>
+        <v>-883.4191941500339</v>
       </c>
       <c r="O86">
-        <v>-160.4475151558963</v>
+        <v>-176.6838388300068</v>
       </c>
       <c r="P86">
-        <v>-641.7900606235853</v>
+        <v>-706.7353553200271</v>
       </c>
       <c r="Q86">
-        <v>4202.109939376414</v>
+        <v>4137.164644679972</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3675313807771547</v>
+        <v>0.3889801394956317</v>
       </c>
       <c r="T86">
-        <v>4.977082137782163</v>
+        <v>5.308887613634307</v>
       </c>
       <c r="U86">
         <v>0.1344309777667576</v>
       </c>
       <c r="V86">
-        <v>0.1764714044326754</v>
+        <v>0.1743952702628792</v>
       </c>
       <c r="W86">
-        <v>0.1107077543210001</v>
+        <v>0.1109868510674208</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.882357022163377</v>
+        <v>0.8719763513143961</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8391,22 +8391,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1526858443316524</v>
+        <v>0.15357215410932</v>
       </c>
       <c r="C87">
-        <v>-12432.35499689799</v>
+        <v>-13265.69440231202</v>
       </c>
       <c r="D87">
-        <v>27900.15520197798</v>
+        <v>27670.70650478603</v>
       </c>
       <c r="E87">
-        <v>17363.43937666895</v>
+        <v>17967.33008489101</v>
       </c>
       <c r="F87">
-        <v>51330.71019887598</v>
+        <v>51934.60090709805</v>
       </c>
       <c r="G87">
         <v>10998.2</v>
@@ -8427,37 +8427,37 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M87">
-        <v>6900.437561496974</v>
+        <v>6981.619179867526</v>
       </c>
       <c r="N87">
-        <v>-883.4191941500339</v>
+        <v>-964.6008125205863</v>
       </c>
       <c r="O87">
-        <v>-176.6838388300068</v>
+        <v>-192.9201625041173</v>
       </c>
       <c r="P87">
-        <v>-706.7353553200271</v>
+        <v>-771.680650016469</v>
       </c>
       <c r="Q87">
-        <v>4137.164644679972</v>
+        <v>4072.219349983531</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3889801394956317</v>
+        <v>0.4134930066024625</v>
       </c>
       <c r="T87">
-        <v>5.308887613634307</v>
+        <v>5.688093871751043</v>
       </c>
       <c r="U87">
         <v>0.1344309777667576</v>
       </c>
       <c r="V87">
-        <v>0.1743952702628792</v>
+        <v>0.1723674182830783</v>
       </c>
       <c r="W87">
-        <v>0.1109868510674208</v>
+        <v>0.1112594571918317</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.8719763513143961</v>
+        <v>0.8618370914153916</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8473,22 +8473,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.15357215410932</v>
+        <v>0.1544584638869876</v>
       </c>
       <c r="C88">
-        <v>-13265.69440231202</v>
+        <v>-14095.29065479497</v>
       </c>
       <c r="D88">
-        <v>27670.70650478603</v>
+        <v>27445.00096052516</v>
       </c>
       <c r="E88">
-        <v>17967.33008489101</v>
+        <v>18571.22079311309</v>
       </c>
       <c r="F88">
-        <v>51934.60090709805</v>
+        <v>52538.49161532013</v>
       </c>
       <c r="G88">
         <v>10998.2</v>
@@ -8509,37 +8509,37 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M88">
-        <v>6981.619179867526</v>
+        <v>7062.80079823808</v>
       </c>
       <c r="N88">
-        <v>-964.6008125205863</v>
+        <v>-1045.782430891139</v>
       </c>
       <c r="O88">
-        <v>-192.9201625041173</v>
+        <v>-209.1564861782279</v>
       </c>
       <c r="P88">
-        <v>-771.680650016469</v>
+        <v>-836.6259447129116</v>
       </c>
       <c r="Q88">
-        <v>4072.219349983531</v>
+        <v>4007.274055287088</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4134930066024625</v>
+        <v>0.4417770840334211</v>
       </c>
       <c r="T88">
-        <v>5.688093871751043</v>
+        <v>6.125639554193431</v>
       </c>
       <c r="U88">
         <v>0.1344309777667576</v>
       </c>
       <c r="V88">
-        <v>0.1723674182830783</v>
+        <v>0.1703861835901694</v>
       </c>
       <c r="W88">
-        <v>0.1112594571918317</v>
+        <v>0.1115257965087849</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.8618370914153916</v>
+        <v>0.8519309179508467</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8555,22 +8555,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1544584638869876</v>
+        <v>0.1553447736646552</v>
       </c>
       <c r="C89">
-        <v>-14095.29065479497</v>
+        <v>-14921.23461015663</v>
       </c>
       <c r="D89">
-        <v>27445.00096052516</v>
+        <v>27222.94771338556</v>
       </c>
       <c r="E89">
-        <v>18571.22079311309</v>
+        <v>19175.11150133516</v>
       </c>
       <c r="F89">
-        <v>52538.49161532013</v>
+        <v>53142.3823235422</v>
       </c>
       <c r="G89">
         <v>10998.2</v>
@@ -8591,37 +8591,37 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M89">
-        <v>7062.80079823808</v>
+        <v>7143.982416608632</v>
       </c>
       <c r="N89">
-        <v>-1045.782430891139</v>
+        <v>-1126.964049261692</v>
       </c>
       <c r="O89">
-        <v>-209.1564861782279</v>
+        <v>-225.3928098523384</v>
       </c>
       <c r="P89">
-        <v>-836.6259447129116</v>
+        <v>-901.5712394093534</v>
       </c>
       <c r="Q89">
-        <v>4007.274055287088</v>
+        <v>3942.328760590646</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4417770840334211</v>
+        <v>0.4747751743695396</v>
       </c>
       <c r="T89">
-        <v>6.125639554193431</v>
+        <v>6.636109517042884</v>
       </c>
       <c r="U89">
         <v>0.1344309777667576</v>
       </c>
       <c r="V89">
-        <v>0.1703861835901694</v>
+        <v>0.1684499769584629</v>
       </c>
       <c r="W89">
-        <v>0.1115257965087849</v>
+        <v>0.1117860826594436</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.8519309179508467</v>
+        <v>0.8422498847923144</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8637,22 +8637,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1553447736646552</v>
+        <v>0.1562310834423227</v>
       </c>
       <c r="C90">
-        <v>-14921.23461015663</v>
+        <v>-15743.61420740521</v>
       </c>
       <c r="D90">
-        <v>27222.94771338556</v>
+        <v>27004.45882435905</v>
       </c>
       <c r="E90">
-        <v>19175.11150133516</v>
+        <v>19779.00220955723</v>
       </c>
       <c r="F90">
-        <v>53142.3823235422</v>
+        <v>53746.27303176426</v>
       </c>
       <c r="G90">
         <v>10998.2</v>
@@ -8673,37 +8673,37 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M90">
-        <v>7143.982416608632</v>
+        <v>7225.164034979184</v>
       </c>
       <c r="N90">
-        <v>-1126.964049261692</v>
+        <v>-1208.145667632244</v>
       </c>
       <c r="O90">
-        <v>-225.3928098523384</v>
+        <v>-241.6291335264488</v>
       </c>
       <c r="P90">
-        <v>-901.5712394093534</v>
+        <v>-966.5165341057952</v>
       </c>
       <c r="Q90">
-        <v>3942.328760590646</v>
+        <v>3877.383465894204</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4747751743695396</v>
+        <v>0.5137729174940432</v>
       </c>
       <c r="T90">
-        <v>6.636109517042884</v>
+        <v>7.239392200410419</v>
       </c>
       <c r="U90">
         <v>0.1344309777667576</v>
       </c>
       <c r="V90">
-        <v>0.1684499769584629</v>
+        <v>0.1665572805881431</v>
       </c>
       <c r="W90">
-        <v>0.1117860826594436</v>
+        <v>0.1120405196831213</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.8422498847923144</v>
+        <v>0.8327864029407154</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8719,22 +8719,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1562310834423227</v>
+        <v>0.1571173932199903</v>
       </c>
       <c r="C91">
-        <v>-15743.61420740521</v>
+        <v>-16562.51458486514</v>
       </c>
       <c r="D91">
-        <v>27004.45882435905</v>
+        <v>26789.44915512119</v>
       </c>
       <c r="E91">
-        <v>19779.00220955723</v>
+        <v>20382.8929177793</v>
       </c>
       <c r="F91">
-        <v>53746.27303176426</v>
+        <v>54350.16373998634</v>
       </c>
       <c r="G91">
         <v>10998.2</v>
@@ -8755,37 +8755,37 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M91">
-        <v>7225.164034979184</v>
+        <v>7306.345653349737</v>
       </c>
       <c r="N91">
-        <v>-1208.145667632244</v>
+        <v>-1289.327286002797</v>
       </c>
       <c r="O91">
-        <v>-241.6291335264488</v>
+        <v>-257.8654572005595</v>
       </c>
       <c r="P91">
-        <v>-966.5165341057952</v>
+        <v>-1031.461828802238</v>
       </c>
       <c r="Q91">
-        <v>3877.383465894204</v>
+        <v>3812.438171197762</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.5137729174940432</v>
+        <v>0.5605702092434475</v>
       </c>
       <c r="T91">
-        <v>7.239392200410419</v>
+        <v>7.963331420451461</v>
       </c>
       <c r="U91">
         <v>0.1344309777667576</v>
       </c>
       <c r="V91">
-        <v>0.1665572805881431</v>
+        <v>0.1647066441371637</v>
       </c>
       <c r="W91">
-        <v>0.1120405196831213</v>
+        <v>0.1122893025507173</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.8327864029407154</v>
+        <v>0.8235332206858185</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8801,22 +8801,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1571173932199903</v>
+        <v>0.1580037029976579</v>
       </c>
       <c r="C92">
-        <v>-16562.51458486514</v>
+        <v>-17378.01819079174</v>
       </c>
       <c r="D92">
-        <v>26789.44915512119</v>
+        <v>26577.83625741666</v>
       </c>
       <c r="E92">
-        <v>20382.8929177793</v>
+        <v>20986.78362600137</v>
       </c>
       <c r="F92">
-        <v>54350.16373998634</v>
+        <v>54954.05444820841</v>
       </c>
       <c r="G92">
         <v>10998.2</v>
@@ -8837,37 +8837,37 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M92">
-        <v>7306.345653349737</v>
+        <v>7387.52727172029</v>
       </c>
       <c r="N92">
-        <v>-1289.327286002797</v>
+        <v>-1370.50890437335</v>
       </c>
       <c r="O92">
-        <v>-257.8654572005595</v>
+        <v>-274.1017808746699</v>
       </c>
       <c r="P92">
-        <v>-1031.461828802238</v>
+        <v>-1096.40712349868</v>
       </c>
       <c r="Q92">
-        <v>3812.438171197762</v>
+        <v>3747.49287650132</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.5605702092434475</v>
+        <v>0.6177668991593863</v>
       </c>
       <c r="T92">
-        <v>7.963331420451461</v>
+        <v>8.848146022723849</v>
       </c>
       <c r="U92">
         <v>0.1344309777667576</v>
       </c>
       <c r="V92">
-        <v>0.1647066441371637</v>
+        <v>0.1628966810147773</v>
       </c>
       <c r="W92">
-        <v>0.1122893025507173</v>
+        <v>0.1125326176629814</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.8235332206858185</v>
+        <v>0.8144834050738865</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8883,22 +8883,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1580037029976579</v>
+        <v>0.1588900127753254</v>
       </c>
       <c r="C93">
-        <v>-17378.01819079174</v>
+        <v>-18190.20488878432</v>
       </c>
       <c r="D93">
-        <v>26577.83625741666</v>
+        <v>26369.54026764616</v>
       </c>
       <c r="E93">
-        <v>20986.78362600137</v>
+        <v>21590.67433422344</v>
       </c>
       <c r="F93">
-        <v>54954.05444820841</v>
+        <v>55557.94515643048</v>
       </c>
       <c r="G93">
         <v>10998.2</v>
@@ -8919,37 +8919,37 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M93">
-        <v>7387.52727172029</v>
+        <v>7468.708890090842</v>
       </c>
       <c r="N93">
-        <v>-1370.50890437335</v>
+        <v>-1451.690522743902</v>
       </c>
       <c r="O93">
-        <v>-274.1017808746699</v>
+        <v>-290.3381045487804</v>
       </c>
       <c r="P93">
-        <v>-1096.40712349868</v>
+        <v>-1161.352418195122</v>
       </c>
       <c r="Q93">
-        <v>3747.49287650132</v>
+        <v>3682.547581804878</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.6177668991593863</v>
+        <v>0.6892627615543098</v>
       </c>
       <c r="T93">
-        <v>8.848146022723849</v>
+        <v>9.954164275564333</v>
       </c>
       <c r="U93">
         <v>0.1344309777667576</v>
       </c>
       <c r="V93">
-        <v>0.1628966810147773</v>
+        <v>0.1611260649167906</v>
       </c>
       <c r="W93">
-        <v>0.1125326176629814</v>
+        <v>0.1127706433162834</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.8144834050738865</v>
+        <v>0.8056303245839529</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8965,22 +8965,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1588900127753254</v>
+        <v>0.1875557593128538</v>
       </c>
       <c r="C94">
-        <v>-18190.20488878432</v>
+        <v>-24126.52484917682</v>
       </c>
       <c r="D94">
-        <v>26369.54026764616</v>
+        <v>21037.11101547573</v>
       </c>
       <c r="E94">
-        <v>21590.67433422344</v>
+        <v>22194.56504244552</v>
       </c>
       <c r="F94">
-        <v>55557.94515643048</v>
+        <v>56161.83586465255</v>
       </c>
       <c r="G94">
         <v>10998.2</v>
@@ -9001,45 +9001,45 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M94">
-        <v>7468.708890090842</v>
+        <v>9133.654279844597</v>
       </c>
       <c r="N94">
-        <v>-1451.690522743902</v>
+        <v>-3116.635912497657</v>
       </c>
       <c r="O94">
-        <v>-290.3381045487804</v>
+        <v>-623.3271824995314</v>
       </c>
       <c r="P94">
-        <v>-1161.352418195122</v>
+        <v>-2493.308729998126</v>
       </c>
       <c r="Q94">
-        <v>3682.547581804878</v>
+        <v>2350.591270001874</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.6892627615543098</v>
+        <v>0.8033779669172215</v>
       </c>
       <c r="T94">
-        <v>9.954164275564333</v>
+        <v>11.71949020954429</v>
       </c>
       <c r="U94">
-        <v>0.1344309777667576</v>
+        <v>0.1626309777667576</v>
       </c>
       <c r="V94">
-        <v>0.1611260649167906</v>
+        <v>0.1317548964082165</v>
       </c>
       <c r="W94">
-        <v>0.1127706433162834</v>
+        <v>0.1412035501383315</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y94">
-        <v>0.8056303245839529</v>
+        <v>0.6587744820410824</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9047,22 +9047,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1875557593128538</v>
+        <v>0.1887240690905213</v>
       </c>
       <c r="C95">
-        <v>-24126.52484917682</v>
+        <v>-24902.38003230963</v>
       </c>
       <c r="D95">
-        <v>21037.11101547573</v>
+        <v>20865.14654056499</v>
       </c>
       <c r="E95">
-        <v>22194.56504244552</v>
+        <v>22798.45575066758</v>
       </c>
       <c r="F95">
-        <v>56161.83586465255</v>
+        <v>56765.72657287462</v>
       </c>
       <c r="G95">
         <v>10998.2</v>
@@ -9083,37 +9083,37 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M95">
-        <v>9133.654279844597</v>
+        <v>9231.865616187013</v>
       </c>
       <c r="N95">
-        <v>-3116.635912497657</v>
+        <v>-3214.847248840073</v>
       </c>
       <c r="O95">
-        <v>-623.3271824995314</v>
+        <v>-642.9694497680147</v>
       </c>
       <c r="P95">
-        <v>-2493.308729998126</v>
+        <v>-2571.877799072058</v>
       </c>
       <c r="Q95">
-        <v>2350.591270001874</v>
+        <v>2272.022200927941</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.8033779669172215</v>
+        <v>0.9296409614034254</v>
       </c>
       <c r="T95">
-        <v>11.71949020954429</v>
+        <v>13.67273857780168</v>
       </c>
       <c r="U95">
         <v>0.1626309777667576</v>
       </c>
       <c r="V95">
-        <v>0.1317548964082165</v>
+        <v>0.1303532485740865</v>
       </c>
       <c r="W95">
-        <v>0.1412035501383315</v>
+        <v>0.1414315014960807</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.6587744820410824</v>
+        <v>0.6517662428704325</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9129,22 +9129,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1887240690905213</v>
+        <v>0.2430383165143261</v>
       </c>
       <c r="C96">
-        <v>-24902.38003230963</v>
+        <v>-31251.98360082108</v>
       </c>
       <c r="D96">
-        <v>20865.14654056499</v>
+        <v>15119.43368027561</v>
       </c>
       <c r="E96">
-        <v>22798.45575066758</v>
+        <v>23402.34645888965</v>
       </c>
       <c r="F96">
-        <v>56765.72657287462</v>
+        <v>57369.61728109669</v>
       </c>
       <c r="G96">
         <v>10998.2</v>
@@ -9165,45 +9165,45 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M96">
-        <v>9231.865616187013</v>
+        <v>12428.03628570865</v>
       </c>
       <c r="N96">
-        <v>-3214.847248840073</v>
+        <v>-6411.017918361707</v>
       </c>
       <c r="O96">
-        <v>-642.9694497680147</v>
+        <v>-1282.203583672342</v>
       </c>
       <c r="P96">
-        <v>-2571.877799072058</v>
+        <v>-5128.814334689366</v>
       </c>
       <c r="Q96">
-        <v>2272.022200927941</v>
+        <v>-284.9143346893661</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.9296409614034254</v>
+        <v>1.143327906606855</v>
       </c>
       <c r="T96">
-        <v>13.67273857780168</v>
+        <v>16.97840765950645</v>
       </c>
       <c r="U96">
-        <v>0.1626309777667576</v>
+        <v>0.2166309777667576</v>
       </c>
       <c r="V96">
-        <v>0.1303532485740865</v>
+        <v>0.09682975216713974</v>
       </c>
       <c r="W96">
-        <v>0.1414315014960807</v>
+        <v>0.1956546538778773</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y96">
-        <v>0.6517662428704325</v>
+        <v>0.4841487608356986</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9211,22 +9211,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2430383165143261</v>
+        <v>0.2447466262919937</v>
       </c>
       <c r="C97">
-        <v>-31251.98360082108</v>
+        <v>-31985.70147359584</v>
       </c>
       <c r="D97">
-        <v>15119.43368027561</v>
+        <v>14989.60651572292</v>
       </c>
       <c r="E97">
-        <v>23402.34645888965</v>
+        <v>24006.23716711173</v>
       </c>
       <c r="F97">
-        <v>57369.61728109669</v>
+        <v>57973.50798931876</v>
       </c>
       <c r="G97">
         <v>10998.2</v>
@@ -9247,37 +9247,37 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M97">
-        <v>12428.03628570865</v>
+        <v>12558.85772029506</v>
       </c>
       <c r="N97">
-        <v>-6411.017918361707</v>
+        <v>-6541.839352948116</v>
       </c>
       <c r="O97">
-        <v>-1282.203583672342</v>
+        <v>-1308.367870589623</v>
       </c>
       <c r="P97">
-        <v>-5128.814334689366</v>
+        <v>-5233.471482358493</v>
       </c>
       <c r="Q97">
-        <v>-284.9143346893661</v>
+        <v>-389.5714823584931</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.143327906606855</v>
+        <v>1.41770988325857</v>
       </c>
       <c r="T97">
-        <v>16.97840765950645</v>
+        <v>21.22300957438307</v>
       </c>
       <c r="U97">
         <v>0.2166309777667576</v>
       </c>
       <c r="V97">
-        <v>0.09682975216713974</v>
+        <v>0.09582110891539868</v>
       </c>
       <c r="W97">
-        <v>0.1956546538778773</v>
+        <v>0.1958731572517198</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.4841487608356986</v>
+        <v>0.4791055445769934</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9293,22 +9293,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2447466262919937</v>
+        <v>0.2464549360696613</v>
       </c>
       <c r="C98">
-        <v>-31985.70147359584</v>
+        <v>-32717.20873526919</v>
       </c>
       <c r="D98">
-        <v>14989.60651572292</v>
+        <v>14861.98996227163</v>
       </c>
       <c r="E98">
-        <v>24006.23716711172</v>
+        <v>24610.12787533379</v>
       </c>
       <c r="F98">
-        <v>57973.50798931876</v>
+        <v>58577.39869754083</v>
       </c>
       <c r="G98">
         <v>10998.2</v>
@@ -9329,37 +9329,37 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M98">
-        <v>12558.85772029505</v>
+        <v>12689.67915488146</v>
       </c>
       <c r="N98">
-        <v>-6541.839352948115</v>
+        <v>-6672.660787534522</v>
       </c>
       <c r="O98">
-        <v>-1308.367870589623</v>
+        <v>-1334.532157506904</v>
       </c>
       <c r="P98">
-        <v>-5233.471482358492</v>
+        <v>-5338.128630027617</v>
       </c>
       <c r="Q98">
-        <v>-389.5714823584922</v>
+        <v>-494.2286300276173</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.417709883258566</v>
+        <v>1.875013177678089</v>
       </c>
       <c r="T98">
-        <v>21.22300957438302</v>
+        <v>28.29734609917736</v>
       </c>
       <c r="U98">
         <v>0.2166309777667576</v>
       </c>
       <c r="V98">
-        <v>0.09582110891539869</v>
+        <v>0.09483326243173479</v>
       </c>
       <c r="W98">
-        <v>0.1958731572517198</v>
+        <v>0.1960871554013594</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.4791055445769934</v>
+        <v>0.4741663121586739</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9375,22 +9375,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2464549360696613</v>
+        <v>0.2481632458473288</v>
       </c>
       <c r="C99">
-        <v>-32717.20873526919</v>
+        <v>-33446.56137044267</v>
       </c>
       <c r="D99">
-        <v>14861.98996227163</v>
+        <v>14736.52803532023</v>
       </c>
       <c r="E99">
-        <v>24610.12787533379</v>
+        <v>25214.01858355586</v>
       </c>
       <c r="F99">
-        <v>58577.39869754083</v>
+        <v>59181.28940576289</v>
       </c>
       <c r="G99">
         <v>10998.2</v>
@@ -9411,37 +9411,37 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M99">
-        <v>12689.67915488146</v>
+        <v>12820.50058946787</v>
       </c>
       <c r="N99">
-        <v>-6672.660787534522</v>
+        <v>-6803.482222120927</v>
       </c>
       <c r="O99">
-        <v>-1334.532157506904</v>
+        <v>-1360.696444424186</v>
       </c>
       <c r="P99">
-        <v>-5338.128630027617</v>
+        <v>-5442.785777696741</v>
       </c>
       <c r="Q99">
-        <v>-494.2286300276173</v>
+        <v>-598.8857776967416</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.875013177678089</v>
+        <v>2.789619766517132</v>
       </c>
       <c r="T99">
-        <v>28.29734609917736</v>
+        <v>42.44601914876603</v>
       </c>
       <c r="U99">
         <v>0.2166309777667576</v>
       </c>
       <c r="V99">
-        <v>0.09483326243173479</v>
+        <v>0.09386557608039056</v>
       </c>
       <c r="W99">
-        <v>0.1960871554013594</v>
+        <v>0.1962967862418226</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.4741663121586739</v>
+        <v>0.4693278804019527</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9457,22 +9457,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2481632458473288</v>
+        <v>0.2498715556249964</v>
       </c>
       <c r="C100">
-        <v>-33446.56137044267</v>
+        <v>-34173.81348909996</v>
       </c>
       <c r="D100">
-        <v>14736.52803532023</v>
+        <v>14613.16662488501</v>
       </c>
       <c r="E100">
-        <v>25214.01858355586</v>
+        <v>25817.90929177793</v>
       </c>
       <c r="F100">
-        <v>59181.28940576289</v>
+        <v>59785.18011398497</v>
       </c>
       <c r="G100">
         <v>10998.2</v>
@@ -9493,37 +9493,37 @@
         <v>6017.01836734694</v>
       </c>
       <c r="M100">
-        <v>12820.50058946787</v>
+        <v>12951.32202405428</v>
       </c>
       <c r="N100">
-        <v>-6803.482222120927</v>
+        <v>-6934.303656707336</v>
       </c>
       <c r="O100">
-        <v>-1360.696444424186</v>
+        <v>-1386.860731341467</v>
       </c>
       <c r="P100">
-        <v>-5442.785777696741</v>
+        <v>-5547.442925365869</v>
       </c>
       <c r="Q100">
-        <v>-598.8857776967416</v>
+        <v>-703.5429253658695</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.789619766517132</v>
+        <v>5.533439533034263</v>
       </c>
       <c r="T100">
-        <v>42.44601914876603</v>
+        <v>84.89203829753205</v>
       </c>
       <c r="U100">
         <v>0.2166309777667576</v>
       </c>
       <c r="V100">
-        <v>0.09386557608039056</v>
+        <v>0.09291743894826539</v>
       </c>
       <c r="W100">
-        <v>0.1962967862418226</v>
+        <v>0.1965021821158118</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9531,91 +9531,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.4693278804019527</v>
+        <v>0.4645871947413269</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2498715556249964</v>
-      </c>
-      <c r="C101">
-        <v>-34173.81348909996</v>
-      </c>
-      <c r="D101">
-        <v>14613.16662488501</v>
-      </c>
-      <c r="E101">
-        <v>25817.90929177793</v>
-      </c>
-      <c r="F101">
-        <v>59785.18011398497</v>
-      </c>
-      <c r="G101">
-        <v>10998.2</v>
-      </c>
-      <c r="H101">
-        <v>26421.8</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>10860.91836734694</v>
-      </c>
-      <c r="K101">
-        <v>4843.9</v>
-      </c>
-      <c r="L101">
-        <v>6017.01836734694</v>
-      </c>
-      <c r="M101">
-        <v>12951.32202405428</v>
-      </c>
-      <c r="N101">
-        <v>-6934.303656707336</v>
-      </c>
-      <c r="O101">
-        <v>-1386.860731341467</v>
-      </c>
-      <c r="P101">
-        <v>-5547.442925365869</v>
-      </c>
-      <c r="Q101">
-        <v>-703.5429253658695</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>5.533439533034263</v>
-      </c>
-      <c r="T101">
-        <v>84.89203829753205</v>
-      </c>
-      <c r="U101">
-        <v>0.2166309777667576</v>
-      </c>
-      <c r="V101">
-        <v>0.09291743894826539</v>
-      </c>
-      <c r="W101">
-        <v>0.1965021821158118</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>C2/C</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.4645871947413269</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
